--- a/hmm_regime_results_weekly.xlsx
+++ b/hmm_regime_results_weekly.xlsx
@@ -786,13 +786,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8619021926297404</v>
+        <v>0.8619021926294949</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1380554024303599</v>
+        <v>0.1380554024306054</v>
       </c>
       <c r="D22" t="n">
-        <v>4.240493989961779e-05</v>
+        <v>4.240493989978257e-05</v>
       </c>
     </row>
     <row r="23">
@@ -802,13 +802,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>8.6403233909171e-06</v>
+        <v>8.640323391013399e-06</v>
       </c>
       <c r="C23" t="n">
-        <v>4.89716231742568e-06</v>
+        <v>4.897162317452685e-06</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9999864625142917</v>
+        <v>0.9999864625142915</v>
       </c>
     </row>
     <row r="24">
@@ -818,13 +818,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.01687570795005601</v>
+        <v>0.0168757079500379</v>
       </c>
       <c r="C24" t="n">
-        <v>0.9767174394813074</v>
+        <v>0.9767174394813007</v>
       </c>
       <c r="D24" t="n">
-        <v>0.006406852568636602</v>
+        <v>0.006406852568661279</v>
       </c>
     </row>
     <row r="27">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.8619021926297404</v>
+        <v>0.8619021926294949</v>
       </c>
       <c r="C28" t="n">
-        <v>7.241244586301504</v>
+        <v>7.241244586288627</v>
       </c>
     </row>
     <row r="29">
@@ -859,7 +859,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4.89716231742568e-06</v>
+        <v>4.897162317452685e-06</v>
       </c>
       <c r="C29" t="n">
         <v>1.0000048971863</v>
@@ -872,10 +872,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.006406852568636602</v>
+        <v>0.006406852568661279</v>
       </c>
       <c r="C30" t="n">
-        <v>1.006448165011202</v>
+        <v>1.006448165011226</v>
       </c>
     </row>
     <row r="33">
@@ -1210,7 +1210,7 @@
         <v>8</v>
       </c>
       <c r="B4" t="n">
-        <v>3226.761072632768</v>
+        <v>3226.761072632718</v>
       </c>
       <c r="C4" t="n">
         <v>3</v>
@@ -1262,7 +1262,7 @@
         <v>1</v>
       </c>
       <c r="B6" t="n">
-        <v>3226.331016445572</v>
+        <v>3226.331016445612</v>
       </c>
       <c r="C6" t="n">
         <v>3</v>
@@ -1288,7 +1288,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>3224.096920605834</v>
+        <v>3224.096920605832</v>
       </c>
       <c r="C7" t="n">
         <v>3</v>
@@ -1314,7 +1314,7 @@
         <v>35</v>
       </c>
       <c r="B8" t="n">
-        <v>3223.593795118616</v>
+        <v>3223.59379511862</v>
       </c>
       <c r="C8" t="n">
         <v>3</v>
@@ -1496,7 +1496,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>3222.149795067055</v>
+        <v>3222.149795067125</v>
       </c>
       <c r="C15" t="n">
         <v>3</v>
@@ -1548,7 +1548,7 @@
         <v>17</v>
       </c>
       <c r="B17" t="n">
-        <v>3221.791824187165</v>
+        <v>3221.791824187164</v>
       </c>
       <c r="C17" t="n">
         <v>2</v>
@@ -1626,7 +1626,7 @@
         <v>12</v>
       </c>
       <c r="B20" t="n">
-        <v>3221.428469138203</v>
+        <v>3221.428469138204</v>
       </c>
       <c r="C20" t="n">
         <v>3</v>
@@ -1652,7 +1652,7 @@
         <v>39</v>
       </c>
       <c r="B21" t="n">
-        <v>3221.080350483249</v>
+        <v>3221.080350483254</v>
       </c>
       <c r="C21" t="n">
         <v>3</v>
@@ -1730,7 +1730,7 @@
         <v>25</v>
       </c>
       <c r="B24" t="n">
-        <v>3219.862888495672</v>
+        <v>3219.862888495697</v>
       </c>
       <c r="C24" t="n">
         <v>3</v>
@@ -1756,7 +1756,7 @@
         <v>9</v>
       </c>
       <c r="B25" t="n">
-        <v>3219.650822917364</v>
+        <v>3219.650822917376</v>
       </c>
       <c r="C25" t="n">
         <v>2</v>
@@ -1834,7 +1834,7 @@
         <v>29</v>
       </c>
       <c r="B28" t="n">
-        <v>3218.673495428613</v>
+        <v>3218.673495428617</v>
       </c>
       <c r="C28" t="n">
         <v>3</v>
@@ -1912,7 +1912,7 @@
         <v>38</v>
       </c>
       <c r="B31" t="n">
-        <v>3218.45629468851</v>
+        <v>3218.456294688571</v>
       </c>
       <c r="C31" t="n">
         <v>3</v>
@@ -1990,7 +1990,7 @@
         <v>26</v>
       </c>
       <c r="B34" t="n">
-        <v>3217.92247811992</v>
+        <v>3217.92247811985</v>
       </c>
       <c r="C34" t="n">
         <v>3</v>
@@ -2068,7 +2068,7 @@
         <v>3</v>
       </c>
       <c r="B37" t="n">
-        <v>3215.96976882414</v>
+        <v>3215.969768824141</v>
       </c>
       <c r="C37" t="n">
         <v>3</v>
@@ -2120,7 +2120,7 @@
         <v>11</v>
       </c>
       <c r="B39" t="n">
-        <v>3199.176643631522</v>
+        <v>3199.176643631533</v>
       </c>
       <c r="C39" t="n">
         <v>3</v>
@@ -2172,7 +2172,7 @@
         <v>32</v>
       </c>
       <c r="B41" t="n">
-        <v>3198.93903820067</v>
+        <v>3198.939038200667</v>
       </c>
       <c r="C41" t="n">
         <v>3</v>
@@ -2253,10 +2253,10 @@
         <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>5.976004838374711e-26</v>
+        <v>5.976004838619293e-26</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0001021876833804352</v>
+        <v>0.0001021876833898221</v>
       </c>
       <c r="G2" t="n">
         <v>0.9998978123168114</v>
@@ -2276,13 +2276,13 @@
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001445684371187945</v>
+        <v>0.001445684371193204</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9938441611393141</v>
+        <v>0.9938441611388622</v>
       </c>
       <c r="G3" t="n">
-        <v>0.004710154489698305</v>
+        <v>0.004710154489743285</v>
       </c>
     </row>
     <row r="4">
@@ -2299,10 +2299,10 @@
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>0.000419815910016176</v>
+        <v>0.0004198159100167487</v>
       </c>
       <c r="F4" t="n">
-        <v>0.005713253951696131</v>
+        <v>0.005713253951750691</v>
       </c>
       <c r="G4" t="n">
         <v>0.993866930138109</v>
@@ -2322,13 +2322,13 @@
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001342025989059798</v>
+        <v>0.00134202598906529</v>
       </c>
       <c r="F5" t="n">
         <v>0.9852574525268196</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01340052148412566</v>
+        <v>0.01340052148424754</v>
       </c>
     </row>
     <row r="6">
@@ -2345,13 +2345,13 @@
         <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0008371854991637411</v>
+        <v>0.0008371854991660254</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0138260396990506</v>
+        <v>0.01382603969916377</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9853367748018993</v>
+        <v>0.9853367748014512</v>
       </c>
     </row>
     <row r="7">
@@ -2368,13 +2368,13 @@
         <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>0.004424430367019562</v>
+        <v>0.00442443036703767</v>
       </c>
       <c r="F7" t="n">
         <v>0.9772656205620346</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01830994907086682</v>
+        <v>0.01830994907103335</v>
       </c>
     </row>
     <row r="8">
@@ -2391,10 +2391,10 @@
         <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0007199505585254658</v>
+        <v>0.0007199505585264481</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02188073657070164</v>
+        <v>0.02188073657088074</v>
       </c>
       <c r="G8" t="n">
         <v>0.9773993128707463</v>
@@ -2414,13 +2414,13 @@
         <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>0.000437070766220742</v>
+        <v>0.0004370707662227296</v>
       </c>
       <c r="F9" t="n">
         <v>0.9716397486078188</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02792318062587565</v>
+        <v>0.02792318062610421</v>
       </c>
     </row>
     <row r="10">
@@ -2437,10 +2437,10 @@
         <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0001086271810501195</v>
+        <v>0.0001086271810503665</v>
       </c>
       <c r="F10" t="n">
-        <v>0.02804242515636832</v>
+        <v>0.02804242515661061</v>
       </c>
       <c r="G10" t="n">
         <v>0.9718489476624969</v>
@@ -2460,13 +2460,13 @@
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0006595876272084761</v>
+        <v>0.0006595876272111756</v>
       </c>
       <c r="F11" t="n">
         <v>0.965844385796883</v>
       </c>
       <c r="G11" t="n">
-        <v>0.03349602657571898</v>
+        <v>0.03349602657599317</v>
       </c>
     </row>
     <row r="12">
@@ -2483,13 +2483,13 @@
         <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0001332614472176088</v>
+        <v>0.00013326144721773</v>
       </c>
       <c r="F12" t="n">
-        <v>0.03381197785122855</v>
+        <v>0.03381197785148993</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9660547607017504</v>
+        <v>0.9660547607013111</v>
       </c>
     </row>
     <row r="13">
@@ -2506,13 +2506,13 @@
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>0.000397920470899422</v>
+        <v>0.0003979204709012315</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9588822186817975</v>
+        <v>0.9588822186813615</v>
       </c>
       <c r="G13" t="n">
-        <v>0.04071986084741378</v>
+        <v>0.04071986084772858</v>
       </c>
     </row>
     <row r="14">
@@ -2529,13 +2529,13 @@
         <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>9.222160622299786e-05</v>
+        <v>9.222160622312367e-05</v>
       </c>
       <c r="F14" t="n">
-        <v>0.04075516609053222</v>
+        <v>0.04075516609084729</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9591526123032316</v>
+        <v>0.9591526123027954</v>
       </c>
     </row>
     <row r="15">
@@ -2552,13 +2552,13 @@
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>0.001102993309154281</v>
+        <v>0.001102993309156287</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9512879443815239</v>
+        <v>0.9512879443810912</v>
       </c>
       <c r="G15" t="n">
-        <v>0.04760906230942698</v>
+        <v>0.04760906230979504</v>
       </c>
     </row>
     <row r="16">
@@ -2575,13 +2575,13 @@
         <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>0.001046563237447664</v>
+        <v>0.001046563237449568</v>
       </c>
       <c r="F16" t="n">
-        <v>0.04737120691707267</v>
+        <v>0.04737120691743888</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9515822298454246</v>
+        <v>0.9515822298449919</v>
       </c>
     </row>
     <row r="17">
@@ -2598,13 +2598,13 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0009816920990921337</v>
+        <v>0.0009816920990965981</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9469624711378645</v>
+        <v>0.9469624711374338</v>
       </c>
       <c r="G17" t="n">
-        <v>0.05205583676301565</v>
+        <v>0.05205583676344176</v>
       </c>
     </row>
     <row r="18">
@@ -2621,13 +2621,13 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0002884105470356657</v>
+        <v>0.0002884105470360591</v>
       </c>
       <c r="F18" t="n">
-        <v>0.05228956586532863</v>
+        <v>0.05228956586578042</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9474220235875876</v>
+        <v>0.9474220235871568</v>
       </c>
     </row>
     <row r="19">
@@ -2644,13 +2644,13 @@
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0004199937410274114</v>
+        <v>0.0004199937410293213</v>
       </c>
       <c r="F19" t="n">
-        <v>0.943258067517255</v>
+        <v>0.9432580675168262</v>
       </c>
       <c r="G19" t="n">
-        <v>0.05632193874150294</v>
+        <v>0.05632193874198957</v>
       </c>
     </row>
     <row r="20">
@@ -2667,13 +2667,13 @@
         <v>2</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0001465772413754848</v>
+        <v>0.0001465772413756848</v>
       </c>
       <c r="F20" t="n">
-        <v>0.05597621118771131</v>
+        <v>0.0559762111881695</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9438772115707704</v>
+        <v>0.9438772115703412</v>
       </c>
     </row>
     <row r="21">
@@ -2690,13 +2690,13 @@
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0002810930101109607</v>
+        <v>0.0002810930101122389</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9402006497961637</v>
+        <v>0.9402006497957361</v>
       </c>
       <c r="G21" t="n">
-        <v>0.05951825719374518</v>
+        <v>0.05951825719425943</v>
       </c>
     </row>
     <row r="22">
@@ -2713,13 +2713,13 @@
         <v>2</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0001129341809792199</v>
+        <v>0.0001129341809794253</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0589530235266889</v>
+        <v>0.05895302352719827</v>
       </c>
       <c r="G22" t="n">
-        <v>0.9409340422921296</v>
+        <v>0.9409340422917017</v>
       </c>
     </row>
     <row r="23">
@@ -2736,13 +2736,13 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0006820704832946834</v>
+        <v>0.0006820704832968545</v>
       </c>
       <c r="F23" t="n">
-        <v>0.93655965547696</v>
+        <v>0.9365596554765341</v>
       </c>
       <c r="G23" t="n">
-        <v>0.06275827403960488</v>
+        <v>0.06275827404014711</v>
       </c>
     </row>
     <row r="24">
@@ -2759,13 +2759,13 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0004215118705131776</v>
+        <v>0.000421511870514136</v>
       </c>
       <c r="F24" t="n">
-        <v>0.06231862215664123</v>
+        <v>0.06231862215712299</v>
       </c>
       <c r="G24" t="n">
-        <v>0.9372598659727223</v>
+        <v>0.937259865972296</v>
       </c>
     </row>
     <row r="25">
@@ -2782,13 +2782,13 @@
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>0.003026721831407741</v>
+        <v>0.003026721831410494</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9315738496193562</v>
+        <v>0.9315738496189325</v>
       </c>
       <c r="G25" t="n">
-        <v>0.06539942854918621</v>
+        <v>0.06539942854966205</v>
       </c>
     </row>
     <row r="26">
@@ -2805,13 +2805,13 @@
         <v>2</v>
       </c>
       <c r="E26" t="n">
-        <v>0.003064599498968182</v>
+        <v>0.003064599498972363</v>
       </c>
       <c r="F26" t="n">
-        <v>0.06455102397812824</v>
+        <v>0.06455102397862728</v>
       </c>
       <c r="G26" t="n">
-        <v>0.9323843765229541</v>
+        <v>0.9323843765225301</v>
       </c>
     </row>
     <row r="27">
@@ -2828,13 +2828,13 @@
         <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>0.00611633584747516</v>
+        <v>0.006116335847480722</v>
       </c>
       <c r="F27" t="n">
-        <v>0.9267951685013703</v>
+        <v>0.9267951685009489</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0670884956510415</v>
+        <v>0.06708849565159065</v>
       </c>
     </row>
     <row r="28">
@@ -2851,13 +2851,13 @@
         <v>2</v>
       </c>
       <c r="E28" t="n">
-        <v>0.007716679918962923</v>
+        <v>0.007716679918976959</v>
       </c>
       <c r="F28" t="n">
-        <v>0.06444567815326574</v>
+        <v>0.06444567815373464</v>
       </c>
       <c r="G28" t="n">
-        <v>0.9278376419279323</v>
+        <v>0.9278376419275103</v>
       </c>
     </row>
     <row r="29">
@@ -2874,13 +2874,13 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>0.000583898296213036</v>
+        <v>0.0005838982962148946</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9336497231502949</v>
+        <v>0.9336497231498704</v>
       </c>
       <c r="G29" t="n">
-        <v>0.06576637855356804</v>
+        <v>0.06576637855407645</v>
       </c>
     </row>
     <row r="30">
@@ -2897,13 +2897,13 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0006132539164884305</v>
+        <v>0.0006132539164903826</v>
       </c>
       <c r="F30" t="n">
-        <v>0.06357345848749436</v>
+        <v>0.06357345848795692</v>
       </c>
       <c r="G30" t="n">
-        <v>0.9358132875962302</v>
+        <v>0.9358132875953791</v>
       </c>
     </row>
     <row r="31">
@@ -2920,13 +2920,13 @@
         <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>0.00177738597115057</v>
+        <v>0.001777385971154612</v>
       </c>
       <c r="F31" t="n">
-        <v>0.9333451897077991</v>
+        <v>0.9333451897073747</v>
       </c>
       <c r="G31" t="n">
-        <v>0.06487742432105487</v>
+        <v>0.06487742432152692</v>
       </c>
     </row>
     <row r="32">
@@ -2943,13 +2943,13 @@
         <v>2</v>
       </c>
       <c r="E32" t="n">
-        <v>0.001018891292222544</v>
+        <v>0.001018891292224398</v>
       </c>
       <c r="F32" t="n">
-        <v>0.06398418201893206</v>
+        <v>0.06398418201939762</v>
       </c>
       <c r="G32" t="n">
-        <v>0.934996926688926</v>
+        <v>0.9349969266885008</v>
       </c>
     </row>
     <row r="33">
@@ -2966,13 +2966,13 @@
         <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>0.000382355834995179</v>
+        <v>0.0003823558349960484</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9339723958798993</v>
+        <v>0.9339723958794747</v>
       </c>
       <c r="G33" t="n">
-        <v>0.06564524828512786</v>
+        <v>0.06564524828560549</v>
       </c>
     </row>
     <row r="34">
@@ -2989,13 +2989,13 @@
         <v>2</v>
       </c>
       <c r="E34" t="n">
-        <v>0.0002631572244782701</v>
+        <v>0.0002631572244789881</v>
       </c>
       <c r="F34" t="n">
-        <v>0.06410688929288144</v>
+        <v>0.06410688929334787</v>
       </c>
       <c r="G34" t="n">
-        <v>0.9356299534828147</v>
+        <v>0.9356299534823892</v>
       </c>
     </row>
     <row r="35">
@@ -3012,13 +3012,13 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>0.0001465683505943982</v>
+        <v>0.0001465683505946648</v>
       </c>
       <c r="F35" t="n">
-        <v>0.9342149883472703</v>
+        <v>0.9342149883464207</v>
       </c>
       <c r="G35" t="n">
-        <v>0.06563844330231985</v>
+        <v>0.06563844330276759</v>
       </c>
     </row>
     <row r="36">
@@ -3035,13 +3035,13 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>0.0001554317275845003</v>
+        <v>0.0001554317275850657</v>
       </c>
       <c r="F36" t="n">
-        <v>0.0636687309691792</v>
+        <v>0.06366873096967141</v>
       </c>
       <c r="G36" t="n">
-        <v>0.936175837303025</v>
+        <v>0.9361758373025993</v>
       </c>
     </row>
     <row r="37">
@@ -3058,13 +3058,13 @@
         <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>0.0001271266963179322</v>
+        <v>0.0001271266963181634</v>
       </c>
       <c r="F37" t="n">
-        <v>0.9347483794779415</v>
+        <v>0.9347483794775165</v>
       </c>
       <c r="G37" t="n">
-        <v>0.0651244938256603</v>
+        <v>0.06512449382613414</v>
       </c>
     </row>
     <row r="38">
@@ -3081,13 +3081,13 @@
         <v>2</v>
       </c>
       <c r="E38" t="n">
-        <v>0.0001948067416030515</v>
+        <v>0.0001948067416039374</v>
       </c>
       <c r="F38" t="n">
-        <v>0.0630998003370461</v>
+        <v>0.0630998003375339</v>
       </c>
       <c r="G38" t="n">
-        <v>0.9367053929211595</v>
+        <v>0.9367053929207335</v>
       </c>
     </row>
     <row r="39">
@@ -3107,10 +3107,10 @@
         <v>0.001294843993770586</v>
       </c>
       <c r="F39" t="n">
-        <v>0.9341046842433077</v>
+        <v>0.934104684242883</v>
       </c>
       <c r="G39" t="n">
-        <v>0.06460047176312463</v>
+        <v>0.06460047176356527</v>
       </c>
     </row>
     <row r="40">
@@ -3127,13 +3127,13 @@
         <v>2</v>
       </c>
       <c r="E40" t="n">
-        <v>0.003573577064809355</v>
+        <v>0.003573577064823981</v>
       </c>
       <c r="F40" t="n">
-        <v>0.06030635292119968</v>
+        <v>0.06030635292163847</v>
       </c>
       <c r="G40" t="n">
-        <v>0.9361200700138632</v>
+        <v>0.9361200700134374</v>
       </c>
     </row>
     <row r="41">
@@ -3150,13 +3150,13 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>0.005553926569668554</v>
+        <v>0.005553926569678657</v>
       </c>
       <c r="F41" t="n">
-        <v>0.9330930376608449</v>
+        <v>0.9330930376604206</v>
       </c>
       <c r="G41" t="n">
-        <v>0.06135303576949673</v>
+        <v>0.06135303576994313</v>
       </c>
     </row>
     <row r="42">
@@ -3173,13 +3173,13 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>0.01015055600441829</v>
+        <v>0.01015055600444599</v>
       </c>
       <c r="F42" t="n">
-        <v>0.05466166976159985</v>
+        <v>0.05466166976194785</v>
       </c>
       <c r="G42" t="n">
-        <v>0.9351877742338163</v>
+        <v>0.9351877742333909</v>
       </c>
     </row>
     <row r="43">
@@ -3196,13 +3196,13 @@
         <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>0.03690528861869385</v>
+        <v>0.03690528861874419</v>
       </c>
       <c r="F43" t="n">
-        <v>0.9077038490272668</v>
+        <v>0.907703849026854</v>
       </c>
       <c r="G43" t="n">
-        <v>0.0553908623539858</v>
+        <v>0.05539086235436364</v>
       </c>
     </row>
     <row r="44">
@@ -3219,13 +3219,13 @@
         <v>2</v>
       </c>
       <c r="E44" t="n">
-        <v>0.03001075101247412</v>
+        <v>0.03001075101250141</v>
       </c>
       <c r="F44" t="n">
-        <v>0.06067785928501549</v>
+        <v>0.06067785928540179</v>
       </c>
       <c r="G44" t="n">
-        <v>0.9093113897025121</v>
+        <v>0.9093113897020986</v>
       </c>
     </row>
     <row r="45">
@@ -3242,13 +3242,13 @@
         <v>1</v>
       </c>
       <c r="E45" t="n">
-        <v>0.01091092248743402</v>
+        <v>0.01091092248745386</v>
       </c>
       <c r="F45" t="n">
-        <v>0.9275794101600031</v>
+        <v>0.9275794101595813</v>
       </c>
       <c r="G45" t="n">
-        <v>0.06150966735241109</v>
+        <v>0.06150966735280269</v>
       </c>
     </row>
     <row r="46">
@@ -3265,13 +3265,13 @@
         <v>2</v>
       </c>
       <c r="E46" t="n">
-        <v>0.004705910110374513</v>
+        <v>0.004705910110376653</v>
       </c>
       <c r="F46" t="n">
-        <v>0.06575141966257123</v>
+        <v>0.06575141966298982</v>
       </c>
       <c r="G46" t="n">
-        <v>0.9295426702271929</v>
+        <v>0.9295426702267703</v>
       </c>
     </row>
     <row r="47">
@@ -3288,13 +3288,13 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>0.0003995235266897487</v>
+        <v>0.0003995235266904755</v>
       </c>
       <c r="F47" t="n">
-        <v>0.9324544095862239</v>
+        <v>0.9324544095857998</v>
       </c>
       <c r="G47" t="n">
-        <v>0.06714606688722149</v>
+        <v>0.06714606688764899</v>
       </c>
     </row>
     <row r="48">
@@ -3311,13 +3311,13 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>0.000317614310529978</v>
+        <v>0.0003176143105308446</v>
       </c>
       <c r="F48" t="n">
-        <v>0.06528949277708038</v>
+        <v>0.06528949277749604</v>
       </c>
       <c r="G48" t="n">
-        <v>0.9343928929125017</v>
+        <v>0.9343928929120768</v>
       </c>
     </row>
     <row r="49">
@@ -3334,13 +3334,13 @@
         <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>0.0001168714206696206</v>
+        <v>0.0001168714206698332</v>
       </c>
       <c r="F49" t="n">
-        <v>0.9333467899756045</v>
+        <v>0.9333467899751801</v>
       </c>
       <c r="G49" t="n">
-        <v>0.06653633860395039</v>
+        <v>0.066536338604374</v>
       </c>
     </row>
     <row r="50">
@@ -3357,13 +3357,13 @@
         <v>2</v>
       </c>
       <c r="E50" t="n">
-        <v>0.0001801675410665019</v>
+        <v>0.0001801675410672393</v>
       </c>
       <c r="F50" t="n">
-        <v>0.06406655668719667</v>
+        <v>0.06406655668760455</v>
       </c>
       <c r="G50" t="n">
-        <v>0.9357532757715774</v>
+        <v>0.9357532757711519</v>
       </c>
     </row>
     <row r="51">
@@ -3380,13 +3380,13 @@
         <v>1</v>
       </c>
       <c r="E51" t="n">
-        <v>0.0002131638177847037</v>
+        <v>0.0002131638177850914</v>
       </c>
       <c r="F51" t="n">
-        <v>0.934590622727958</v>
+        <v>0.9345906227275329</v>
       </c>
       <c r="G51" t="n">
-        <v>0.06519621345417735</v>
+        <v>0.06519621345459242</v>
       </c>
     </row>
     <row r="52">
@@ -3403,13 +3403,13 @@
         <v>2</v>
       </c>
       <c r="E52" t="n">
-        <v>0.0004262745372586578</v>
+        <v>0.0004262745372602086</v>
       </c>
       <c r="F52" t="n">
-        <v>0.062269046655822</v>
+        <v>0.06226904665619012</v>
       </c>
       <c r="G52" t="n">
-        <v>0.9373046788068352</v>
+        <v>0.937304678806409</v>
       </c>
     </row>
     <row r="53">
@@ -3426,13 +3426,13 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>0.0001501473570018643</v>
+        <v>0.0001501473570020692</v>
       </c>
       <c r="F53" t="n">
         <v>0.9367285148952518</v>
       </c>
       <c r="G53" t="n">
-        <v>0.0631213377475511</v>
+        <v>0.06312133774792426</v>
       </c>
     </row>
     <row r="54">
@@ -3449,13 +3449,13 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>0.0001983933471743743</v>
+        <v>0.0001983933471750059</v>
       </c>
       <c r="F54" t="n">
-        <v>0.06052770978187825</v>
+        <v>0.0605277097821535</v>
       </c>
       <c r="G54" t="n">
-        <v>0.9392738968710223</v>
+        <v>0.9392738968705951</v>
       </c>
     </row>
     <row r="55">
@@ -3475,10 +3475,10 @@
         <v>0.0002786985484232656</v>
       </c>
       <c r="F55" t="n">
-        <v>0.9381450981340013</v>
+        <v>0.9381450981335746</v>
       </c>
       <c r="G55" t="n">
-        <v>0.06157620331764528</v>
+        <v>0.0615762033179533</v>
       </c>
     </row>
     <row r="56">
@@ -3495,13 +3495,13 @@
         <v>2</v>
       </c>
       <c r="E56" t="n">
-        <v>0.0006007979751581359</v>
+        <v>0.000600797975159502</v>
       </c>
       <c r="F56" t="n">
-        <v>0.0586167952317699</v>
+        <v>0.05861679523206312</v>
       </c>
       <c r="G56" t="n">
-        <v>0.9407824067930483</v>
+        <v>0.9407824067926205</v>
       </c>
     </row>
     <row r="57">
@@ -3521,10 +3521,10 @@
         <v>0.00348732512812244</v>
       </c>
       <c r="F57" t="n">
-        <v>0.9370573588095568</v>
+        <v>0.9370573588091307</v>
       </c>
       <c r="G57" t="n">
-        <v>0.05945531606233213</v>
+        <v>0.05945531606265658</v>
       </c>
     </row>
     <row r="58">
@@ -3541,10 +3541,10 @@
         <v>2</v>
       </c>
       <c r="E58" t="n">
-        <v>0.01165507459910315</v>
+        <v>0.01165507459914025</v>
       </c>
       <c r="F58" t="n">
-        <v>0.04816550319074365</v>
+        <v>0.04816550319102839</v>
       </c>
       <c r="G58" t="n">
         <v>0.9401794222099292</v>
@@ -3564,13 +3564,13 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>0.003619166652272222</v>
+        <v>0.003619166652280451</v>
       </c>
       <c r="F59" t="n">
         <v>0.9477919478178233</v>
       </c>
       <c r="G59" t="n">
-        <v>0.04858888552969468</v>
+        <v>0.04858888552995983</v>
       </c>
     </row>
     <row r="60">
@@ -3587,13 +3587,13 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>0.003600267258599384</v>
+        <v>0.003600267258609207</v>
       </c>
       <c r="F60" t="n">
-        <v>0.04551565906710796</v>
+        <v>0.04551565906733564</v>
       </c>
       <c r="G60" t="n">
-        <v>0.9508840736742955</v>
+        <v>0.9508840736738631</v>
       </c>
     </row>
     <row r="61">
@@ -3610,13 +3610,13 @@
         <v>1</v>
       </c>
       <c r="E61" t="n">
-        <v>0.001170465385582575</v>
+        <v>0.001170465385584704</v>
       </c>
       <c r="F61" t="n">
         <v>0.9527277856433631</v>
       </c>
       <c r="G61" t="n">
-        <v>0.04610174897097309</v>
+        <v>0.04610174897122467</v>
       </c>
     </row>
     <row r="62">
@@ -3633,10 +3633,10 @@
         <v>2</v>
       </c>
       <c r="E62" t="n">
-        <v>0.001690525025318658</v>
+        <v>0.001690525025321733</v>
       </c>
       <c r="F62" t="n">
-        <v>0.04220387276880194</v>
+        <v>0.04220387276899386</v>
       </c>
       <c r="G62" t="n">
         <v>0.9561056022057041</v>
@@ -3662,7 +3662,7 @@
         <v>0.9513758023585734</v>
       </c>
       <c r="G63" t="n">
-        <v>0.04279975088965093</v>
+        <v>0.04279975088984556</v>
       </c>
     </row>
     <row r="64">
@@ -3679,10 +3679,10 @@
         <v>2</v>
       </c>
       <c r="E64" t="n">
-        <v>0.00646212743764204</v>
+        <v>0.006462127437644979</v>
       </c>
       <c r="F64" t="n">
-        <v>0.04065933362787742</v>
+        <v>0.04065933362802533</v>
       </c>
       <c r="G64" t="n">
         <v>0.9528785389343185</v>
@@ -3702,13 +3702,13 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>0.04089515106594079</v>
+        <v>0.0408951510659222</v>
       </c>
       <c r="F65" t="n">
-        <v>0.9171891652355377</v>
+        <v>0.9171891652351207</v>
       </c>
       <c r="G65" t="n">
-        <v>0.0419156836986065</v>
+        <v>0.04191568369875899</v>
       </c>
     </row>
     <row r="66">
@@ -3725,10 +3725,10 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>0.04375445315254167</v>
+        <v>0.04375445315252177</v>
       </c>
       <c r="F66" t="n">
-        <v>0.03822175382624966</v>
+        <v>0.03822175382635395</v>
       </c>
       <c r="G66" t="n">
         <v>0.9180237930212468</v>
@@ -3748,13 +3748,13 @@
         <v>1</v>
       </c>
       <c r="E67" t="n">
-        <v>0.09392681501770668</v>
+        <v>0.09392681501766398</v>
       </c>
       <c r="F67" t="n">
         <v>0.8666534960434075</v>
       </c>
       <c r="G67" t="n">
-        <v>0.03941968893876294</v>
+        <v>0.0394196889388705</v>
       </c>
     </row>
     <row r="68">
@@ -3774,10 +3774,10 @@
         <v>0.1310268230508759</v>
       </c>
       <c r="F68" t="n">
-        <v>0.001042729582851507</v>
+        <v>0.001042729582856249</v>
       </c>
       <c r="G68" t="n">
-        <v>0.8679304473664414</v>
+        <v>0.8679304473660467</v>
       </c>
     </row>
     <row r="69">
@@ -3797,10 +3797,10 @@
         <v>0.9951051835215518</v>
       </c>
       <c r="F69" t="n">
-        <v>0.003917466640438297</v>
+        <v>0.003917466640434734</v>
       </c>
       <c r="G69" t="n">
-        <v>0.0009773498380528584</v>
+        <v>0.0009773498380564139</v>
       </c>
     </row>
     <row r="70">
@@ -3817,13 +3817,13 @@
         <v>1</v>
       </c>
       <c r="E70" t="n">
-        <v>0.2991590362012733</v>
+        <v>0.2991590362011372</v>
       </c>
       <c r="F70" t="n">
         <v>0.6968970455677097</v>
       </c>
       <c r="G70" t="n">
-        <v>0.003943918231196886</v>
+        <v>0.003943918231193299</v>
       </c>
     </row>
     <row r="71">
@@ -3840,10 +3840,10 @@
         <v>2</v>
       </c>
       <c r="E71" t="n">
-        <v>0.1496003409622269</v>
+        <v>0.1496003409621589</v>
       </c>
       <c r="F71" t="n">
-        <v>0.1532061392144145</v>
+        <v>0.1532061392144842</v>
       </c>
       <c r="G71" t="n">
         <v>0.6971935198234127</v>
@@ -3869,7 +3869,7 @@
         <v>0.826862892726868</v>
       </c>
       <c r="G72" t="n">
-        <v>0.154193124654017</v>
+        <v>0.1541931246540871</v>
       </c>
     </row>
     <row r="73">
@@ -3886,10 +3886,10 @@
         <v>2</v>
       </c>
       <c r="E73" t="n">
-        <v>0.008310333684763914</v>
+        <v>0.008310333684756355</v>
       </c>
       <c r="F73" t="n">
-        <v>0.1604198654226707</v>
+        <v>0.1604198654227437</v>
       </c>
       <c r="G73" t="n">
         <v>0.8312698008927202</v>
@@ -3909,13 +3909,13 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>0.002997315680248874</v>
+        <v>0.002997315680247511</v>
       </c>
       <c r="F74" t="n">
         <v>0.8351713972746519</v>
       </c>
       <c r="G74" t="n">
-        <v>0.1618312870449734</v>
+        <v>0.161831287045047</v>
       </c>
     </row>
     <row r="75">
@@ -3932,10 +3932,10 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>0.00713970430978074</v>
+        <v>0.007139704309783988</v>
       </c>
       <c r="F75" t="n">
-        <v>0.1529510584264751</v>
+        <v>0.1529510584266142</v>
       </c>
       <c r="G75" t="n">
         <v>0.8399092372635673</v>
@@ -3955,7 +3955,7 @@
         <v>1</v>
       </c>
       <c r="E76" t="n">
-        <v>0.01914281077054957</v>
+        <v>0.01914281077056698</v>
       </c>
       <c r="F76" t="n">
         <v>0.8266361697625412</v>
@@ -4001,13 +4001,13 @@
         <v>1</v>
       </c>
       <c r="E78" t="n">
-        <v>0.001007299907769403</v>
+        <v>0.001007299907769861</v>
       </c>
       <c r="F78" t="n">
-        <v>0.8275098727715767</v>
+        <v>0.8275098727712004</v>
       </c>
       <c r="G78" t="n">
-        <v>0.171482827320832</v>
+        <v>0.17148282732091</v>
       </c>
     </row>
     <row r="79">
@@ -4024,10 +4024,10 @@
         <v>2</v>
       </c>
       <c r="E79" t="n">
-        <v>0.0006026889056106384</v>
+        <v>0.0006026889056109125</v>
       </c>
       <c r="F79" t="n">
-        <v>0.1701108057570131</v>
+        <v>0.1701108057570904</v>
       </c>
       <c r="G79" t="n">
         <v>0.8292865053372147</v>
@@ -4047,13 +4047,13 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>0.0004169501585921441</v>
+        <v>0.0004169501585927129</v>
       </c>
       <c r="F80" t="n">
-        <v>0.8260985743361882</v>
+        <v>0.8260985743358125</v>
       </c>
       <c r="G80" t="n">
-        <v>0.1734844755053955</v>
+        <v>0.1734844755055533</v>
       </c>
     </row>
     <row r="81">
@@ -4073,10 +4073,10 @@
         <v>0.0002347725584445635</v>
       </c>
       <c r="F81" t="n">
-        <v>0.1716268696111447</v>
+        <v>0.1716268696113008</v>
       </c>
       <c r="G81" t="n">
-        <v>0.8281383578304288</v>
+        <v>0.8281383578300522</v>
       </c>
     </row>
     <row r="82">
@@ -4093,13 +4093,13 @@
         <v>1</v>
       </c>
       <c r="E82" t="n">
-        <v>0.0003812182733669605</v>
+        <v>0.0003812182733674806</v>
       </c>
       <c r="F82" t="n">
-        <v>0.8248570301263948</v>
+        <v>0.8248570301260196</v>
       </c>
       <c r="G82" t="n">
-        <v>0.1747617516003731</v>
+        <v>0.174761751600532</v>
       </c>
     </row>
     <row r="83">
@@ -4119,10 +4119,10 @@
         <v>0.0004471378700743681</v>
       </c>
       <c r="F83" t="n">
-        <v>0.1728648446831239</v>
+        <v>0.1728648446832811</v>
       </c>
       <c r="G83" t="n">
-        <v>0.8266880174468099</v>
+        <v>0.8266880174464339</v>
       </c>
     </row>
     <row r="84">
@@ -4139,13 +4139,13 @@
         <v>1</v>
       </c>
       <c r="E84" t="n">
-        <v>0.002011840335086447</v>
+        <v>0.002011840335090107</v>
       </c>
       <c r="F84" t="n">
         <v>0.8213272852732753</v>
       </c>
       <c r="G84" t="n">
-        <v>0.1766608743915614</v>
+        <v>0.1766608743918024</v>
       </c>
     </row>
     <row r="85">
@@ -4162,13 +4162,13 @@
         <v>2</v>
       </c>
       <c r="E85" t="n">
-        <v>0.0008901830739694768</v>
+        <v>0.0008901830739706912</v>
       </c>
       <c r="F85" t="n">
-        <v>0.1762774295024258</v>
+        <v>0.1762774295025861</v>
       </c>
       <c r="G85" t="n">
-        <v>0.8228323874238305</v>
+        <v>0.8228323874234563</v>
       </c>
     </row>
     <row r="86">
@@ -4185,13 +4185,13 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>0.0002850532414091321</v>
+        <v>0.0002850532414093913</v>
       </c>
       <c r="F86" t="n">
-        <v>0.8197099586766415</v>
+        <v>0.8197099586762688</v>
       </c>
       <c r="G86" t="n">
-        <v>0.1800049880820775</v>
+        <v>0.1800049880821593</v>
       </c>
     </row>
     <row r="87">
@@ -4208,10 +4208,10 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>0.0001594180792011182</v>
+        <v>0.0001594180792011907</v>
       </c>
       <c r="F87" t="n">
-        <v>0.1782512564132369</v>
+        <v>0.1782512564133991</v>
       </c>
       <c r="G87" t="n">
         <v>0.8215893255075868</v>
@@ -4231,13 +4231,13 @@
         <v>1</v>
       </c>
       <c r="E88" t="n">
-        <v>0.0002447623813276098</v>
+        <v>0.0002447623813278324</v>
       </c>
       <c r="F88" t="n">
-        <v>0.817929812680384</v>
+        <v>0.8179298126800121</v>
       </c>
       <c r="G88" t="n">
-        <v>0.1818254249384138</v>
+        <v>0.1818254249384965</v>
       </c>
     </row>
     <row r="89">
@@ -4254,13 +4254,13 @@
         <v>2</v>
       </c>
       <c r="E89" t="n">
-        <v>0.0001654771582051127</v>
+        <v>0.000165477158205188</v>
       </c>
       <c r="F89" t="n">
-        <v>0.1799127341300699</v>
+        <v>0.1799127341301517</v>
       </c>
       <c r="G89" t="n">
-        <v>0.8199217887117951</v>
+        <v>0.8199217887114223</v>
       </c>
     </row>
     <row r="90">
@@ -4277,13 +4277,13 @@
         <v>1</v>
       </c>
       <c r="E90" t="n">
-        <v>0.0003586495118656683</v>
+        <v>0.0003586495118659945</v>
       </c>
       <c r="F90" t="n">
-        <v>0.8161891558737273</v>
+        <v>0.8161891558733562</v>
       </c>
       <c r="G90" t="n">
-        <v>0.1834521946145368</v>
+        <v>0.1834521946147036</v>
       </c>
     </row>
     <row r="91">
@@ -4300,13 +4300,13 @@
         <v>2</v>
       </c>
       <c r="E91" t="n">
-        <v>0.0002768770758379388</v>
+        <v>0.0002768770758380646</v>
       </c>
       <c r="F91" t="n">
-        <v>0.1814984734593598</v>
+        <v>0.1814984734596074</v>
       </c>
       <c r="G91" t="n">
-        <v>0.8182246494648542</v>
+        <v>0.8182246494644821</v>
       </c>
     </row>
     <row r="92">
@@ -4323,13 +4323,13 @@
         <v>1</v>
       </c>
       <c r="E92" t="n">
-        <v>0.000272875959586546</v>
+        <v>0.0002728759595870424</v>
       </c>
       <c r="F92" t="n">
-        <v>0.8147987572414781</v>
+        <v>0.8147987572411075</v>
       </c>
       <c r="G92" t="n">
-        <v>0.1849283667988905</v>
+        <v>0.1849283667992269</v>
       </c>
     </row>
     <row r="93">
@@ -4346,10 +4346,10 @@
         <v>2</v>
       </c>
       <c r="E93" t="n">
-        <v>0.000199210067166816</v>
+        <v>0.0001992100671670878</v>
       </c>
       <c r="F93" t="n">
-        <v>0.1828062634242351</v>
+        <v>0.1828062634245676</v>
       </c>
       <c r="G93" t="n">
         <v>0.8169945265083712</v>
@@ -4369,13 +4369,13 @@
         <v>1</v>
       </c>
       <c r="E94" t="n">
-        <v>0.0004139293583543777</v>
+        <v>0.0004139293583549425</v>
       </c>
       <c r="F94" t="n">
-        <v>0.8133450790543473</v>
+        <v>0.8133450790539773</v>
       </c>
       <c r="G94" t="n">
-        <v>0.1862409915874617</v>
+        <v>0.186240991587631</v>
       </c>
     </row>
     <row r="95">
@@ -4392,13 +4392,13 @@
         <v>2</v>
       </c>
       <c r="E95" t="n">
-        <v>0.000421044089021739</v>
+        <v>0.0004210440890219305</v>
       </c>
       <c r="F95" t="n">
-        <v>0.1840967788157414</v>
+        <v>0.1840967788160762</v>
       </c>
       <c r="G95" t="n">
-        <v>0.815482177095228</v>
+        <v>0.8154821770948572</v>
       </c>
     </row>
     <row r="96">
@@ -4415,13 +4415,13 @@
         <v>1</v>
       </c>
       <c r="E96" t="n">
-        <v>0.0003432395291074241</v>
+        <v>0.0003432395291082046</v>
       </c>
       <c r="F96" t="n">
-        <v>0.8122502783649331</v>
+        <v>0.8122502783645638</v>
       </c>
       <c r="G96" t="n">
-        <v>0.1874064821060351</v>
+        <v>0.187406482106376</v>
       </c>
     </row>
     <row r="97">
@@ -4438,10 +4438,10 @@
         <v>2</v>
       </c>
       <c r="E97" t="n">
-        <v>0.0002789836369383991</v>
+        <v>0.0002789836369387797</v>
       </c>
       <c r="F97" t="n">
-        <v>0.1853712688740616</v>
+        <v>0.1853712688743145</v>
       </c>
       <c r="G97" t="n">
         <v>0.8143497474889648</v>
@@ -4461,13 +4461,13 @@
         <v>1</v>
       </c>
       <c r="E98" t="n">
-        <v>0.001061686094079561</v>
+        <v>0.001061686094081009</v>
       </c>
       <c r="F98" t="n">
-        <v>0.8101166664254039</v>
+        <v>0.8101166664250355</v>
       </c>
       <c r="G98" t="n">
-        <v>0.1888216474804073</v>
+        <v>0.1888216474807507</v>
       </c>
     </row>
     <row r="99">
@@ -4484,10 +4484,10 @@
         <v>2</v>
       </c>
       <c r="E99" t="n">
-        <v>0.001200409833835491</v>
+        <v>0.001200409833837129</v>
       </c>
       <c r="F99" t="n">
-        <v>0.1872283252293973</v>
+        <v>0.1872283252297379</v>
       </c>
       <c r="G99" t="n">
         <v>0.8115712649366259</v>
@@ -4507,13 +4507,13 @@
         <v>1</v>
       </c>
       <c r="E100" t="n">
-        <v>0.0004537628290806293</v>
+        <v>0.0004537628290814547</v>
       </c>
       <c r="F100" t="n">
         <v>0.8082861271195555</v>
       </c>
       <c r="G100" t="n">
-        <v>0.1912601100511758</v>
+        <v>0.1912601100515237</v>
       </c>
     </row>
     <row r="101">
@@ -4530,13 +4530,13 @@
         <v>2</v>
       </c>
       <c r="E101" t="n">
-        <v>0.0003615860833313053</v>
+        <v>0.0003615860833314698</v>
       </c>
       <c r="F101" t="n">
-        <v>0.1894355935035865</v>
+        <v>0.1894355935038449</v>
       </c>
       <c r="G101" t="n">
-        <v>0.8102028204132159</v>
+        <v>0.8102028204128474</v>
       </c>
     </row>
     <row r="102">
@@ -4553,13 +4553,13 @@
         <v>1</v>
       </c>
       <c r="E102" t="n">
-        <v>0.001268127107858297</v>
+        <v>0.001268127107860027</v>
       </c>
       <c r="F102" t="n">
         <v>0.8053742517777415</v>
       </c>
       <c r="G102" t="n">
-        <v>0.1933576211142605</v>
+        <v>0.1933576211146122</v>
       </c>
     </row>
     <row r="103">
@@ -4576,13 +4576,13 @@
         <v>2</v>
       </c>
       <c r="E103" t="n">
-        <v>0.00201703976267475</v>
+        <v>0.002017039762675667</v>
       </c>
       <c r="F103" t="n">
-        <v>0.1906764441345562</v>
+        <v>0.1906764441348163</v>
       </c>
       <c r="G103" t="n">
-        <v>0.8073065161029715</v>
+        <v>0.8073065161026044</v>
       </c>
     </row>
     <row r="104">
@@ -4599,13 +4599,13 @@
         <v>1</v>
       </c>
       <c r="E104" t="n">
-        <v>0.002613395605887431</v>
+        <v>0.002613395605890997</v>
       </c>
       <c r="F104" t="n">
-        <v>0.8041192116940979</v>
+        <v>0.8041192116937322</v>
       </c>
       <c r="G104" t="n">
-        <v>0.193267392700085</v>
+        <v>0.1932673927004366</v>
       </c>
     </row>
     <row r="105">
@@ -4625,10 +4625,10 @@
         <v>0.0008688632686340741</v>
       </c>
       <c r="F105" t="n">
-        <v>0.1927428760895617</v>
+        <v>0.1927428760898247</v>
       </c>
       <c r="G105" t="n">
-        <v>0.8063882606419522</v>
+        <v>0.8063882606415855</v>
       </c>
     </row>
     <row r="106">
@@ -4645,13 +4645,13 @@
         <v>1</v>
       </c>
       <c r="E106" t="n">
-        <v>0.0004046321565700658</v>
+        <v>0.0004046321565709858</v>
       </c>
       <c r="F106" t="n">
-        <v>0.8034433840323363</v>
+        <v>0.8034433840319709</v>
       </c>
       <c r="G106" t="n">
-        <v>0.196151983811306</v>
+        <v>0.1961519838116628</v>
       </c>
     </row>
     <row r="107">
@@ -4668,13 +4668,13 @@
         <v>2</v>
       </c>
       <c r="E107" t="n">
-        <v>0.0004714072262802157</v>
+        <v>0.0004714072262806444</v>
       </c>
       <c r="F107" t="n">
-        <v>0.1940764837222249</v>
+        <v>0.194076483722578</v>
       </c>
       <c r="G107" t="n">
-        <v>0.8054521090516998</v>
+        <v>0.8054521090513336</v>
       </c>
     </row>
     <row r="108">
@@ -4691,13 +4691,13 @@
         <v>1</v>
       </c>
       <c r="E108" t="n">
-        <v>0.0007844292926009286</v>
+        <v>0.0007844292926023554</v>
       </c>
       <c r="F108" t="n">
         <v>0.8013968317922376</v>
       </c>
       <c r="G108" t="n">
-        <v>0.1978187389149913</v>
+        <v>0.1978187389152612</v>
       </c>
     </row>
     <row r="109">
@@ -4717,7 +4717,7 @@
         <v>0.0002506994834067123</v>
       </c>
       <c r="F109" t="n">
-        <v>0.1969093266747999</v>
+        <v>0.1969093266751581</v>
       </c>
       <c r="G109" t="n">
         <v>0.802839973841571</v>
@@ -4737,13 +4737,13 @@
         <v>1</v>
       </c>
       <c r="E110" t="n">
-        <v>0.0003415382292920281</v>
+        <v>0.0003415382292926493</v>
       </c>
       <c r="F110" t="n">
-        <v>0.7978512378342962</v>
+        <v>0.7978512378339334</v>
       </c>
       <c r="G110" t="n">
-        <v>0.2018072239363268</v>
+        <v>0.2018072239367856</v>
       </c>
     </row>
     <row r="111">
@@ -4763,10 +4763,10 @@
         <v>0.0001870555044156505</v>
       </c>
       <c r="F111" t="n">
-        <v>0.2004925680870476</v>
+        <v>0.2004925680873211</v>
       </c>
       <c r="G111" t="n">
-        <v>0.7993203764086633</v>
+        <v>0.7993203764082998</v>
       </c>
     </row>
     <row r="112">
@@ -4783,13 +4783,13 @@
         <v>1</v>
       </c>
       <c r="E112" t="n">
-        <v>0.000818797428727112</v>
+        <v>0.000818797428728229</v>
       </c>
       <c r="F112" t="n">
-        <v>0.7931928204315697</v>
+        <v>0.793192820431209</v>
       </c>
       <c r="G112" t="n">
-        <v>0.2059883821398804</v>
+        <v>0.2059883821402551</v>
       </c>
     </row>
     <row r="113">
@@ -4806,13 +4806,13 @@
         <v>2</v>
       </c>
       <c r="E113" t="n">
-        <v>0.0004303532451204868</v>
+        <v>0.0004303532451210739</v>
       </c>
       <c r="F113" t="n">
-        <v>0.2049849971825125</v>
+        <v>0.2049849971828854</v>
       </c>
       <c r="G113" t="n">
-        <v>0.7945846495725599</v>
+        <v>0.7945846495721987</v>
       </c>
     </row>
     <row r="114">
@@ -4829,13 +4829,13 @@
         <v>1</v>
       </c>
       <c r="E114" t="n">
-        <v>0.003697609390403243</v>
+        <v>0.003697609390406606</v>
       </c>
       <c r="F114" t="n">
-        <v>0.7857298784746177</v>
+        <v>0.7857298784742605</v>
       </c>
       <c r="G114" t="n">
-        <v>0.2105725121349913</v>
+        <v>0.2105725121352786</v>
       </c>
     </row>
     <row r="115">
@@ -4855,10 +4855,10 @@
         <v>0.001720986919279391</v>
       </c>
       <c r="F115" t="n">
-        <v>0.2114123722458418</v>
+        <v>0.2114123722461302</v>
       </c>
       <c r="G115" t="n">
-        <v>0.7868666408347247</v>
+        <v>0.7868666408343669</v>
       </c>
     </row>
     <row r="116">
@@ -4878,10 +4878,10 @@
         <v>0.009224337840285243</v>
       </c>
       <c r="F116" t="n">
-        <v>0.7720719691503684</v>
+        <v>0.7720719691500173</v>
       </c>
       <c r="G116" t="n">
-        <v>0.218703693009199</v>
+        <v>0.2187036930095969</v>
       </c>
     </row>
     <row r="117">
@@ -4898,13 +4898,13 @@
         <v>2</v>
       </c>
       <c r="E117" t="n">
-        <v>0.02225750754308067</v>
+        <v>0.02225750754310091</v>
       </c>
       <c r="F117" t="n">
-        <v>0.2045518762984542</v>
+        <v>0.2045518762989193</v>
       </c>
       <c r="G117" t="n">
-        <v>0.7731906161584935</v>
+        <v>0.7731906161581419</v>
       </c>
     </row>
     <row r="118">
@@ -4921,13 +4921,13 @@
         <v>1</v>
       </c>
       <c r="E118" t="n">
-        <v>0.002541666797686561</v>
+        <v>0.002541666797690028</v>
       </c>
       <c r="F118" t="n">
-        <v>0.7898781487961227</v>
+        <v>0.7898781487954044</v>
       </c>
       <c r="G118" t="n">
-        <v>0.2075801844062068</v>
+        <v>0.2075801844066787</v>
       </c>
     </row>
     <row r="119">
@@ -4944,13 +4944,13 @@
         <v>2</v>
       </c>
       <c r="E119" t="n">
-        <v>0.001211666482629092</v>
+        <v>0.001211666482630745</v>
       </c>
       <c r="F119" t="n">
-        <v>0.2062843125804831</v>
+        <v>0.206284312581046</v>
       </c>
       <c r="G119" t="n">
-        <v>0.7925040209367986</v>
+        <v>0.7925040209364382</v>
       </c>
     </row>
     <row r="120">
@@ -4967,13 +4967,13 @@
         <v>1</v>
       </c>
       <c r="E120" t="n">
-        <v>0.002480939620213196</v>
+        <v>0.002480939620215453</v>
       </c>
       <c r="F120" t="n">
-        <v>0.7886932508818066</v>
+        <v>0.788693250881448</v>
       </c>
       <c r="G120" t="n">
-        <v>0.2088258094981951</v>
+        <v>0.20882580949848</v>
       </c>
     </row>
     <row r="121">
@@ -4990,13 +4990,13 @@
         <v>2</v>
       </c>
       <c r="E121" t="n">
-        <v>0.005196394498546535</v>
+        <v>0.005196394498555987</v>
       </c>
       <c r="F121" t="n">
-        <v>0.2031078180453555</v>
+        <v>0.2031078180456326</v>
       </c>
       <c r="G121" t="n">
-        <v>0.7916957874559887</v>
+        <v>0.7916957874556286</v>
       </c>
     </row>
     <row r="122">
@@ -5013,13 +5013,13 @@
         <v>1</v>
       </c>
       <c r="E122" t="n">
-        <v>0.001639174051789421</v>
+        <v>0.001639174051790912</v>
       </c>
       <c r="F122" t="n">
-        <v>0.794203654107818</v>
+        <v>0.7942036541074569</v>
       </c>
       <c r="G122" t="n">
-        <v>0.2041571718402623</v>
+        <v>0.2041571718406337</v>
       </c>
     </row>
     <row r="123">
@@ -5039,10 +5039,10 @@
         <v>0.0006643131340461572</v>
       </c>
       <c r="F123" t="n">
-        <v>0.2013413698587983</v>
+        <v>0.2013413698591645</v>
       </c>
       <c r="G123" t="n">
-        <v>0.7979943170069302</v>
+        <v>0.7979943170065674</v>
       </c>
     </row>
     <row r="124">
@@ -5059,13 +5059,13 @@
         <v>1</v>
       </c>
       <c r="E124" t="n">
-        <v>0.0004464917259805387</v>
+        <v>0.0004464917259809448</v>
       </c>
       <c r="F124" t="n">
-        <v>0.7962590152682865</v>
+        <v>0.7962590152679244</v>
       </c>
       <c r="G124" t="n">
-        <v>0.2032944930056571</v>
+        <v>0.2032944930061194</v>
       </c>
     </row>
     <row r="125">
@@ -5082,13 +5082,13 @@
         <v>2</v>
       </c>
       <c r="E125" t="n">
-        <v>0.001156029949914083</v>
+        <v>0.00115602994991566</v>
       </c>
       <c r="F125" t="n">
-        <v>0.1986360318401185</v>
+        <v>0.1986360318404798</v>
       </c>
       <c r="G125" t="n">
-        <v>0.800207938209995</v>
+        <v>0.8002079382096312</v>
       </c>
     </row>
     <row r="126">
@@ -5105,13 +5105,13 @@
         <v>1</v>
       </c>
       <c r="E126" t="n">
-        <v>0.000530764065519368</v>
+        <v>0.0005307640655200921</v>
       </c>
       <c r="F126" t="n">
-        <v>0.7992373592129723</v>
+        <v>0.799237359212609</v>
       </c>
       <c r="G126" t="n">
-        <v>0.2002318767213404</v>
+        <v>0.2002318767217046</v>
       </c>
     </row>
     <row r="127">
@@ -5128,13 +5128,13 @@
         <v>2</v>
       </c>
       <c r="E127" t="n">
-        <v>0.0003927391623227901</v>
+        <v>0.0003927391623231473</v>
       </c>
       <c r="F127" t="n">
-        <v>0.1969176102866624</v>
+        <v>0.196917610286931</v>
       </c>
       <c r="G127" t="n">
-        <v>0.802689650550913</v>
+        <v>0.802689650550548</v>
       </c>
     </row>
     <row r="128">
@@ -5151,13 +5151,13 @@
         <v>1</v>
       </c>
       <c r="E128" t="n">
-        <v>0.0002743121089689913</v>
+        <v>0.0002743121089692408</v>
       </c>
       <c r="F128" t="n">
         <v>0.8006240021063235</v>
       </c>
       <c r="G128" t="n">
-        <v>0.1991016857846432</v>
+        <v>0.1991016857849148</v>
       </c>
     </row>
     <row r="129">
@@ -5174,13 +5174,13 @@
         <v>2</v>
       </c>
       <c r="E129" t="n">
-        <v>0.0003337085901225878</v>
+        <v>0.0003337085901228913</v>
       </c>
       <c r="F129" t="n">
-        <v>0.1953933504309079</v>
+        <v>0.1953933504310856</v>
       </c>
       <c r="G129" t="n">
-        <v>0.8042729409790182</v>
+        <v>0.8042729409786525</v>
       </c>
     </row>
     <row r="130">
@@ -5197,13 +5197,13 @@
         <v>1</v>
       </c>
       <c r="E130" t="n">
-        <v>0.001154126375683306</v>
+        <v>0.001154126375684356</v>
       </c>
       <c r="F130" t="n">
-        <v>0.8013495713898509</v>
+        <v>0.8013495713894865</v>
       </c>
       <c r="G130" t="n">
-        <v>0.197496302234615</v>
+        <v>0.1974963022347946</v>
       </c>
     </row>
     <row r="131">
@@ -5220,13 +5220,13 @@
         <v>2</v>
       </c>
       <c r="E131" t="n">
-        <v>0.0005785527068162339</v>
+        <v>0.000578552706816497</v>
       </c>
       <c r="F131" t="n">
-        <v>0.1950830121603229</v>
+        <v>0.1950830121605003</v>
       </c>
       <c r="G131" t="n">
-        <v>0.8043384351329782</v>
+        <v>0.8043384351326125</v>
       </c>
     </row>
     <row r="132">
@@ -5243,13 +5243,13 @@
         <v>1</v>
       </c>
       <c r="E132" t="n">
-        <v>0.0006515682548540072</v>
+        <v>0.0006515682548543035</v>
       </c>
       <c r="F132" t="n">
-        <v>0.8017360144647218</v>
+        <v>0.8017360144643572</v>
       </c>
       <c r="G132" t="n">
-        <v>0.1976124172805686</v>
+        <v>0.1976124172807483</v>
       </c>
     </row>
     <row r="133">
@@ -5266,13 +5266,13 @@
         <v>2</v>
       </c>
       <c r="E133" t="n">
-        <v>0.0005619054004180179</v>
+        <v>0.0005619054004185289</v>
       </c>
       <c r="F133" t="n">
-        <v>0.1952832863161025</v>
+        <v>0.1952832863162801</v>
       </c>
       <c r="G133" t="n">
-        <v>0.8041548082836012</v>
+        <v>0.8041548082832355</v>
       </c>
     </row>
     <row r="134">
@@ -5289,13 +5289,13 @@
         <v>1</v>
       </c>
       <c r="E134" t="n">
-        <v>0.0004183585649295972</v>
+        <v>0.0004183585649299777</v>
       </c>
       <c r="F134" t="n">
-        <v>0.8012966509394711</v>
+        <v>0.8012966509391067</v>
       </c>
       <c r="G134" t="n">
-        <v>0.1982849904957586</v>
+        <v>0.1982849904960291</v>
       </c>
     </row>
     <row r="135">
@@ -5312,13 +5312,13 @@
         <v>2</v>
       </c>
       <c r="E135" t="n">
-        <v>0.0002486614965437571</v>
+        <v>0.0002486614965440964</v>
       </c>
       <c r="F135" t="n">
-        <v>0.196139711776243</v>
+        <v>0.1961397117763322</v>
       </c>
       <c r="G135" t="n">
-        <v>0.803611626727405</v>
+        <v>0.8036116267270397</v>
       </c>
     </row>
     <row r="136">
@@ -5338,10 +5338,10 @@
         <v>0.0002600357144427368</v>
       </c>
       <c r="F136" t="n">
-        <v>0.800162514694625</v>
+        <v>0.800162514694261</v>
       </c>
       <c r="G136" t="n">
-        <v>0.1995774495910873</v>
+        <v>0.199577449591178</v>
       </c>
     </row>
     <row r="137">
@@ -5358,10 +5358,10 @@
         <v>2</v>
       </c>
       <c r="E137" t="n">
-        <v>0.0003027834577070355</v>
+        <v>0.0003027834577074485</v>
       </c>
       <c r="F137" t="n">
-        <v>0.1972000178269472</v>
+        <v>0.1972000178272163</v>
       </c>
       <c r="G137" t="n">
         <v>0.8024971987152939</v>
@@ -5381,13 +5381,13 @@
         <v>1</v>
       </c>
       <c r="E138" t="n">
-        <v>0.002412267156618045</v>
+        <v>0.002412267156616948</v>
       </c>
       <c r="F138" t="n">
-        <v>0.7972447932520312</v>
+        <v>0.7972447932516686</v>
       </c>
       <c r="G138" t="n">
-        <v>0.2003429395913368</v>
+        <v>0.200342939591519</v>
       </c>
     </row>
     <row r="139">
@@ -5407,7 +5407,7 @@
         <v>0.005964111044715388</v>
       </c>
       <c r="F139" t="n">
-        <v>0.1943169220517639</v>
+        <v>0.1943169220519406</v>
       </c>
       <c r="G139" t="n">
         <v>0.7997189669033525</v>
@@ -5427,13 +5427,13 @@
         <v>1</v>
       </c>
       <c r="E140" t="n">
-        <v>0.03533867767359823</v>
+        <v>0.03533867767355002</v>
       </c>
       <c r="F140" t="n">
-        <v>0.7673678637885332</v>
+        <v>0.7673678637881842</v>
       </c>
       <c r="G140" t="n">
-        <v>0.1972934585380629</v>
+        <v>0.1972934585381526</v>
       </c>
     </row>
     <row r="141">
@@ -5453,10 +5453,10 @@
         <v>0.1210672800615065</v>
       </c>
       <c r="F141" t="n">
-        <v>0.1095724828512871</v>
+        <v>0.1095724828513369</v>
       </c>
       <c r="G141" t="n">
-        <v>0.7693602370874171</v>
+        <v>0.7693602370870671</v>
       </c>
     </row>
     <row r="142">
@@ -5479,7 +5479,7 @@
         <v>0.5712198394274453</v>
       </c>
       <c r="G142" t="n">
-        <v>0.111056926979631</v>
+        <v>0.111056926979732</v>
       </c>
     </row>
     <row r="143">
@@ -5499,10 +5499,10 @@
         <v>0.427176893729236</v>
       </c>
       <c r="F143" t="n">
-        <v>0.0001173763554087778</v>
+        <v>0.0001173763554103257</v>
       </c>
       <c r="G143" t="n">
-        <v>0.5727057299155495</v>
+        <v>0.572705729915289</v>
       </c>
     </row>
     <row r="144">
@@ -5525,7 +5525,7 @@
         <v>7.269701745512763e-05</v>
       </c>
       <c r="G144" t="n">
-        <v>1.792398131914055e-06</v>
+        <v>1.792398131919761e-06</v>
       </c>
     </row>
     <row r="145">
@@ -5545,7 +5545,7 @@
         <v>0.9803086450582578</v>
       </c>
       <c r="F145" t="n">
-        <v>0.01960938542407172</v>
+        <v>0.01960938542410739</v>
       </c>
       <c r="G145" t="n">
         <v>8.196951760071434e-05</v>
@@ -5565,13 +5565,13 @@
         <v>1</v>
       </c>
       <c r="E146" t="n">
-        <v>0.08637523315248734</v>
+        <v>0.08637523315252661</v>
       </c>
       <c r="F146" t="n">
-        <v>0.8939598455497005</v>
+        <v>0.893959845549294</v>
       </c>
       <c r="G146" t="n">
-        <v>0.01966492129800615</v>
+        <v>0.01966492129802404</v>
       </c>
     </row>
     <row r="147">
@@ -5588,10 +5588,10 @@
         <v>2</v>
       </c>
       <c r="E147" t="n">
-        <v>0.04093893447333682</v>
+        <v>0.04093893447329958</v>
       </c>
       <c r="F147" t="n">
-        <v>0.06445903377879501</v>
+        <v>0.06445903377888296</v>
       </c>
       <c r="G147" t="n">
         <v>0.8946020317480172</v>
@@ -5611,13 +5611,13 @@
         <v>1</v>
       </c>
       <c r="E148" t="n">
-        <v>0.00381265557616589</v>
+        <v>0.003812655576162423</v>
       </c>
       <c r="F148" t="n">
         <v>0.93057747708372</v>
       </c>
       <c r="G148" t="n">
-        <v>0.06560986733997627</v>
+        <v>0.06560986734006578</v>
       </c>
     </row>
     <row r="149">
@@ -5634,13 +5634,13 @@
         <v>2</v>
       </c>
       <c r="E149" t="n">
-        <v>0.002951780472890559</v>
+        <v>0.002951780472887874</v>
       </c>
       <c r="F149" t="n">
-        <v>0.06394137205061544</v>
+        <v>0.06394137205064451</v>
       </c>
       <c r="G149" t="n">
-        <v>0.933106847476693</v>
+        <v>0.9331068474762687</v>
       </c>
     </row>
     <row r="150">
@@ -5660,10 +5660,10 @@
         <v>0.001706696641899429</v>
       </c>
       <c r="F150" t="n">
-        <v>0.9334348313041532</v>
+        <v>0.9334348313037286</v>
       </c>
       <c r="G150" t="n">
-        <v>0.06485847205417111</v>
+        <v>0.06485847205423009</v>
       </c>
     </row>
     <row r="151">
@@ -5680,10 +5680,10 @@
         <v>2</v>
       </c>
       <c r="E151" t="n">
-        <v>0.003427199356514408</v>
+        <v>0.003427199356519083</v>
       </c>
       <c r="F151" t="n">
-        <v>0.05989167190092799</v>
+        <v>0.05989167190098246</v>
       </c>
       <c r="G151" t="n">
         <v>0.936681128742435</v>
@@ -5703,13 +5703,13 @@
         <v>1</v>
       </c>
       <c r="E152" t="n">
-        <v>0.01432734188109943</v>
+        <v>0.01432734188112549</v>
       </c>
       <c r="F152" t="n">
         <v>0.9251288338001258</v>
       </c>
       <c r="G152" t="n">
-        <v>0.06054382431863485</v>
+        <v>0.06054382431874498</v>
       </c>
     </row>
     <row r="153">
@@ -5726,10 +5726,10 @@
         <v>2</v>
       </c>
       <c r="E153" t="n">
-        <v>0.006727154743954108</v>
+        <v>0.006727154743960227</v>
       </c>
       <c r="F153" t="n">
-        <v>0.06670752949946525</v>
+        <v>0.0667075294995866</v>
       </c>
       <c r="G153" t="n">
         <v>0.9265653157564858</v>
@@ -5755,7 +5755,7 @@
         <v>0.9267313282493866</v>
       </c>
       <c r="G154" t="n">
-        <v>0.06838334475374797</v>
+        <v>0.06838334475384127</v>
       </c>
     </row>
     <row r="155">
@@ -5772,13 +5772,13 @@
         <v>2</v>
       </c>
       <c r="E155" t="n">
-        <v>0.005522289149628959</v>
+        <v>0.005522289149626448</v>
       </c>
       <c r="F155" t="n">
-        <v>0.06595197659765024</v>
+        <v>0.06595197659771022</v>
       </c>
       <c r="G155" t="n">
-        <v>0.9285257342529024</v>
+        <v>0.9285257342524802</v>
       </c>
     </row>
     <row r="156">
@@ -5795,13 +5795,13 @@
         <v>1</v>
       </c>
       <c r="E156" t="n">
-        <v>0.0007961574691179909</v>
+        <v>0.000796157469118715</v>
       </c>
       <c r="F156" t="n">
         <v>0.9323704798362084</v>
       </c>
       <c r="G156" t="n">
-        <v>0.066833362694624</v>
+        <v>0.06683336269477597</v>
       </c>
     </row>
     <row r="157">
@@ -5818,13 +5818,13 @@
         <v>2</v>
       </c>
       <c r="E157" t="n">
-        <v>0.0006806829045326453</v>
+        <v>0.0006806829045332644</v>
       </c>
       <c r="F157" t="n">
-        <v>0.06380371210775186</v>
+        <v>0.0638037121078099</v>
       </c>
       <c r="G157" t="n">
-        <v>0.9355156049879076</v>
+        <v>0.9355156049874823</v>
       </c>
     </row>
     <row r="158">
@@ -5841,13 +5841,13 @@
         <v>1</v>
       </c>
       <c r="E158" t="n">
-        <v>0.0001106221037291007</v>
+        <v>0.000110622103729151</v>
       </c>
       <c r="F158" t="n">
-        <v>0.9352504216245937</v>
+        <v>0.9352504216241684</v>
       </c>
       <c r="G158" t="n">
-        <v>0.06463895627187398</v>
+        <v>0.06463895627193277</v>
       </c>
     </row>
     <row r="159">
@@ -5864,10 +5864,10 @@
         <v>2</v>
       </c>
       <c r="E159" t="n">
-        <v>0.000244880526996732</v>
+        <v>0.000244880526997066</v>
       </c>
       <c r="F159" t="n">
-        <v>0.06129067820550328</v>
+        <v>0.06129067820555903</v>
       </c>
       <c r="G159" t="n">
         <v>0.9384644412674483</v>
@@ -5887,13 +5887,13 @@
         <v>1</v>
       </c>
       <c r="E160" t="n">
-        <v>0.0005538856434864087</v>
+        <v>0.0005538856434866606</v>
       </c>
       <c r="F160" t="n">
         <v>0.9373294863315671</v>
       </c>
       <c r="G160" t="n">
-        <v>0.0621166280248625</v>
+        <v>0.06211662802497549</v>
       </c>
     </row>
     <row r="161">
@@ -5910,13 +5910,13 @@
         <v>2</v>
       </c>
       <c r="E161" t="n">
-        <v>0.0005231827991094222</v>
+        <v>0.0005231827991098979</v>
       </c>
       <c r="F161" t="n">
-        <v>0.05905424272263264</v>
+        <v>0.05905424272271321</v>
       </c>
       <c r="G161" t="n">
-        <v>0.9404225744784035</v>
+        <v>0.9404225744779758</v>
       </c>
     </row>
     <row r="162">
@@ -5933,13 +5933,13 @@
         <v>1</v>
       </c>
       <c r="E162" t="n">
-        <v>0.0001476944621912937</v>
+        <v>0.0001476944621913609</v>
       </c>
       <c r="F162" t="n">
-        <v>0.9399259045435572</v>
+        <v>0.9399259045431297</v>
       </c>
       <c r="G162" t="n">
-        <v>0.05992640099440067</v>
+        <v>0.05992640099448242</v>
       </c>
     </row>
     <row r="163">
@@ -5956,13 +5956,13 @@
         <v>2</v>
       </c>
       <c r="E163" t="n">
-        <v>0.0002543880928193515</v>
+        <v>0.0002543880928196986</v>
       </c>
       <c r="F163" t="n">
-        <v>0.05708778609832862</v>
+        <v>0.0570877860984065</v>
       </c>
       <c r="G163" t="n">
-        <v>0.9426578258089806</v>
+        <v>0.942657825808552</v>
       </c>
     </row>
     <row r="164">
@@ -5979,13 +5979,13 @@
         <v>1</v>
       </c>
       <c r="E164" t="n">
-        <v>0.0001893017507246173</v>
+        <v>0.0001893017507247895</v>
       </c>
       <c r="F164" t="n">
         <v>0.9417282087462753</v>
       </c>
       <c r="G164" t="n">
-        <v>0.05808248950295651</v>
+        <v>0.05808248950306216</v>
       </c>
     </row>
     <row r="165">
@@ -6002,10 +6002,10 @@
         <v>2</v>
       </c>
       <c r="E165" t="n">
-        <v>0.0002270897398010481</v>
+        <v>0.0002270897398012546</v>
       </c>
       <c r="F165" t="n">
-        <v>0.05541008861636557</v>
+        <v>0.05541008861644117</v>
       </c>
       <c r="G165" t="n">
         <v>0.9443628216438739</v>
@@ -6025,13 +6025,13 @@
         <v>1</v>
       </c>
       <c r="E166" t="n">
-        <v>0.0003013367932473804</v>
+        <v>0.0003013367932477915</v>
       </c>
       <c r="F166" t="n">
         <v>0.9433444291143382</v>
       </c>
       <c r="G166" t="n">
-        <v>0.05635423409249393</v>
+        <v>0.05635423409257081</v>
       </c>
     </row>
     <row r="167">
@@ -6048,10 +6048,10 @@
         <v>2</v>
       </c>
       <c r="E167" t="n">
-        <v>0.0008693395707519781</v>
+        <v>0.0008693395707531641</v>
       </c>
       <c r="F167" t="n">
-        <v>0.05297231780771092</v>
+        <v>0.05297231780775909</v>
       </c>
       <c r="G167" t="n">
         <v>0.9461583426216551</v>
@@ -6071,13 +6071,13 @@
         <v>1</v>
       </c>
       <c r="E168" t="n">
-        <v>0.0004142010870370113</v>
+        <v>0.000414201087037388</v>
       </c>
       <c r="F168" t="n">
         <v>0.9461016969905788</v>
       </c>
       <c r="G168" t="n">
-        <v>0.05348410192219552</v>
+        <v>0.05348410192226849</v>
       </c>
     </row>
     <row r="169">
@@ -6094,10 +6094,10 @@
         <v>2</v>
       </c>
       <c r="E169" t="n">
-        <v>0.0003297948732147019</v>
+        <v>0.0003297948732151518</v>
       </c>
       <c r="F169" t="n">
-        <v>0.05094937635177177</v>
+        <v>0.05094937635184128</v>
       </c>
       <c r="G169" t="n">
         <v>0.948720828775005</v>
@@ -6117,13 +6117,13 @@
         <v>1</v>
       </c>
       <c r="E170" t="n">
-        <v>0.000123008747412534</v>
+        <v>0.0001230087474127018</v>
       </c>
       <c r="F170" t="n">
         <v>0.9480542204043116</v>
       </c>
       <c r="G170" t="n">
-        <v>0.05182277084834714</v>
+        <v>0.0518227708484414</v>
       </c>
     </row>
     <row r="171">
@@ -6140,10 +6140,10 @@
         <v>2</v>
       </c>
       <c r="E171" t="n">
-        <v>0.0002047568746735612</v>
+        <v>0.0002047568746739337</v>
       </c>
       <c r="F171" t="n">
-        <v>0.04901698085061756</v>
+        <v>0.04901698085068443</v>
       </c>
       <c r="G171" t="n">
         <v>0.950778262274603</v>
@@ -6163,13 +6163,13 @@
         <v>1</v>
       </c>
       <c r="E172" t="n">
-        <v>0.000335096872969793</v>
+        <v>0.0003350968729700977</v>
       </c>
       <c r="F172" t="n">
         <v>0.9498055466444467</v>
       </c>
       <c r="G172" t="n">
-        <v>0.04985935648266403</v>
+        <v>0.04985935648270937</v>
       </c>
     </row>
     <row r="173">
@@ -6186,13 +6186,13 @@
         <v>2</v>
       </c>
       <c r="E173" t="n">
-        <v>0.0003647793817159871</v>
+        <v>0.0003647793817163188</v>
       </c>
       <c r="F173" t="n">
-        <v>0.04722675850047076</v>
+        <v>0.04722675850049224</v>
       </c>
       <c r="G173" t="n">
-        <v>0.9524084621180214</v>
+        <v>0.9524084621175883</v>
       </c>
     </row>
     <row r="174">
@@ -6209,13 +6209,13 @@
         <v>1</v>
       </c>
       <c r="E174" t="n">
-        <v>0.0005299987481812745</v>
+        <v>0.0005299987481815155</v>
       </c>
       <c r="F174" t="n">
         <v>0.9513750321130204</v>
       </c>
       <c r="G174" t="n">
-        <v>0.0480949691389144</v>
+        <v>0.04809496913900189</v>
       </c>
     </row>
     <row r="175">
@@ -6232,10 +6232,10 @@
         <v>2</v>
       </c>
       <c r="E175" t="n">
-        <v>0.001788066541712613</v>
+        <v>0.001788066541715053</v>
       </c>
       <c r="F175" t="n">
-        <v>0.04445580779412111</v>
+        <v>0.04445580779418176</v>
       </c>
       <c r="G175" t="n">
         <v>0.9537561256641307</v>
@@ -6255,13 +6255,13 @@
         <v>1</v>
       </c>
       <c r="E176" t="n">
-        <v>0.0001629064254298868</v>
+        <v>0.0001629064254299609</v>
       </c>
       <c r="F176" t="n">
-        <v>0.9547186389826749</v>
+        <v>0.9547186389822407</v>
       </c>
       <c r="G176" t="n">
-        <v>0.04511845459209206</v>
+        <v>0.04511845459215361</v>
       </c>
     </row>
     <row r="177">
@@ -6278,10 +6278,10 @@
         <v>2</v>
       </c>
       <c r="E177" t="n">
-        <v>0.0003912086554655557</v>
+        <v>0.0003912086554660894</v>
       </c>
       <c r="F177" t="n">
-        <v>0.04166690879034472</v>
+        <v>0.04166690879036367</v>
       </c>
       <c r="G177" t="n">
         <v>0.9579418825539928</v>
@@ -6301,13 +6301,13 @@
         <v>1</v>
       </c>
       <c r="E178" t="n">
-        <v>0.0007034757262899392</v>
+        <v>0.0007034757262896192</v>
       </c>
       <c r="F178" t="n">
         <v>0.9570337714609852</v>
       </c>
       <c r="G178" t="n">
-        <v>0.04226275281264576</v>
+        <v>0.0422627528126842</v>
       </c>
     </row>
     <row r="179">
@@ -6324,13 +6324,13 @@
         <v>2</v>
       </c>
       <c r="E179" t="n">
-        <v>0.0006341408158961154</v>
+        <v>0.0006341408158958271</v>
       </c>
       <c r="F179" t="n">
-        <v>0.04070162896669093</v>
+        <v>0.04070162896670944</v>
       </c>
       <c r="G179" t="n">
-        <v>0.95866423021761</v>
+        <v>0.9586642302171741</v>
       </c>
     </row>
     <row r="180">
@@ -6347,13 +6347,13 @@
         <v>1</v>
       </c>
       <c r="E180" t="n">
-        <v>0.0006114661578118856</v>
+        <v>0.0006114661578121636</v>
       </c>
       <c r="F180" t="n">
         <v>0.9575357207602579</v>
       </c>
       <c r="G180" t="n">
-        <v>0.04185281308190631</v>
+        <v>0.0418528130819634</v>
       </c>
     </row>
     <row r="181">
@@ -6370,10 +6370,10 @@
         <v>2</v>
       </c>
       <c r="E181" t="n">
-        <v>0.001120027459419608</v>
+        <v>0.001120027459420627</v>
       </c>
       <c r="F181" t="n">
-        <v>0.03960959767578914</v>
+        <v>0.03960959767582517</v>
       </c>
       <c r="G181" t="n">
         <v>0.9592703748647422</v>
@@ -6393,13 +6393,13 @@
         <v>1</v>
       </c>
       <c r="E182" t="n">
-        <v>0.001758610019452999</v>
+        <v>0.001758610019451399</v>
       </c>
       <c r="F182" t="n">
         <v>0.9577228570875634</v>
       </c>
       <c r="G182" t="n">
-        <v>0.04051853289314616</v>
+        <v>0.04051853289320143</v>
       </c>
     </row>
     <row r="183">
@@ -6416,10 +6416,10 @@
         <v>2</v>
       </c>
       <c r="E183" t="n">
-        <v>0.002360204651481815</v>
+        <v>0.002360204651479668</v>
       </c>
       <c r="F183" t="n">
-        <v>0.03794988144557884</v>
+        <v>0.03794988144561335</v>
       </c>
       <c r="G183" t="n">
         <v>0.9596899139029377</v>
@@ -6439,13 +6439,13 @@
         <v>1</v>
       </c>
       <c r="E184" t="n">
-        <v>0.01429973105933721</v>
+        <v>0.0142997310593177</v>
       </c>
       <c r="F184" t="n">
         <v>0.9468459539858485</v>
       </c>
       <c r="G184" t="n">
-        <v>0.03885431495467467</v>
+        <v>0.03885431495469234</v>
       </c>
     </row>
     <row r="185">
@@ -6462,10 +6462,10 @@
         <v>2</v>
       </c>
       <c r="E185" t="n">
-        <v>0.04506403050853937</v>
+        <v>0.04506403050855987</v>
       </c>
       <c r="F185" t="n">
-        <v>0.006198599774715902</v>
+        <v>0.00619859977472154</v>
       </c>
       <c r="G185" t="n">
         <v>0.9487373697169443</v>
@@ -6491,7 +6491,7 @@
         <v>0.07161072380627455</v>
       </c>
       <c r="G186" t="n">
-        <v>0.006220839649295619</v>
+        <v>0.006220839649301277</v>
       </c>
     </row>
     <row r="187">
@@ -6511,7 +6511,7 @@
         <v>0.9257177503419998</v>
       </c>
       <c r="F187" t="n">
-        <v>0.002626876588728803</v>
+        <v>0.002626876588732387</v>
       </c>
       <c r="G187" t="n">
         <v>0.07165537306904765</v>
@@ -6537,7 +6537,7 @@
         <v>0.9432545575427858</v>
       </c>
       <c r="G188" t="n">
-        <v>0.002675710487037185</v>
+        <v>0.002675710487042053</v>
       </c>
     </row>
     <row r="189">
@@ -6554,10 +6554,10 @@
         <v>2</v>
       </c>
       <c r="E189" t="n">
-        <v>0.04287633176705258</v>
+        <v>0.04287633176703308</v>
       </c>
       <c r="F189" t="n">
-        <v>0.01350647843144738</v>
+        <v>0.01350647843145352</v>
       </c>
       <c r="G189" t="n">
         <v>0.9436171898013744</v>
@@ -6577,7 +6577,7 @@
         <v>1</v>
       </c>
       <c r="E190" t="n">
-        <v>0.007161458009707055</v>
+        <v>0.007161458009703799</v>
       </c>
       <c r="F190" t="n">
         <v>0.9789823136417642</v>
@@ -6600,10 +6600,10 @@
         <v>2</v>
       </c>
       <c r="E191" t="n">
-        <v>0.004959407806195974</v>
+        <v>0.004959407806193719</v>
       </c>
       <c r="F191" t="n">
-        <v>0.01508787297571158</v>
+        <v>0.01508787297572531</v>
       </c>
       <c r="G191" t="n">
         <v>0.9799527192179991</v>
@@ -6623,13 +6623,13 @@
         <v>1</v>
       </c>
       <c r="E192" t="n">
-        <v>0.0004417204097523507</v>
+        <v>0.000441720409751949</v>
       </c>
       <c r="F192" t="n">
         <v>0.9839640364347148</v>
       </c>
       <c r="G192" t="n">
-        <v>0.01559424315536044</v>
+        <v>0.01559424315538172</v>
       </c>
     </row>
     <row r="193">
@@ -6649,7 +6649,7 @@
         <v>0.0005440819619599643</v>
       </c>
       <c r="F193" t="n">
-        <v>0.0140736139364811</v>
+        <v>0.0140736139364939</v>
       </c>
       <c r="G193" t="n">
         <v>0.9853823041013778</v>
@@ -6669,13 +6669,13 @@
         <v>1</v>
       </c>
       <c r="E194" t="n">
-        <v>0.0002764713631341034</v>
+        <v>0.0002764713631342291</v>
       </c>
       <c r="F194" t="n">
         <v>0.9851957205838541</v>
       </c>
       <c r="G194" t="n">
-        <v>0.01452780805283507</v>
+        <v>0.01452780805285489</v>
       </c>
     </row>
     <row r="195">
@@ -6692,10 +6692,10 @@
         <v>2</v>
       </c>
       <c r="E195" t="n">
-        <v>0.0003822195508718891</v>
+        <v>0.0003822195508722368</v>
       </c>
       <c r="F195" t="n">
-        <v>0.01292608143378258</v>
+        <v>0.01292608143380021</v>
       </c>
       <c r="G195" t="n">
         <v>0.9866916990155229</v>
@@ -6715,13 +6715,13 @@
         <v>1</v>
       </c>
       <c r="E196" t="n">
-        <v>0.001998822282460152</v>
+        <v>0.00199882228246197</v>
       </c>
       <c r="F196" t="n">
         <v>0.98464654391601</v>
       </c>
       <c r="G196" t="n">
-        <v>0.01335463380164975</v>
+        <v>0.01335463380167404</v>
       </c>
     </row>
     <row r="197">
@@ -6738,10 +6738,10 @@
         <v>2</v>
       </c>
       <c r="E197" t="n">
-        <v>0.001720777727289773</v>
+        <v>0.001720777727291338</v>
       </c>
       <c r="F197" t="n">
-        <v>0.01260369558960274</v>
+        <v>0.01260369558961993</v>
       </c>
       <c r="G197" t="n">
         <v>0.9856755266829647</v>
@@ -6761,13 +6761,13 @@
         <v>1</v>
       </c>
       <c r="E198" t="n">
-        <v>0.001732866571437573</v>
+        <v>0.001732866571438361</v>
       </c>
       <c r="F198" t="n">
         <v>0.9850959340496298</v>
       </c>
       <c r="G198" t="n">
-        <v>0.0131711993787877</v>
+        <v>0.01317119937880567</v>
       </c>
     </row>
     <row r="199">
@@ -6784,10 +6784,10 @@
         <v>2</v>
       </c>
       <c r="E199" t="n">
-        <v>0.002070401095840875</v>
+        <v>0.002070401095843699</v>
       </c>
       <c r="F199" t="n">
-        <v>0.01183049205942364</v>
+        <v>0.01183049205944516</v>
       </c>
       <c r="G199" t="n">
         <v>0.9860991068447964</v>
@@ -6807,13 +6807,13 @@
         <v>1</v>
       </c>
       <c r="E200" t="n">
-        <v>0.003094144212242526</v>
+        <v>0.00309414421224534</v>
       </c>
       <c r="F200" t="n">
         <v>0.9847610661176071</v>
       </c>
       <c r="G200" t="n">
-        <v>0.01214478967013664</v>
+        <v>0.01214478967016425</v>
       </c>
     </row>
     <row r="201">
@@ -6830,10 +6830,10 @@
         <v>2</v>
       </c>
       <c r="E201" t="n">
-        <v>0.001535000119971055</v>
+        <v>0.001535000119972451</v>
       </c>
       <c r="F201" t="n">
-        <v>0.01319050125768798</v>
+        <v>0.01319050125772397</v>
       </c>
       <c r="G201" t="n">
         <v>0.9852744986222693</v>
@@ -6853,13 +6853,13 @@
         <v>1</v>
       </c>
       <c r="E202" t="n">
-        <v>0.0002158530023397479</v>
+        <v>0.0002158530023399442</v>
       </c>
       <c r="F202" t="n">
         <v>0.9855645842469475</v>
       </c>
       <c r="G202" t="n">
-        <v>0.01421956275082975</v>
+        <v>0.01421956275086209</v>
       </c>
     </row>
     <row r="203">
@@ -6876,10 +6876,10 @@
         <v>2</v>
       </c>
       <c r="E203" t="n">
-        <v>0.0001695052892925258</v>
+        <v>0.0001695052892928341</v>
       </c>
       <c r="F203" t="n">
-        <v>0.01359218929649079</v>
+        <v>0.01359218929652787</v>
       </c>
       <c r="G203" t="n">
         <v>0.9862383054142042</v>
@@ -6899,13 +6899,13 @@
         <v>1</v>
       </c>
       <c r="E204" t="n">
-        <v>0.0002333718115114327</v>
+        <v>0.0002333718115118572</v>
       </c>
       <c r="F204" t="n">
         <v>0.985176051669443</v>
       </c>
       <c r="G204" t="n">
-        <v>0.01459057651884183</v>
+        <v>0.01459057651888827</v>
       </c>
     </row>
     <row r="205">
@@ -6922,10 +6922,10 @@
         <v>2</v>
       </c>
       <c r="E205" t="n">
-        <v>0.0001842876811212425</v>
+        <v>0.0001842876811214102</v>
       </c>
       <c r="F205" t="n">
-        <v>0.01411097118353761</v>
+        <v>0.01411097118356328</v>
       </c>
       <c r="G205" t="n">
         <v>0.9857047411354084</v>
@@ -6945,13 +6945,13 @@
         <v>1</v>
       </c>
       <c r="E206" t="n">
-        <v>0.0001631261005959699</v>
+        <v>0.0001631261005960441</v>
       </c>
       <c r="F206" t="n">
         <v>0.9847724338559022</v>
       </c>
       <c r="G206" t="n">
-        <v>0.01506444004335809</v>
+        <v>0.01506444004338549</v>
       </c>
     </row>
     <row r="207">
@@ -6968,10 +6968,10 @@
         <v>2</v>
       </c>
       <c r="E207" t="n">
-        <v>0.0002187709704119642</v>
+        <v>0.0002187709704123622</v>
       </c>
       <c r="F207" t="n">
-        <v>0.01428177325586499</v>
+        <v>0.01428177325589096</v>
       </c>
       <c r="G207" t="n">
         <v>0.9854994557738804</v>
@@ -6991,13 +6991,13 @@
         <v>1</v>
       </c>
       <c r="E208" t="n">
-        <v>0.0002404734097733638</v>
+        <v>0.0002404734097735825</v>
       </c>
       <c r="F208" t="n">
         <v>0.9845767986354649</v>
       </c>
       <c r="G208" t="n">
-        <v>0.01518272795494855</v>
+        <v>0.01518272795498307</v>
       </c>
     </row>
     <row r="209">
@@ -7014,10 +7014,10 @@
         <v>2</v>
       </c>
       <c r="E209" t="n">
-        <v>0.0002137826731388989</v>
+        <v>0.0002137826731390933</v>
       </c>
       <c r="F209" t="n">
-        <v>0.01442510915437882</v>
+        <v>0.01442510915441162</v>
       </c>
       <c r="G209" t="n">
         <v>0.9853611081726614</v>
@@ -7037,13 +7037,13 @@
         <v>1</v>
       </c>
       <c r="E210" t="n">
-        <v>0.0007183468853671048</v>
+        <v>0.0007183468853674315</v>
       </c>
       <c r="F210" t="n">
         <v>0.9839781868850412</v>
       </c>
       <c r="G210" t="n">
-        <v>0.01530346622951493</v>
+        <v>0.01530346622954972</v>
       </c>
     </row>
     <row r="211">
@@ -7060,10 +7060,10 @@
         <v>2</v>
       </c>
       <c r="E211" t="n">
-        <v>0.0008641466229841839</v>
+        <v>0.0008641466229853628</v>
       </c>
       <c r="F211" t="n">
-        <v>0.01434154330041535</v>
+        <v>0.01434154330043491</v>
       </c>
       <c r="G211" t="n">
         <v>0.9847943100766283</v>
@@ -7083,13 +7083,13 @@
         <v>1</v>
       </c>
       <c r="E212" t="n">
-        <v>0.0003032503368126476</v>
+        <v>0.0003032503368125097</v>
       </c>
       <c r="F212" t="n">
         <v>0.9849016477760838</v>
       </c>
       <c r="G212" t="n">
-        <v>0.01479510188693675</v>
+        <v>0.01479510188695693</v>
       </c>
     </row>
     <row r="213">
@@ -7106,7 +7106,7 @@
         <v>2</v>
       </c>
       <c r="E213" t="n">
-        <v>0.0004966119408658648</v>
+        <v>0.0004966119408663165</v>
       </c>
       <c r="F213" t="n">
         <v>0.0133715996480768</v>
@@ -7135,7 +7135,7 @@
         <v>0.9853873620820081</v>
       </c>
       <c r="G214" t="n">
-        <v>0.01385885648864356</v>
+        <v>0.01385885648865616</v>
       </c>
     </row>
     <row r="215">
@@ -7152,7 +7152,7 @@
         <v>2</v>
       </c>
       <c r="E215" t="n">
-        <v>0.0005307062803428324</v>
+        <v>0.0005307062803433151</v>
       </c>
       <c r="F215" t="n">
         <v>0.0130484708844182</v>
@@ -7175,7 +7175,7 @@
         <v>1</v>
       </c>
       <c r="E216" t="n">
-        <v>0.0002188660125797817</v>
+        <v>0.0002188660125796822</v>
       </c>
       <c r="F216" t="n">
         <v>0.9861463992981242</v>
@@ -7198,7 +7198,7 @@
         <v>2</v>
       </c>
       <c r="E217" t="n">
-        <v>0.0001821228517011868</v>
+        <v>0.0001821228517014352</v>
       </c>
       <c r="F217" t="n">
         <v>0.01263511667037825</v>
@@ -7221,7 +7221,7 @@
         <v>1</v>
       </c>
       <c r="E218" t="n">
-        <v>0.0001777632621866307</v>
+        <v>0.0001777632621865499</v>
       </c>
       <c r="F218" t="n">
         <v>0.9866138991956898</v>
@@ -7244,10 +7244,10 @@
         <v>2</v>
       </c>
       <c r="E219" t="n">
-        <v>0.0002915509687809594</v>
+        <v>0.0002915509687812246</v>
       </c>
       <c r="F219" t="n">
-        <v>0.01206023463775376</v>
+        <v>0.01206023463774828</v>
       </c>
       <c r="G219" t="n">
         <v>0.987648214393392</v>
@@ -7267,13 +7267,13 @@
         <v>1</v>
       </c>
       <c r="E220" t="n">
-        <v>0.001699470338423156</v>
+        <v>0.001699470338421611</v>
       </c>
       <c r="F220" t="n">
         <v>0.9856697215176367</v>
       </c>
       <c r="G220" t="n">
-        <v>0.01263080814387928</v>
+        <v>0.0126308081438678</v>
       </c>
     </row>
     <row r="221">
@@ -7290,13 +7290,13 @@
         <v>2</v>
       </c>
       <c r="E221" t="n">
-        <v>0.003079965178845633</v>
+        <v>0.003079965178847033</v>
       </c>
       <c r="F221" t="n">
-        <v>0.01016230656363174</v>
+        <v>0.01016230656361788</v>
       </c>
       <c r="G221" t="n">
-        <v>0.9867577282572957</v>
+        <v>0.9867577282577443</v>
       </c>
     </row>
     <row r="222">
@@ -7313,13 +7313,13 @@
         <v>1</v>
       </c>
       <c r="E222" t="n">
-        <v>0.06386086255473784</v>
+        <v>0.06386086255467976</v>
       </c>
       <c r="F222" t="n">
         <v>0.9255740860523922</v>
       </c>
       <c r="G222" t="n">
-        <v>0.01056505139293271</v>
+        <v>0.01056505139291349</v>
       </c>
     </row>
     <row r="223">
@@ -7339,7 +7339,7 @@
         <v>0.04604160950812596</v>
       </c>
       <c r="F223" t="n">
-        <v>0.02819789936992645</v>
+        <v>0.02819789936984952</v>
       </c>
       <c r="G223" t="n">
         <v>0.9257604911220568</v>
@@ -7359,13 +7359,13 @@
         <v>1</v>
       </c>
       <c r="E224" t="n">
-        <v>0.0031755943942843</v>
+        <v>0.003175594394278524</v>
       </c>
       <c r="F224" t="n">
-        <v>0.9664274282579355</v>
+        <v>0.9664274282583749</v>
       </c>
       <c r="G224" t="n">
-        <v>0.03039697734760033</v>
+        <v>0.03039697734754504</v>
       </c>
     </row>
     <row r="225">
@@ -7385,7 +7385,7 @@
         <v>0.0009738479296728578</v>
       </c>
       <c r="F225" t="n">
-        <v>0.0320503187857696</v>
+        <v>0.0320503187857113</v>
       </c>
       <c r="G225" t="n">
         <v>0.9669758332845271</v>
@@ -7405,13 +7405,13 @@
         <v>1</v>
       </c>
       <c r="E226" t="n">
-        <v>0.0004157002555926091</v>
+        <v>0.0004157002555918529</v>
       </c>
       <c r="F226" t="n">
-        <v>0.9649414716227341</v>
+        <v>0.964941471623173</v>
       </c>
       <c r="G226" t="n">
-        <v>0.03464282812147462</v>
+        <v>0.0346428281214116</v>
       </c>
     </row>
     <row r="227">
@@ -7428,13 +7428,13 @@
         <v>2</v>
       </c>
       <c r="E227" t="n">
-        <v>0.0001389312251518833</v>
+        <v>0.0001389312251519465</v>
       </c>
       <c r="F227" t="n">
-        <v>0.03442597885434576</v>
+        <v>0.03442597885428315</v>
       </c>
       <c r="G227" t="n">
-        <v>0.9654350899202923</v>
+        <v>0.9654350899207313</v>
       </c>
     </row>
     <row r="228">
@@ -7451,13 +7451,13 @@
         <v>1</v>
       </c>
       <c r="E228" t="n">
-        <v>0.0006851283532569327</v>
+        <v>0.000685128353255998</v>
       </c>
       <c r="F228" t="n">
         <v>0.9616180055539749</v>
       </c>
       <c r="G228" t="n">
-        <v>0.03769686609279395</v>
+        <v>0.03769686609272538</v>
       </c>
     </row>
     <row r="229">
@@ -7474,10 +7474,10 @@
         <v>2</v>
       </c>
       <c r="E229" t="n">
-        <v>0.0003230571457266297</v>
+        <v>0.0003230571457267766</v>
       </c>
       <c r="F229" t="n">
-        <v>0.03768042321092097</v>
+        <v>0.0376804232108353</v>
       </c>
       <c r="G229" t="n">
         <v>0.9619965196435477</v>
@@ -7497,13 +7497,13 @@
         <v>1</v>
       </c>
       <c r="E230" t="n">
-        <v>0.0007581493226781</v>
+        <v>0.0007581493226770657</v>
       </c>
       <c r="F230" t="n">
         <v>0.9570892327382027</v>
       </c>
       <c r="G230" t="n">
-        <v>0.04215261793909097</v>
+        <v>0.04215261793903347</v>
       </c>
     </row>
     <row r="231">
@@ -7520,10 +7520,10 @@
         <v>2</v>
       </c>
       <c r="E231" t="n">
-        <v>0.0002177013880884985</v>
+        <v>0.0002177013880886965</v>
       </c>
       <c r="F231" t="n">
-        <v>0.04227786839584935</v>
+        <v>0.04227786839581089</v>
       </c>
       <c r="G231" t="n">
         <v>0.957504430215991</v>
@@ -7543,13 +7543,13 @@
         <v>1</v>
       </c>
       <c r="E232" t="n">
-        <v>0.0007215657618071526</v>
+        <v>0.0007215657618068245</v>
       </c>
       <c r="F232" t="n">
         <v>0.9521919487103472</v>
       </c>
       <c r="G232" t="n">
-        <v>0.04708648552768914</v>
+        <v>0.04708648552766773</v>
       </c>
     </row>
     <row r="233">
@@ -7566,10 +7566,10 @@
         <v>2</v>
       </c>
       <c r="E233" t="n">
-        <v>0.0002018302425120075</v>
+        <v>0.0002018302425121911</v>
       </c>
       <c r="F233" t="n">
-        <v>0.04727304027178055</v>
+        <v>0.04727304027175906</v>
       </c>
       <c r="G233" t="n">
         <v>0.9525251294856802</v>
@@ -7589,7 +7589,7 @@
         <v>1</v>
       </c>
       <c r="E234" t="n">
-        <v>0.001343961866267038</v>
+        <v>0.001343961866265815</v>
       </c>
       <c r="F234" t="n">
         <v>0.9460974715884481</v>
@@ -7612,10 +7612,10 @@
         <v>2</v>
       </c>
       <c r="E235" t="n">
-        <v>0.0006722010232795184</v>
+        <v>0.0006722010232798241</v>
       </c>
       <c r="F235" t="n">
-        <v>0.05278546513406113</v>
+        <v>0.05278546513403713</v>
       </c>
       <c r="G235" t="n">
         <v>0.9465423338427356</v>
@@ -7635,13 +7635,13 @@
         <v>1</v>
       </c>
       <c r="E236" t="n">
-        <v>0.0007292027079144836</v>
+        <v>0.0007292027079138204</v>
       </c>
       <c r="F236" t="n">
         <v>0.9426904143062519</v>
       </c>
       <c r="G236" t="n">
-        <v>0.05658038298603846</v>
+        <v>0.05658038298601273</v>
       </c>
     </row>
     <row r="237">
@@ -7658,7 +7658,7 @@
         <v>2</v>
       </c>
       <c r="E237" t="n">
-        <v>0.0001805676846289308</v>
+        <v>0.0001805676846290951</v>
       </c>
       <c r="F237" t="n">
         <v>0.05652648490332436</v>
@@ -7681,13 +7681,13 @@
         <v>1</v>
       </c>
       <c r="E238" t="n">
-        <v>0.0005780953046175602</v>
+        <v>0.0005780953046170343</v>
       </c>
       <c r="F238" t="n">
         <v>0.9389817930153925</v>
       </c>
       <c r="G238" t="n">
-        <v>0.0604401116801663</v>
+        <v>0.06044011168013882</v>
       </c>
     </row>
     <row r="239">
@@ -7704,7 +7704,7 @@
         <v>2</v>
       </c>
       <c r="E239" t="n">
-        <v>0.0006554534911364386</v>
+        <v>0.0006554534911373327</v>
       </c>
       <c r="F239" t="n">
         <v>0.05969643718471074</v>
@@ -7750,10 +7750,10 @@
         <v>2</v>
       </c>
       <c r="E241" t="n">
-        <v>0.0009205923146212069</v>
+        <v>0.0009205923146224629</v>
       </c>
       <c r="F241" t="n">
-        <v>0.06162796105087974</v>
+        <v>0.06162796105093579</v>
       </c>
       <c r="G241" t="n">
         <v>0.9374514466345967</v>
@@ -7796,7 +7796,7 @@
         <v>2</v>
       </c>
       <c r="E243" t="n">
-        <v>0.0004980436174648805</v>
+        <v>0.0004980436174655599</v>
       </c>
       <c r="F243" t="n">
         <v>0.06311287871110978</v>
@@ -7819,13 +7819,13 @@
         <v>1</v>
       </c>
       <c r="E244" t="n">
-        <v>0.0001539331940197571</v>
+        <v>0.000153933194019617</v>
       </c>
       <c r="F244" t="n">
         <v>0.9349826845514178</v>
       </c>
       <c r="G244" t="n">
-        <v>0.06486338225451713</v>
+        <v>0.06486338225448764</v>
       </c>
     </row>
     <row r="245">
@@ -7842,7 +7842,7 @@
         <v>2</v>
       </c>
       <c r="E245" t="n">
-        <v>0.0001558130144252098</v>
+        <v>0.0001558130144255641</v>
       </c>
       <c r="F245" t="n">
         <v>0.06314168741260422</v>
@@ -7865,7 +7865,7 @@
         <v>1</v>
       </c>
       <c r="E246" t="n">
-        <v>0.0001945649803451389</v>
+        <v>0.0001945649803449619</v>
       </c>
       <c r="F246" t="n">
         <v>0.9351118884138857</v>
@@ -7888,10 +7888,10 @@
         <v>2</v>
       </c>
       <c r="E247" t="n">
-        <v>0.0001999523317003862</v>
+        <v>0.0001999523317007499</v>
       </c>
       <c r="F247" t="n">
-        <v>0.06286073062890157</v>
+        <v>0.06286073062893016</v>
       </c>
       <c r="G247" t="n">
         <v>0.936939317039411</v>
@@ -7911,13 +7911,13 @@
         <v>1</v>
       </c>
       <c r="E248" t="n">
-        <v>0.0005159370689940352</v>
+        <v>0.0005159370689938005</v>
       </c>
       <c r="F248" t="n">
         <v>0.9349977698890202</v>
       </c>
       <c r="G248" t="n">
-        <v>0.06448629304199839</v>
+        <v>0.06448629304196907</v>
       </c>
     </row>
     <row r="249">
@@ -7934,7 +7934,7 @@
         <v>2</v>
       </c>
       <c r="E249" t="n">
-        <v>0.001026909387741596</v>
+        <v>0.001026909387742997</v>
       </c>
       <c r="F249" t="n">
         <v>0.06229575136630949</v>
@@ -7957,13 +7957,13 @@
         <v>1</v>
       </c>
       <c r="E250" t="n">
-        <v>0.0004385766821802801</v>
+        <v>0.0004385766821798813</v>
       </c>
       <c r="F250" t="n">
         <v>0.935861960081839</v>
       </c>
       <c r="G250" t="n">
-        <v>0.06369946323591719</v>
+        <v>0.06369946323588822</v>
       </c>
     </row>
     <row r="251">
@@ -7980,10 +7980,10 @@
         <v>2</v>
       </c>
       <c r="E251" t="n">
-        <v>0.0001917281953365119</v>
+        <v>0.0001917281953368607</v>
       </c>
       <c r="F251" t="n">
-        <v>0.06266184204417126</v>
+        <v>0.06266184204419976</v>
       </c>
       <c r="G251" t="n">
         <v>0.9371464297605359</v>
@@ -8003,7 +8003,7 @@
         <v>1</v>
       </c>
       <c r="E252" t="n">
-        <v>0.0002677412749555954</v>
+        <v>0.0002677412749554736</v>
       </c>
       <c r="F252" t="n">
         <v>0.9349629763497745</v>
@@ -8026,7 +8026,7 @@
         <v>2</v>
       </c>
       <c r="E253" t="n">
-        <v>0.000262021980571278</v>
+        <v>0.0002620219805716354</v>
       </c>
       <c r="F253" t="n">
         <v>0.06352128239297576</v>
@@ -8049,7 +8049,7 @@
         <v>1</v>
       </c>
       <c r="E254" t="n">
-        <v>0.0002696137787819372</v>
+        <v>0.0002696137787818146</v>
       </c>
       <c r="F254" t="n">
         <v>0.9338818394882644</v>
@@ -8072,7 +8072,7 @@
         <v>2</v>
       </c>
       <c r="E255" t="n">
-        <v>0.0001740769426255731</v>
+        <v>0.0001740769426258106</v>
       </c>
       <c r="F255" t="n">
         <v>0.06490954529523613</v>
@@ -8095,13 +8095,13 @@
         <v>1</v>
       </c>
       <c r="E256" t="n">
-        <v>0.0005321345048187569</v>
+        <v>0.0005321345048182729</v>
       </c>
       <c r="F256" t="n">
         <v>0.9320482412246048</v>
       </c>
       <c r="G256" t="n">
-        <v>0.06741962427062279</v>
+        <v>0.06741962427065344</v>
       </c>
     </row>
     <row r="257">
@@ -8118,10 +8118,10 @@
         <v>2</v>
       </c>
       <c r="E257" t="n">
-        <v>0.0002702185055488032</v>
+        <v>0.0002702185055490489</v>
       </c>
       <c r="F257" t="n">
-        <v>0.06647922636027181</v>
+        <v>0.06647922636030205</v>
       </c>
       <c r="G257" t="n">
         <v>0.9332505551341653</v>
@@ -8141,13 +8141,13 @@
         <v>1</v>
       </c>
       <c r="E258" t="n">
-        <v>0.0003905330188017742</v>
+        <v>0.0003905330188014191</v>
       </c>
       <c r="F258" t="n">
         <v>0.9305610973437662</v>
       </c>
       <c r="G258" t="n">
-        <v>0.06904836963741276</v>
+        <v>0.06904836963747556</v>
       </c>
     </row>
     <row r="259">
@@ -8164,13 +8164,13 @@
         <v>2</v>
       </c>
       <c r="E259" t="n">
-        <v>0.0001449517952475387</v>
+        <v>0.0001449517952476705</v>
       </c>
       <c r="F259" t="n">
-        <v>0.06841760047258444</v>
+        <v>0.06841760047261555</v>
       </c>
       <c r="G259" t="n">
-        <v>0.9314374477323796</v>
+        <v>0.931437447731956</v>
       </c>
     </row>
     <row r="260">
@@ -8187,13 +8187,13 @@
         <v>1</v>
       </c>
       <c r="E260" t="n">
-        <v>0.0002446987617107494</v>
+        <v>0.0002446987617106381</v>
       </c>
       <c r="F260" t="n">
         <v>0.9277429612826587</v>
       </c>
       <c r="G260" t="n">
-        <v>0.07201233995550645</v>
+        <v>0.0720123399555392</v>
       </c>
     </row>
     <row r="261">
@@ -8210,10 +8210,10 @@
         <v>2</v>
       </c>
       <c r="E261" t="n">
-        <v>0.0001171614946000803</v>
+        <v>0.0001171614946002402</v>
       </c>
       <c r="F261" t="n">
-        <v>0.07129304670048972</v>
+        <v>0.07129304670052214</v>
       </c>
       <c r="G261" t="n">
         <v>0.9285897918048821</v>
@@ -8233,13 +8233,13 @@
         <v>1</v>
       </c>
       <c r="E262" t="n">
-        <v>0.0002821738810328986</v>
+        <v>0.0002821738810325137</v>
       </c>
       <c r="F262" t="n">
-        <v>0.9247817158682807</v>
+        <v>0.9247817158678602</v>
       </c>
       <c r="G262" t="n">
-        <v>0.07493611025088445</v>
+        <v>0.07493611025091854</v>
       </c>
     </row>
     <row r="263">
@@ -8256,7 +8256,7 @@
         <v>2</v>
       </c>
       <c r="E263" t="n">
-        <v>0.0002338414072063202</v>
+        <v>0.0002338414072067455</v>
       </c>
       <c r="F263" t="n">
         <v>0.07408190182825627</v>
@@ -8279,7 +8279,7 @@
         <v>1</v>
       </c>
       <c r="E264" t="n">
-        <v>0.001044422829642553</v>
+        <v>0.001044422829642077</v>
       </c>
       <c r="F264" t="n">
         <v>0.9220175070174577</v>
@@ -8302,10 +8302,10 @@
         <v>2</v>
       </c>
       <c r="E265" t="n">
-        <v>0.0003318782172415606</v>
+        <v>0.0003318782172418624</v>
       </c>
       <c r="F265" t="n">
-        <v>0.07656144362535837</v>
+        <v>0.07656144362542801</v>
       </c>
       <c r="G265" t="n">
         <v>0.9231066781573183</v>
@@ -8325,13 +8325,13 @@
         <v>1</v>
       </c>
       <c r="E266" t="n">
-        <v>0.0002090714903726962</v>
+        <v>0.000209071490372506</v>
       </c>
       <c r="F266" t="n">
         <v>0.9202986186617614</v>
       </c>
       <c r="G266" t="n">
-        <v>0.07949230984779988</v>
+        <v>0.07949230984787219</v>
       </c>
     </row>
     <row r="267">
@@ -8348,10 +8348,10 @@
         <v>2</v>
       </c>
       <c r="E267" t="n">
-        <v>0.0001283981989503745</v>
+        <v>0.000128398198950608</v>
       </c>
       <c r="F267" t="n">
-        <v>0.07838697103838907</v>
+        <v>0.07838697103846036</v>
       </c>
       <c r="G267" t="n">
         <v>0.9214846307626192</v>
@@ -8371,13 +8371,13 @@
         <v>1</v>
       </c>
       <c r="E268" t="n">
-        <v>0.0002023544608263274</v>
+        <v>0.0002023544608260513</v>
       </c>
       <c r="F268" t="n">
-        <v>0.9185132260834057</v>
+        <v>0.9185132260829879</v>
       </c>
       <c r="G268" t="n">
-        <v>0.0812844194559785</v>
+        <v>0.08128441945601546</v>
       </c>
     </row>
     <row r="269">
@@ -8394,13 +8394,13 @@
         <v>2</v>
       </c>
       <c r="E269" t="n">
-        <v>0.0001158115452067896</v>
+        <v>0.0001158115452069476</v>
       </c>
       <c r="F269" t="n">
-        <v>0.08014549470724654</v>
+        <v>0.08014549470728298</v>
       </c>
       <c r="G269" t="n">
-        <v>0.919738693747738</v>
+        <v>0.9197386937473198</v>
       </c>
     </row>
     <row r="270">
@@ -8417,13 +8417,13 @@
         <v>1</v>
       </c>
       <c r="E270" t="n">
-        <v>0.0002067190812694677</v>
+        <v>0.0002067190812693736</v>
       </c>
       <c r="F270" t="n">
         <v>0.9166659024767866</v>
       </c>
       <c r="G270" t="n">
-        <v>0.08312737844189101</v>
+        <v>0.08312737844200441</v>
       </c>
     </row>
     <row r="271">
@@ -8440,10 +8440,10 @@
         <v>2</v>
       </c>
       <c r="E271" t="n">
-        <v>0.0001427215532210767</v>
+        <v>0.0001427215532214661</v>
       </c>
       <c r="F271" t="n">
-        <v>0.08196578719345911</v>
+        <v>0.08196578719357094</v>
       </c>
       <c r="G271" t="n">
         <v>0.9178914912532699</v>
@@ -8463,13 +8463,13 @@
         <v>1</v>
       </c>
       <c r="E272" t="n">
-        <v>0.0004504814449650455</v>
+        <v>0.000450481444964431</v>
       </c>
       <c r="F272" t="n">
-        <v>0.9145164016217281</v>
+        <v>0.9145164016213122</v>
       </c>
       <c r="G272" t="n">
-        <v>0.08503311693351542</v>
+        <v>0.08503311693355409</v>
       </c>
     </row>
     <row r="273">
@@ -8486,13 +8486,13 @@
         <v>2</v>
       </c>
       <c r="E273" t="n">
-        <v>0.0004178933439968153</v>
+        <v>0.0004178933439973854</v>
       </c>
       <c r="F273" t="n">
-        <v>0.08385697917137511</v>
+        <v>0.0838569791714895</v>
       </c>
       <c r="G273" t="n">
-        <v>0.915725127484703</v>
+        <v>0.9157251274842866</v>
       </c>
     </row>
     <row r="274">
@@ -8509,13 +8509,13 @@
         <v>1</v>
       </c>
       <c r="E274" t="n">
-        <v>0.0002523089719627217</v>
+        <v>0.0002523089719626069</v>
       </c>
       <c r="F274" t="n">
-        <v>0.9130592788142222</v>
+        <v>0.913059278813807</v>
       </c>
       <c r="G274" t="n">
-        <v>0.08668841221396541</v>
+        <v>0.08668841221408366</v>
       </c>
     </row>
     <row r="275">
@@ -8532,10 +8532,10 @@
         <v>2</v>
       </c>
       <c r="E275" t="n">
-        <v>0.0001824775834176262</v>
+        <v>0.0001824775834178752</v>
       </c>
       <c r="F275" t="n">
-        <v>0.08538724448617449</v>
+        <v>0.08538724448629098</v>
       </c>
       <c r="G275" t="n">
         <v>0.914430277930405</v>
@@ -8555,13 +8555,13 @@
         <v>1</v>
       </c>
       <c r="E276" t="n">
-        <v>0.001471898818121021</v>
+        <v>0.001471898818119682</v>
       </c>
       <c r="F276" t="n">
         <v>0.9104141071237457</v>
       </c>
       <c r="G276" t="n">
-        <v>0.08811399405808856</v>
+        <v>0.08811399405820877</v>
       </c>
     </row>
     <row r="277">
@@ -8581,7 +8581,7 @@
         <v>0.0002678490440543098</v>
       </c>
       <c r="F277" t="n">
-        <v>0.08858529551674632</v>
+        <v>0.08858529551682688</v>
       </c>
       <c r="G277" t="n">
         <v>0.9111468554390564</v>
@@ -8607,7 +8607,7 @@
         <v>0.9057599708081081</v>
       </c>
       <c r="G278" t="n">
-        <v>0.09374946567424051</v>
+        <v>0.09374946567436841</v>
       </c>
     </row>
     <row r="279">
@@ -8624,13 +8624,13 @@
         <v>2</v>
       </c>
       <c r="E279" t="n">
-        <v>0.0001563291909125755</v>
+        <v>0.0001563291909127177</v>
       </c>
       <c r="F279" t="n">
-        <v>0.09335485491752377</v>
+        <v>0.09335485491765112</v>
       </c>
       <c r="G279" t="n">
-        <v>0.9064888158916458</v>
+        <v>0.9064888158912335</v>
       </c>
     </row>
     <row r="280">
@@ -8647,13 +8647,13 @@
         <v>1</v>
       </c>
       <c r="E280" t="n">
-        <v>0.001134943834865881</v>
+        <v>0.001134943834864849</v>
       </c>
       <c r="F280" t="n">
         <v>0.9004379463364997</v>
       </c>
       <c r="G280" t="n">
-        <v>0.09842710982859049</v>
+        <v>0.09842710982872477</v>
       </c>
     </row>
     <row r="281">
@@ -8670,10 +8670,10 @@
         <v>2</v>
       </c>
       <c r="E281" t="n">
-        <v>0.0006047376867123085</v>
+        <v>0.0006047376867134085</v>
       </c>
       <c r="F281" t="n">
-        <v>0.0981801532857374</v>
+        <v>0.09818015328596062</v>
       </c>
       <c r="G281" t="n">
         <v>0.9012151090273472</v>
@@ -8693,13 +8693,13 @@
         <v>1</v>
       </c>
       <c r="E282" t="n">
-        <v>0.0002941896450031029</v>
+        <v>0.0002941896450028354</v>
       </c>
       <c r="F282" t="n">
         <v>0.8972723748974537</v>
       </c>
       <c r="G282" t="n">
-        <v>0.1024334354573768</v>
+        <v>0.10243343545747</v>
       </c>
     </row>
     <row r="283">
@@ -8716,13 +8716,13 @@
         <v>2</v>
       </c>
       <c r="E283" t="n">
-        <v>0.0001137963052829417</v>
+        <v>0.0001137963052832005</v>
       </c>
       <c r="F283" t="n">
-        <v>0.1015440008421414</v>
+        <v>0.1015440008422799</v>
       </c>
       <c r="G283" t="n">
-        <v>0.8983422028527384</v>
+        <v>0.8983422028523298</v>
       </c>
     </row>
     <row r="284">
@@ -8739,13 +8739,13 @@
         <v>1</v>
       </c>
       <c r="E284" t="n">
-        <v>0.0005256391079357874</v>
+        <v>0.0005256391079355484</v>
       </c>
       <c r="F284" t="n">
-        <v>0.8936860065408646</v>
+        <v>0.8936860065404582</v>
       </c>
       <c r="G284" t="n">
-        <v>0.105788354351408</v>
+        <v>0.1057883543515524</v>
       </c>
     </row>
     <row r="285">
@@ -8762,13 +8762,13 @@
         <v>2</v>
       </c>
       <c r="E285" t="n">
-        <v>0.0001566050641972694</v>
+        <v>0.0001566050641976255</v>
       </c>
       <c r="F285" t="n">
-        <v>0.1052267276618805</v>
+        <v>0.1052267276619762</v>
       </c>
       <c r="G285" t="n">
-        <v>0.8946166672740467</v>
+        <v>0.8946166672736399</v>
       </c>
     </row>
     <row r="286">
@@ -8785,13 +8785,13 @@
         <v>1</v>
       </c>
       <c r="E286" t="n">
-        <v>0.0002845149805195721</v>
+        <v>0.0002845149805194427</v>
       </c>
       <c r="F286" t="n">
         <v>0.8900194750292342</v>
       </c>
       <c r="G286" t="n">
-        <v>0.1096960099902157</v>
+        <v>0.1096960099903653</v>
       </c>
     </row>
     <row r="287">
@@ -8808,10 +8808,10 @@
         <v>2</v>
       </c>
       <c r="E287" t="n">
-        <v>0.0001081482497082315</v>
+        <v>0.0001081482497084282</v>
       </c>
       <c r="F287" t="n">
-        <v>0.1088791679564161</v>
+        <v>0.1088791679565152</v>
       </c>
       <c r="G287" t="n">
         <v>0.8910126837939228</v>
@@ -8831,13 +8831,13 @@
         <v>1</v>
       </c>
       <c r="E288" t="n">
-        <v>0.0003480722280709535</v>
+        <v>0.0003480722280704786</v>
       </c>
       <c r="F288" t="n">
-        <v>0.8858698623351553</v>
+        <v>0.8858698623347525</v>
       </c>
       <c r="G288" t="n">
-        <v>0.1137820654369045</v>
+        <v>0.113782065437008</v>
       </c>
     </row>
     <row r="289">
@@ -8854,13 +8854,13 @@
         <v>2</v>
       </c>
       <c r="E289" t="n">
-        <v>0.0002013094955874004</v>
+        <v>0.0002013094955875835</v>
       </c>
       <c r="F289" t="n">
-        <v>0.1128976231679766</v>
+        <v>0.1128976231681306</v>
       </c>
       <c r="G289" t="n">
-        <v>0.8869010673365668</v>
+        <v>0.8869010673361635</v>
       </c>
     </row>
     <row r="290">
@@ -8877,13 +8877,13 @@
         <v>1</v>
       </c>
       <c r="E290" t="n">
-        <v>0.0003514966983365184</v>
+        <v>0.0003514966983361987</v>
       </c>
       <c r="F290" t="n">
         <v>0.8819610511984646</v>
       </c>
       <c r="G290" t="n">
-        <v>0.1176874521031566</v>
+        <v>0.1176874521033707</v>
       </c>
     </row>
     <row r="291">
@@ -8900,13 +8900,13 @@
         <v>2</v>
       </c>
       <c r="E291" t="n">
-        <v>0.0001516379920630896</v>
+        <v>0.0001516379920633655</v>
       </c>
       <c r="F291" t="n">
-        <v>0.1168119636933658</v>
+        <v>0.1168119636936314</v>
       </c>
       <c r="G291" t="n">
-        <v>0.8830363983146097</v>
+        <v>0.8830363983142081</v>
       </c>
     </row>
     <row r="292">
@@ -8923,13 +8923,13 @@
         <v>1</v>
       </c>
       <c r="E292" t="n">
-        <v>0.0004704773560729393</v>
+        <v>0.0004704773560725114</v>
       </c>
       <c r="F292" t="n">
-        <v>0.8778916801781016</v>
+        <v>0.8778916801777024</v>
       </c>
       <c r="G292" t="n">
-        <v>0.1216378424659008</v>
+        <v>0.1216378424660114</v>
       </c>
     </row>
     <row r="293">
@@ -8946,10 +8946,10 @@
         <v>2</v>
       </c>
       <c r="E293" t="n">
-        <v>0.0002446250313459041</v>
+        <v>0.0002446250313461265</v>
       </c>
       <c r="F293" t="n">
-        <v>0.120819353316503</v>
+        <v>0.1208193533167227</v>
       </c>
       <c r="G293" t="n">
         <v>0.8789360216521336</v>
@@ -8969,13 +8969,13 @@
         <v>1</v>
       </c>
       <c r="E294" t="n">
-        <v>0.002959421623868548</v>
+        <v>0.002959421623865857</v>
       </c>
       <c r="F294" t="n">
-        <v>0.8717238603991854</v>
+        <v>0.8717238603987889</v>
       </c>
       <c r="G294" t="n">
-        <v>0.1253167179769084</v>
+        <v>0.1253167179771363</v>
       </c>
     </row>
     <row r="295">
@@ -8992,13 +8992,13 @@
         <v>2</v>
       </c>
       <c r="E295" t="n">
-        <v>0.0004648877669733258</v>
+        <v>0.0004648877669735372</v>
       </c>
       <c r="F295" t="n">
-        <v>0.1268608899960407</v>
+        <v>0.1268608899962715</v>
       </c>
       <c r="G295" t="n">
-        <v>0.8726742222371521</v>
+        <v>0.8726742222367552</v>
       </c>
     </row>
     <row r="296">
@@ -9015,13 +9015,13 @@
         <v>1</v>
       </c>
       <c r="E296" t="n">
-        <v>0.0007398149272676457</v>
+        <v>0.0007398149272662999</v>
       </c>
       <c r="F296" t="n">
-        <v>0.8668002604788209</v>
+        <v>0.8668002604784266</v>
       </c>
       <c r="G296" t="n">
-        <v>0.132459924594011</v>
+        <v>0.132459924594252</v>
       </c>
     </row>
     <row r="297">
@@ -9038,10 +9038,10 @@
         <v>2</v>
       </c>
       <c r="E297" t="n">
-        <v>0.0001168212817788655</v>
+        <v>0.0001168212817790249</v>
       </c>
       <c r="F297" t="n">
-        <v>0.1323397689296102</v>
+        <v>0.1323397689298509</v>
       </c>
       <c r="G297" t="n">
         <v>0.8675434097885424</v>
@@ -9061,13 +9061,13 @@
         <v>1</v>
       </c>
       <c r="E298" t="n">
-        <v>0.0004180402100189</v>
+        <v>0.0004180402100183297</v>
       </c>
       <c r="F298" t="n">
-        <v>0.8600181810463351</v>
+        <v>0.8600181810459441</v>
       </c>
       <c r="G298" t="n">
-        <v>0.139563778743588</v>
+        <v>0.1395637787438418</v>
       </c>
     </row>
     <row r="299">
@@ -9084,13 +9084,13 @@
         <v>2</v>
       </c>
       <c r="E299" t="n">
-        <v>0.0001118309346626525</v>
+        <v>0.0001118309346629068</v>
       </c>
       <c r="F299" t="n">
-        <v>0.1391018931219958</v>
+        <v>0.1391018931223121</v>
       </c>
       <c r="G299" t="n">
-        <v>0.8607862759431947</v>
+        <v>0.8607862759428032</v>
       </c>
     </row>
     <row r="300">
@@ -9107,13 +9107,13 @@
         <v>1</v>
       </c>
       <c r="E300" t="n">
-        <v>0.0004503819687575516</v>
+        <v>0.0004503819687573468</v>
       </c>
       <c r="F300" t="n">
         <v>0.8529821667385468</v>
       </c>
       <c r="G300" t="n">
-        <v>0.1465674512925413</v>
+        <v>0.1465674512928745</v>
       </c>
     </row>
     <row r="301">
@@ -9130,13 +9130,13 @@
         <v>2</v>
       </c>
       <c r="E301" t="n">
-        <v>0.0001506723427557364</v>
+        <v>0.0001506723427560105</v>
       </c>
       <c r="F301" t="n">
-        <v>0.146045702957388</v>
+        <v>0.1460457029575873</v>
       </c>
       <c r="G301" t="n">
-        <v>0.8538036247000621</v>
+        <v>0.8538036246996739</v>
       </c>
     </row>
     <row r="302">
@@ -9153,13 +9153,13 @@
         <v>1</v>
       </c>
       <c r="E302" t="n">
-        <v>0.0007559119989271085</v>
+        <v>0.0007559119989267647</v>
       </c>
       <c r="F302" t="n">
-        <v>0.8457074495023658</v>
+        <v>0.8457074495019812</v>
       </c>
       <c r="G302" t="n">
-        <v>0.1535366384988808</v>
+        <v>0.1535366384991601</v>
       </c>
     </row>
     <row r="303">
@@ -9176,13 +9176,13 @@
         <v>2</v>
       </c>
       <c r="E303" t="n">
-        <v>0.0001187810642607238</v>
+        <v>0.0001187810642608318</v>
       </c>
       <c r="F303" t="n">
-        <v>0.153529971473872</v>
+        <v>0.1535299714741513</v>
       </c>
       <c r="G303" t="n">
-        <v>0.8463512474620719</v>
+        <v>0.846351247461687</v>
       </c>
     </row>
     <row r="304">
@@ -9199,13 +9199,13 @@
         <v>1</v>
       </c>
       <c r="E304" t="n">
-        <v>0.0007694220300886679</v>
+        <v>0.0007694220300879681</v>
       </c>
       <c r="F304" t="n">
         <v>0.8356359281556573</v>
       </c>
       <c r="G304" t="n">
-        <v>0.1635946498141712</v>
+        <v>0.1635946498144688</v>
       </c>
     </row>
     <row r="305">
@@ -9222,13 +9222,13 @@
         <v>2</v>
       </c>
       <c r="E305" t="n">
-        <v>0.0001572486826723457</v>
+        <v>0.0001572486826725602</v>
       </c>
       <c r="F305" t="n">
-        <v>0.1635289768867451</v>
+        <v>0.1635289768869681</v>
       </c>
       <c r="G305" t="n">
-        <v>0.8363137744305467</v>
+        <v>0.8363137744301664</v>
       </c>
     </row>
     <row r="306">
@@ -9245,13 +9245,13 @@
         <v>1</v>
       </c>
       <c r="E306" t="n">
-        <v>0.001313082800905958</v>
+        <v>0.001313082800904764</v>
       </c>
       <c r="F306" t="n">
-        <v>0.8251079067161093</v>
+        <v>0.8251079067157342</v>
       </c>
       <c r="G306" t="n">
-        <v>0.1735790104831804</v>
+        <v>0.1735790104834172</v>
       </c>
     </row>
     <row r="307">
@@ -9268,13 +9268,13 @@
         <v>2</v>
       </c>
       <c r="E307" t="n">
-        <v>0.0003167702859847117</v>
+        <v>0.0003167702859849998</v>
       </c>
       <c r="F307" t="n">
-        <v>0.1740728108259519</v>
+        <v>0.1740728108261894</v>
       </c>
       <c r="G307" t="n">
-        <v>0.8256104188882533</v>
+        <v>0.8256104188878778</v>
       </c>
     </row>
     <row r="308">
@@ -9291,13 +9291,13 @@
         <v>1</v>
       </c>
       <c r="E308" t="n">
-        <v>0.0005824517600065159</v>
+        <v>0.0005824517600057213</v>
       </c>
       <c r="F308" t="n">
-        <v>0.816655572255397</v>
+        <v>0.8166555722550256</v>
       </c>
       <c r="G308" t="n">
-        <v>0.1827619759844502</v>
+        <v>0.1827619759847826</v>
       </c>
     </row>
     <row r="309">
@@ -9314,10 +9314,10 @@
         <v>2</v>
       </c>
       <c r="E309" t="n">
-        <v>0.0001067800463020593</v>
+        <v>0.0001067800463022535</v>
       </c>
       <c r="F309" t="n">
-        <v>0.182482374306791</v>
+        <v>0.1824823743070399</v>
       </c>
       <c r="G309" t="n">
         <v>0.8174108456467548</v>
@@ -9337,13 +9337,13 @@
         <v>1</v>
       </c>
       <c r="E310" t="n">
-        <v>0.0005427732912837106</v>
+        <v>0.0005427732912834638</v>
       </c>
       <c r="F310" t="n">
-        <v>0.807277284561835</v>
+        <v>0.8072772845614679</v>
       </c>
       <c r="G310" t="n">
-        <v>0.192179942146987</v>
+        <v>0.1921799421473366</v>
       </c>
     </row>
     <row r="311">
@@ -9360,13 +9360,13 @@
         <v>2</v>
       </c>
       <c r="E311" t="n">
-        <v>8.523644272958381e-05</v>
+        <v>8.523644272973885e-05</v>
       </c>
       <c r="F311" t="n">
-        <v>0.1919165624328436</v>
+        <v>0.1919165624331054</v>
       </c>
       <c r="G311" t="n">
-        <v>0.807998201124533</v>
+        <v>0.8079982011241656</v>
       </c>
     </row>
     <row r="312">
@@ -9383,13 +9383,13 @@
         <v>1</v>
       </c>
       <c r="E312" t="n">
-        <v>0.0006645002409767916</v>
+        <v>0.0006645002409761873</v>
       </c>
       <c r="F312" t="n">
-        <v>0.7973642936927609</v>
+        <v>0.7973642936923983</v>
       </c>
       <c r="G312" t="n">
-        <v>0.201971206066436</v>
+        <v>0.2019712060667115</v>
       </c>
     </row>
     <row r="313">
@@ -9406,13 +9406,13 @@
         <v>2</v>
       </c>
       <c r="E313" t="n">
-        <v>9.968511735868389e-05</v>
+        <v>9.968511735881989e-05</v>
       </c>
       <c r="F313" t="n">
-        <v>0.2017326334215784</v>
+        <v>0.2017326334218537</v>
       </c>
       <c r="G313" t="n">
-        <v>0.7981676814612179</v>
+        <v>0.7981676814608548</v>
       </c>
     </row>
     <row r="314">
@@ -9429,13 +9429,13 @@
         <v>1</v>
       </c>
       <c r="E314" t="n">
-        <v>0.0005413386389309968</v>
+        <v>0.0005413386389307507</v>
       </c>
       <c r="F314" t="n">
         <v>0.7884276073761219</v>
       </c>
       <c r="G314" t="n">
-        <v>0.2110310539847676</v>
+        <v>0.2110310539851515</v>
       </c>
     </row>
     <row r="315">
@@ -9452,13 +9452,13 @@
         <v>2</v>
       </c>
       <c r="E315" t="n">
-        <v>9.89367081871547e-05</v>
+        <v>9.893670818728967e-05</v>
       </c>
       <c r="F315" t="n">
-        <v>0.2106694614253305</v>
+        <v>0.2106694614257137</v>
       </c>
       <c r="G315" t="n">
-        <v>0.7892316018662718</v>
+        <v>0.7892316018659129</v>
       </c>
     </row>
     <row r="316">
@@ -9475,13 +9475,13 @@
         <v>1</v>
       </c>
       <c r="E316" t="n">
-        <v>0.001001327188574195</v>
+        <v>0.00100132718857374</v>
       </c>
       <c r="F316" t="n">
         <v>0.7783058198269339</v>
       </c>
       <c r="G316" t="n">
-        <v>0.2206928529842798</v>
+        <v>0.2206928529846813</v>
       </c>
     </row>
     <row r="317">
@@ -9498,13 +9498,13 @@
         <v>2</v>
       </c>
       <c r="E317" t="n">
-        <v>0.0001348106539767514</v>
+        <v>0.0001348106539769354</v>
       </c>
       <c r="F317" t="n">
-        <v>0.2207681032993332</v>
+        <v>0.2207681032996343</v>
       </c>
       <c r="G317" t="n">
-        <v>0.7790970860467124</v>
+        <v>0.7790970860463581</v>
       </c>
     </row>
     <row r="318">
@@ -9521,13 +9521,13 @@
         <v>1</v>
       </c>
       <c r="E318" t="n">
-        <v>0.0007999042908023211</v>
+        <v>0.0007999042908015936</v>
       </c>
       <c r="F318" t="n">
-        <v>0.7676212029894574</v>
+        <v>0.7676212029891083</v>
       </c>
       <c r="G318" t="n">
-        <v>0.2315788927195331</v>
+        <v>0.2315788927199543</v>
       </c>
     </row>
     <row r="319">
@@ -9544,13 +9544,13 @@
         <v>2</v>
       </c>
       <c r="E319" t="n">
-        <v>0.0001191506530632152</v>
+        <v>0.0001191506530633236</v>
       </c>
       <c r="F319" t="n">
-        <v>0.2314420454669586</v>
+        <v>0.2314420454673796</v>
       </c>
       <c r="G319" t="n">
-        <v>0.7684388038798464</v>
+        <v>0.7684388038794969</v>
       </c>
     </row>
     <row r="320">
@@ -9567,13 +9567,13 @@
         <v>1</v>
       </c>
       <c r="E320" t="n">
-        <v>0.001046202351052065</v>
+        <v>0.001046202351050637</v>
       </c>
       <c r="F320" t="n">
-        <v>0.7570627736304294</v>
+        <v>0.7570627736297408</v>
       </c>
       <c r="G320" t="n">
-        <v>0.2418910240186811</v>
+        <v>0.2418910240191211</v>
       </c>
     </row>
     <row r="321">
@@ -9590,13 +9590,13 @@
         <v>2</v>
       </c>
       <c r="E321" t="n">
-        <v>0.0001159111185183377</v>
+        <v>0.0001159111185184431</v>
       </c>
       <c r="F321" t="n">
-        <v>0.2421252592422542</v>
+        <v>0.2421252592425845</v>
       </c>
       <c r="G321" t="n">
-        <v>0.7577588296392084</v>
+        <v>0.7577588296388638</v>
       </c>
     </row>
     <row r="322">
@@ -9613,13 +9613,13 @@
         <v>1</v>
       </c>
       <c r="E322" t="n">
-        <v>0.001006683138381982</v>
+        <v>0.001006683138381066</v>
       </c>
       <c r="F322" t="n">
-        <v>0.7443185684931124</v>
+        <v>0.7443185684927739</v>
       </c>
       <c r="G322" t="n">
-        <v>0.2546747483683219</v>
+        <v>0.2546747483687851</v>
       </c>
     </row>
     <row r="323">
@@ -9636,13 +9636,13 @@
         <v>2</v>
       </c>
       <c r="E323" t="n">
-        <v>0.0001014961112338884</v>
+        <v>0.0001014961112339807</v>
       </c>
       <c r="F323" t="n">
-        <v>0.254924860503027</v>
+        <v>0.2549248605034907</v>
       </c>
       <c r="G323" t="n">
-        <v>0.7449736433857634</v>
+        <v>0.7449736433854247</v>
       </c>
     </row>
     <row r="324">
@@ -9659,13 +9659,13 @@
         <v>1</v>
       </c>
       <c r="E324" t="n">
-        <v>0.000816007118816912</v>
+        <v>0.0008160071188161699</v>
       </c>
       <c r="F324" t="n">
-        <v>0.7308977879277336</v>
+        <v>0.7308977879274012</v>
       </c>
       <c r="G324" t="n">
-        <v>0.268286204953366</v>
+        <v>0.268286204953854</v>
       </c>
     </row>
     <row r="325">
@@ -9682,13 +9682,13 @@
         <v>2</v>
       </c>
       <c r="E325" t="n">
-        <v>0.0002941659223418716</v>
+        <v>0.0002941659223422729</v>
       </c>
       <c r="F325" t="n">
-        <v>0.268142925779055</v>
+        <v>0.2681429257795428</v>
       </c>
       <c r="G325" t="n">
-        <v>0.7315629082984084</v>
+        <v>0.7315629082980757</v>
       </c>
     </row>
     <row r="326">
@@ -9705,13 +9705,13 @@
         <v>1</v>
       </c>
       <c r="E326" t="n">
-        <v>0.0007757877262189773</v>
+        <v>0.0007757877262186245</v>
       </c>
       <c r="F326" t="n">
-        <v>0.7192542787779017</v>
+        <v>0.7192542787772476</v>
       </c>
       <c r="G326" t="n">
-        <v>0.2799699334958528</v>
+        <v>0.2799699334966167</v>
       </c>
     </row>
     <row r="327">
@@ -9728,13 +9728,13 @@
         <v>2</v>
       </c>
       <c r="E327" t="n">
-        <v>0.0001730079206902453</v>
+        <v>0.0001730079206907174</v>
       </c>
       <c r="F327" t="n">
-        <v>0.2797225879047829</v>
+        <v>0.2797225879054189</v>
       </c>
       <c r="G327" t="n">
-        <v>0.7201044041744857</v>
+        <v>0.7201044041738308</v>
       </c>
     </row>
     <row r="328">
@@ -9751,13 +9751,13 @@
         <v>1</v>
       </c>
       <c r="E328" t="n">
-        <v>0.0009354379215175262</v>
+        <v>0.0009354379215166755</v>
       </c>
       <c r="F328" t="n">
-        <v>0.7083408500134702</v>
+        <v>0.7083408500131481</v>
       </c>
       <c r="G328" t="n">
-        <v>0.2907237120647955</v>
+        <v>0.2907237120653244</v>
       </c>
     </row>
     <row r="329">
@@ -9774,13 +9774,13 @@
         <v>2</v>
       </c>
       <c r="E329" t="n">
-        <v>0.0002597118596282599</v>
+        <v>0.0002597118596284961</v>
       </c>
       <c r="F329" t="n">
-        <v>0.2904735889708193</v>
+        <v>0.2904735889714798</v>
       </c>
       <c r="G329" t="n">
-        <v>0.7092666991695127</v>
+        <v>0.7092666991688675</v>
       </c>
     </row>
     <row r="330">
@@ -9797,13 +9797,13 @@
         <v>1</v>
       </c>
       <c r="E330" t="n">
-        <v>0.003984337408496192</v>
+        <v>0.003984337408492568</v>
       </c>
       <c r="F330" t="n">
-        <v>0.6952193926123803</v>
+        <v>0.695219392611748</v>
       </c>
       <c r="G330" t="n">
-        <v>0.3007962699791354</v>
+        <v>0.3007962699796825</v>
       </c>
     </row>
     <row r="331">
@@ -9820,13 +9820,13 @@
         <v>2</v>
       </c>
       <c r="E331" t="n">
-        <v>0.0002932115004863189</v>
+        <v>0.0002932115004864522</v>
       </c>
       <c r="F331" t="n">
-        <v>0.3036553430950516</v>
+        <v>0.3036553430956039</v>
       </c>
       <c r="G331" t="n">
-        <v>0.6960514454046572</v>
+        <v>0.6960514454040242</v>
       </c>
     </row>
     <row r="332">
@@ -9843,13 +9843,13 @@
         <v>1</v>
       </c>
       <c r="E332" t="n">
-        <v>0.0007175524309150233</v>
+        <v>0.0007175524309137181</v>
       </c>
       <c r="F332" t="n">
-        <v>0.6837281419862173</v>
+        <v>0.6837281419855954</v>
       </c>
       <c r="G332" t="n">
-        <v>0.3155543055827494</v>
+        <v>0.3155543055833234</v>
       </c>
     </row>
     <row r="333">
@@ -9866,13 +9866,13 @@
         <v>2</v>
       </c>
       <c r="E333" t="n">
-        <v>0.000122555425457735</v>
+        <v>0.0001225554254578465</v>
       </c>
       <c r="F333" t="n">
-        <v>0.3152608275785448</v>
+        <v>0.3152608275792616</v>
       </c>
       <c r="G333" t="n">
-        <v>0.6846166169961055</v>
+        <v>0.6846166169954829</v>
       </c>
     </row>
     <row r="334">
@@ -9889,13 +9889,13 @@
         <v>1</v>
       </c>
       <c r="E334" t="n">
-        <v>0.0009558397647448528</v>
+        <v>0.0009558397647435489</v>
       </c>
       <c r="F334" t="n">
-        <v>0.6731338904812835</v>
+        <v>0.6731338904803652</v>
       </c>
       <c r="G334" t="n">
-        <v>0.3259102697540743</v>
+        <v>0.3259102697546672</v>
       </c>
     </row>
     <row r="335">
@@ -9912,13 +9912,13 @@
         <v>2</v>
       </c>
       <c r="E335" t="n">
-        <v>0.00024242293336032</v>
+        <v>0.0002424229333606507</v>
       </c>
       <c r="F335" t="n">
-        <v>0.3256007302754669</v>
+        <v>0.3256007302760592</v>
       </c>
       <c r="G335" t="n">
-        <v>0.6741568467910736</v>
+        <v>0.6741568467904604</v>
       </c>
     </row>
     <row r="336">
@@ -9935,13 +9935,13 @@
         <v>1</v>
       </c>
       <c r="E336" t="n">
-        <v>0.0004932545222843043</v>
+        <v>0.0004932545222838556</v>
       </c>
       <c r="F336" t="n">
-        <v>0.6659823592145783</v>
+        <v>0.6659823592136697</v>
       </c>
       <c r="G336" t="n">
-        <v>0.3335243862632956</v>
+        <v>0.3335243862640539</v>
       </c>
     </row>
     <row r="337">
@@ -9958,13 +9958,13 @@
         <v>2</v>
       </c>
       <c r="E337" t="n">
-        <v>0.0001357737054868319</v>
+        <v>0.0001357737054871406</v>
       </c>
       <c r="F337" t="n">
-        <v>0.3325290541337129</v>
+        <v>0.3325290541343178</v>
       </c>
       <c r="G337" t="n">
-        <v>0.6673351721606661</v>
+        <v>0.6673351721603626</v>
       </c>
     </row>
     <row r="338">
@@ -9981,13 +9981,13 @@
         <v>1</v>
       </c>
       <c r="E338" t="n">
-        <v>0.0004820517082669129</v>
+        <v>0.0004820517082666937</v>
       </c>
       <c r="F338" t="n">
-        <v>0.6587373567805235</v>
+        <v>0.6587373567799243</v>
       </c>
       <c r="G338" t="n">
-        <v>0.3407805915113502</v>
+        <v>0.3407805915118151</v>
       </c>
     </row>
     <row r="339">
@@ -10004,13 +10004,13 @@
         <v>2</v>
       </c>
       <c r="E339" t="n">
-        <v>0.0001592798715115528</v>
+        <v>0.0001592798715117701</v>
       </c>
       <c r="F339" t="n">
-        <v>0.3398311164829309</v>
+        <v>0.33983111648324</v>
       </c>
       <c r="G339" t="n">
-        <v>0.6600096036456308</v>
+        <v>0.6600096036450305</v>
       </c>
     </row>
     <row r="340">
@@ -10027,13 +10027,13 @@
         <v>1</v>
       </c>
       <c r="E340" t="n">
-        <v>0.001069659139242287</v>
+        <v>0.001069659139241314</v>
       </c>
       <c r="F340" t="n">
-        <v>0.6514513089961748</v>
+        <v>0.6514513089955822</v>
       </c>
       <c r="G340" t="n">
-        <v>0.3474790318645181</v>
+        <v>0.3474790318651502</v>
       </c>
     </row>
     <row r="341">
@@ -10050,13 +10050,13 @@
         <v>2</v>
       </c>
       <c r="E341" t="n">
-        <v>0.0002096142037280794</v>
+        <v>0.0002096142037283654</v>
       </c>
       <c r="F341" t="n">
-        <v>0.3469290158381487</v>
+        <v>0.346929015838622</v>
       </c>
       <c r="G341" t="n">
-        <v>0.6528613699580806</v>
+        <v>0.6528613699574869</v>
       </c>
     </row>
     <row r="342">
@@ -10073,13 +10073,13 @@
         <v>1</v>
       </c>
       <c r="E342" t="n">
-        <v>0.0004775483189126714</v>
+        <v>0.0004775483189118027</v>
       </c>
       <c r="F342" t="n">
-        <v>0.6454917496720836</v>
+        <v>0.6454917496714965</v>
       </c>
       <c r="G342" t="n">
-        <v>0.3540307020090249</v>
+        <v>0.3540307020096689</v>
       </c>
     </row>
     <row r="343">
@@ -10096,13 +10096,13 @@
         <v>2</v>
       </c>
       <c r="E343" t="n">
-        <v>0.0001315362133747491</v>
+        <v>0.0001315362133750481</v>
       </c>
       <c r="F343" t="n">
-        <v>0.3529961364820647</v>
+        <v>0.3529961364825462</v>
       </c>
       <c r="G343" t="n">
-        <v>0.6468723273044402</v>
+        <v>0.6468723273038519</v>
       </c>
     </row>
     <row r="344">
@@ -10119,13 +10119,13 @@
         <v>1</v>
       </c>
       <c r="E344" t="n">
-        <v>0.0003914186711964721</v>
+        <v>0.0003914186711962941</v>
       </c>
       <c r="F344" t="n">
-        <v>0.6394348822133039</v>
+        <v>0.6394348822127224</v>
       </c>
       <c r="G344" t="n">
-        <v>0.3601736991153164</v>
+        <v>0.3601736991161353</v>
       </c>
     </row>
     <row r="345">
@@ -10142,13 +10142,13 @@
         <v>2</v>
       </c>
       <c r="E345" t="n">
-        <v>0.000126721160066307</v>
+        <v>0.0001267211600666527</v>
       </c>
       <c r="F345" t="n">
-        <v>0.3589255119244608</v>
+        <v>0.3589255119249504</v>
       </c>
       <c r="G345" t="n">
-        <v>0.6409477669154771</v>
+        <v>0.6409477669148941</v>
       </c>
     </row>
     <row r="346">
@@ -10165,13 +10165,13 @@
         <v>1</v>
       </c>
       <c r="E346" t="n">
-        <v>0.0005348379086191756</v>
+        <v>0.0005348379086189323</v>
       </c>
       <c r="F346" t="n">
-        <v>0.6333053184865276</v>
+        <v>0.6333053184862396</v>
       </c>
       <c r="G346" t="n">
-        <v>0.3661598436047017</v>
+        <v>0.3661598436053677</v>
       </c>
     </row>
     <row r="347">
@@ -10188,13 +10188,13 @@
         <v>2</v>
       </c>
       <c r="E347" t="n">
-        <v>0.0001731787747150673</v>
+        <v>0.0001731787747153824</v>
       </c>
       <c r="F347" t="n">
-        <v>0.3650453542624031</v>
+        <v>0.3650453542630671</v>
       </c>
       <c r="G347" t="n">
-        <v>0.6347814669630863</v>
+        <v>0.6347814669622204</v>
       </c>
     </row>
     <row r="348">
@@ -10211,13 +10211,13 @@
         <v>1</v>
       </c>
       <c r="E348" t="n">
-        <v>0.0004942538909715193</v>
+        <v>0.000494253890970845</v>
       </c>
       <c r="F348" t="n">
-        <v>0.6267044353447536</v>
+        <v>0.6267044353438986</v>
       </c>
       <c r="G348" t="n">
-        <v>0.3728013107645016</v>
+        <v>0.3728013107651797</v>
       </c>
     </row>
     <row r="349">
@@ -10234,13 +10234,13 @@
         <v>2</v>
       </c>
       <c r="E349" t="n">
-        <v>0.0001788859611134449</v>
+        <v>0.0001788859611138517</v>
       </c>
       <c r="F349" t="n">
-        <v>0.3716022250570226</v>
+        <v>0.3716022250575295</v>
       </c>
       <c r="G349" t="n">
-        <v>0.628218888982083</v>
+        <v>0.6282188889815116</v>
       </c>
     </row>
     <row r="350">
@@ -10257,13 +10257,13 @@
         <v>1</v>
       </c>
       <c r="E350" t="n">
-        <v>0.000854188387839589</v>
+        <v>0.0008541883878384237</v>
       </c>
       <c r="F350" t="n">
-        <v>0.6198934022568083</v>
+        <v>0.6198934022562446</v>
       </c>
       <c r="G350" t="n">
-        <v>0.3792524093553612</v>
+        <v>0.3792524093558786</v>
       </c>
     </row>
     <row r="351">
@@ -10280,13 +10280,13 @@
         <v>2</v>
       </c>
       <c r="E351" t="n">
-        <v>0.0002125873092696663</v>
+        <v>0.000212587309270053</v>
       </c>
       <c r="F351" t="n">
-        <v>0.3784484029271639</v>
+        <v>0.3784484029276802</v>
       </c>
       <c r="G351" t="n">
-        <v>0.6213390097635916</v>
+        <v>0.6213390097630265</v>
       </c>
     </row>
     <row r="352">
@@ -10303,13 +10303,13 @@
         <v>1</v>
       </c>
       <c r="E352" t="n">
-        <v>0.0005193827587387993</v>
+        <v>0.0005193827587380908</v>
       </c>
       <c r="F352" t="n">
-        <v>0.6144961056536248</v>
+        <v>0.6144961056530659</v>
       </c>
       <c r="G352" t="n">
-        <v>0.3849845115878109</v>
+        <v>0.3849845115883361</v>
       </c>
     </row>
     <row r="353">
@@ -10326,13 +10326,13 @@
         <v>2</v>
       </c>
       <c r="E353" t="n">
-        <v>0.0002097935505950785</v>
+        <v>0.0002097935505955556</v>
       </c>
       <c r="F353" t="n">
-        <v>0.3836646113860134</v>
+        <v>0.3836646113868858</v>
       </c>
       <c r="G353" t="n">
-        <v>0.6161255950632351</v>
+        <v>0.6161255950626747</v>
       </c>
     </row>
     <row r="354">
@@ -10349,13 +10349,13 @@
         <v>1</v>
       </c>
       <c r="E354" t="n">
-        <v>0.0005156496349312002</v>
+        <v>0.0005156496349304968</v>
       </c>
       <c r="F354" t="n">
-        <v>0.6087591840756288</v>
+        <v>0.6087591840747982</v>
       </c>
       <c r="G354" t="n">
-        <v>0.3907251662895757</v>
+        <v>0.3907251662902864</v>
       </c>
     </row>
     <row r="355">
@@ -10372,13 +10372,13 @@
         <v>2</v>
       </c>
       <c r="E355" t="n">
-        <v>0.000301081810140224</v>
+        <v>0.0003010818101407717</v>
       </c>
       <c r="F355" t="n">
-        <v>0.3894768448096994</v>
+        <v>0.3894768448102306</v>
       </c>
       <c r="G355" t="n">
-        <v>0.6102220733801106</v>
+        <v>0.6102220733795556</v>
       </c>
     </row>
     <row r="356">
@@ -10395,13 +10395,13 @@
         <v>1</v>
       </c>
       <c r="E356" t="n">
-        <v>0.0006213342060914916</v>
+        <v>0.0006213342060909265</v>
       </c>
       <c r="F356" t="n">
-        <v>0.6024864378255916</v>
+        <v>0.6024864378253176</v>
       </c>
       <c r="G356" t="n">
-        <v>0.3968922279680895</v>
+        <v>0.3968922279688115</v>
       </c>
     </row>
     <row r="357">
@@ -10418,13 +10418,13 @@
         <v>2</v>
       </c>
       <c r="E357" t="n">
-        <v>0.000185949319004791</v>
+        <v>0.0001859493190051293</v>
       </c>
       <c r="F357" t="n">
-        <v>0.3958479522989383</v>
+        <v>0.3958479522996584</v>
       </c>
       <c r="G357" t="n">
-        <v>0.6039660983819485</v>
+        <v>0.6039660983813993</v>
       </c>
     </row>
     <row r="358">
@@ -10441,13 +10441,13 @@
         <v>1</v>
       </c>
       <c r="E358" t="n">
-        <v>0.0008222837889200372</v>
+        <v>0.0008222837889192893</v>
       </c>
       <c r="F358" t="n">
-        <v>0.5951695436054858</v>
+        <v>0.5951695436049446</v>
       </c>
       <c r="G358" t="n">
-        <v>0.4040081726054664</v>
+        <v>0.4040081726062013</v>
       </c>
     </row>
     <row r="359">
@@ -10464,13 +10464,13 @@
         <v>2</v>
       </c>
       <c r="E359" t="n">
-        <v>0.0001683965233184989</v>
+        <v>0.0001683965233186521</v>
       </c>
       <c r="F359" t="n">
-        <v>0.4035429405033372</v>
+        <v>0.4035429405038877</v>
       </c>
       <c r="G359" t="n">
-        <v>0.5962886629734547</v>
+        <v>0.5962886629726412</v>
       </c>
     </row>
     <row r="360">
@@ -10487,13 +10487,13 @@
         <v>1</v>
       </c>
       <c r="E360" t="n">
-        <v>0.000612651911989677</v>
+        <v>0.0006126519119885625</v>
       </c>
       <c r="F360" t="n">
-        <v>0.5872215573216917</v>
+        <v>0.5872215573208905</v>
       </c>
       <c r="G360" t="n">
-        <v>0.4121657907665451</v>
+        <v>0.4121657907671074</v>
       </c>
     </row>
     <row r="361">
@@ -10510,13 +10510,13 @@
         <v>2</v>
       </c>
       <c r="E361" t="n">
-        <v>0.0001401174035753084</v>
+        <v>0.0001401174035754996</v>
       </c>
       <c r="F361" t="n">
-        <v>0.4113179375989311</v>
+        <v>0.4113179375994923</v>
       </c>
       <c r="G361" t="n">
-        <v>0.588541944997542</v>
+        <v>0.5885419449970067</v>
       </c>
     </row>
     <row r="362">
@@ -10533,13 +10533,13 @@
         <v>1</v>
       </c>
       <c r="E362" t="n">
-        <v>0.0006063419937549058</v>
+        <v>0.0006063419937540786</v>
       </c>
       <c r="F362" t="n">
-        <v>0.5794470827393082</v>
+        <v>0.5794470827387812</v>
       </c>
       <c r="G362" t="n">
-        <v>0.4199465752668268</v>
+        <v>0.4199465752673996</v>
       </c>
     </row>
     <row r="363">
@@ -10556,13 +10556,13 @@
         <v>2</v>
       </c>
       <c r="E363" t="n">
-        <v>0.0001333548314834389</v>
+        <v>0.0001333548314836815</v>
       </c>
       <c r="F363" t="n">
-        <v>0.4191343828272999</v>
+        <v>0.4191343828278716</v>
       </c>
       <c r="G363" t="n">
-        <v>0.5807322623410429</v>
+        <v>0.5807322623405147</v>
       </c>
     </row>
     <row r="364">
@@ -10579,13 +10579,13 @@
         <v>1</v>
       </c>
       <c r="E364" t="n">
-        <v>0.0004871787571935971</v>
+        <v>0.0004871787571933755</v>
       </c>
       <c r="F364" t="n">
-        <v>0.571593171486363</v>
+        <v>0.5715931714858432</v>
       </c>
       <c r="G364" t="n">
-        <v>0.4279196497563162</v>
+        <v>0.4279196497569</v>
       </c>
     </row>
     <row r="365">
@@ -10602,13 +10602,13 @@
         <v>2</v>
       </c>
       <c r="E365" t="n">
-        <v>0.0001377974549540406</v>
+        <v>0.0001377974549543539</v>
       </c>
       <c r="F365" t="n">
-        <v>0.4268897465933297</v>
+        <v>0.426889746593912</v>
       </c>
       <c r="G365" t="n">
-        <v>0.5729724559516778</v>
+        <v>0.5729724559511566</v>
       </c>
     </row>
     <row r="366">
@@ -10625,13 +10625,13 @@
         <v>1</v>
       </c>
       <c r="E366" t="n">
-        <v>0.0005270573965835847</v>
+        <v>0.0005270573965828657</v>
       </c>
       <c r="F366" t="n">
-        <v>0.5639166453544201</v>
+        <v>0.5639166453539073</v>
       </c>
       <c r="G366" t="n">
-        <v>0.4355562972489178</v>
+        <v>0.4355562972495119</v>
       </c>
     </row>
     <row r="367">
@@ -10648,13 +10648,13 @@
         <v>2</v>
       </c>
       <c r="E367" t="n">
-        <v>0.0001983483617618638</v>
+        <v>0.0001983483617623148</v>
       </c>
       <c r="F367" t="n">
-        <v>0.4344713228548686</v>
+        <v>0.4344713228556589</v>
       </c>
       <c r="G367" t="n">
-        <v>0.5653303287832282</v>
+        <v>0.5653303287827141</v>
       </c>
     </row>
     <row r="368">
@@ -10671,13 +10671,13 @@
         <v>1</v>
       </c>
       <c r="E368" t="n">
-        <v>0.0009422576824648446</v>
+        <v>0.0009422576824639876</v>
       </c>
       <c r="F368" t="n">
-        <v>0.5561046725892733</v>
+        <v>0.5561046725885147</v>
       </c>
       <c r="G368" t="n">
-        <v>0.4429530697284837</v>
+        <v>0.4429530697288865</v>
       </c>
     </row>
     <row r="369">
@@ -10694,13 +10694,13 @@
         <v>2</v>
       </c>
       <c r="E369" t="n">
-        <v>0.0001418100603449478</v>
+        <v>0.0001418100603453347</v>
       </c>
       <c r="F369" t="n">
-        <v>0.4426574070470657</v>
+        <v>0.4426574070476696</v>
       </c>
       <c r="G369" t="n">
-        <v>0.557200782892424</v>
+        <v>0.5572007828921707</v>
       </c>
     </row>
     <row r="370">
@@ -10717,13 +10717,13 @@
         <v>1</v>
       </c>
       <c r="E370" t="n">
-        <v>0.001002609602489647</v>
+        <v>0.00100260960248828</v>
       </c>
       <c r="F370" t="n">
-        <v>0.5452859886108317</v>
+        <v>0.5452859886100878</v>
       </c>
       <c r="G370" t="n">
-        <v>0.4537114017868246</v>
+        <v>0.4537114017872372</v>
       </c>
     </row>
     <row r="371">
@@ -10740,13 +10740,13 @@
         <v>2</v>
       </c>
       <c r="E371" t="n">
-        <v>0.0001944938177938651</v>
+        <v>0.0001944938177942189</v>
       </c>
       <c r="F371" t="n">
-        <v>0.4534532905908775</v>
+        <v>0.4534532905912899</v>
       </c>
       <c r="G371" t="n">
-        <v>0.5463522155913131</v>
+        <v>0.5463522155910646</v>
       </c>
     </row>
     <row r="372">
@@ -10763,13 +10763,13 @@
         <v>1</v>
       </c>
       <c r="E372" t="n">
-        <v>0.0006781130078062708</v>
+        <v>0.0006781130078053457</v>
       </c>
       <c r="F372" t="n">
-        <v>0.5368281493953888</v>
+        <v>0.5368281493949006</v>
       </c>
       <c r="G372" t="n">
-        <v>0.4624937375970267</v>
+        <v>0.4624937375972369</v>
       </c>
     </row>
     <row r="373">
@@ -10786,13 +10786,13 @@
         <v>2</v>
       </c>
       <c r="E373" t="n">
-        <v>0.0001350424925883273</v>
+        <v>0.0001350424925886958</v>
       </c>
       <c r="F373" t="n">
-        <v>0.4617069318260831</v>
+        <v>0.4617069318265031</v>
       </c>
       <c r="G373" t="n">
-        <v>0.5381580256815158</v>
+        <v>0.5381580256810263</v>
       </c>
     </row>
     <row r="374">
@@ -10809,13 +10809,13 @@
         <v>1</v>
       </c>
       <c r="E374" t="n">
-        <v>0.0005718919395043367</v>
+        <v>0.0005718919395035565</v>
       </c>
       <c r="F374" t="n">
-        <v>0.5290663464539426</v>
+        <v>0.5290663464532208</v>
       </c>
       <c r="G374" t="n">
-        <v>0.4703617616067639</v>
+        <v>0.4703617616071917</v>
       </c>
     </row>
     <row r="375">
@@ -10832,13 +10832,13 @@
         <v>2</v>
       </c>
       <c r="E375" t="n">
-        <v>0.0001172626480826931</v>
+        <v>0.0001172626480829064</v>
       </c>
       <c r="F375" t="n">
-        <v>0.4695204324703593</v>
+        <v>0.4695204324707863</v>
       </c>
       <c r="G375" t="n">
-        <v>0.5303623048816459</v>
+        <v>0.5303623048809224</v>
       </c>
     </row>
     <row r="376">
@@ -10855,13 +10855,13 @@
         <v>1</v>
       </c>
       <c r="E376" t="n">
-        <v>0.0005773445450477958</v>
+        <v>0.0005773445450470082</v>
       </c>
       <c r="F376" t="n">
-        <v>0.5207481502826034</v>
+        <v>0.5207481502821297</v>
       </c>
       <c r="G376" t="n">
-        <v>0.4786745051723634</v>
+        <v>0.4786745051730164</v>
       </c>
     </row>
     <row r="377">
@@ -10878,13 +10878,13 @@
         <v>2</v>
       </c>
       <c r="E377" t="n">
-        <v>0.0001375499037501828</v>
+        <v>0.0001375499037504955</v>
       </c>
       <c r="F377" t="n">
-        <v>0.47785963789695</v>
+        <v>0.4778596378973846</v>
       </c>
       <c r="G377" t="n">
-        <v>0.5220028121995195</v>
+        <v>0.5220028121988074</v>
       </c>
     </row>
     <row r="378">
@@ -10901,13 +10901,13 @@
         <v>1</v>
       </c>
       <c r="E378" t="n">
-        <v>0.0008458856896303019</v>
+        <v>0.0008458856896291479</v>
       </c>
       <c r="F378" t="n">
-        <v>0.5117404088517018</v>
+        <v>0.5117404088510036</v>
       </c>
       <c r="G378" t="n">
-        <v>0.4874137054587467</v>
+        <v>0.48741370545919</v>
       </c>
     </row>
     <row r="379">
@@ -10924,13 +10924,13 @@
         <v>2</v>
       </c>
       <c r="E379" t="n">
-        <v>0.0001422460871079931</v>
+        <v>0.0001422460871081872</v>
       </c>
       <c r="F379" t="n">
-        <v>0.4869719716603501</v>
+        <v>0.486971971660793</v>
       </c>
       <c r="G379" t="n">
-        <v>0.5128857822523556</v>
+        <v>0.5128857822521224</v>
       </c>
     </row>
     <row r="380">
@@ -10947,13 +10947,13 @@
         <v>1</v>
       </c>
       <c r="E380" t="n">
-        <v>0.0009826704496666055</v>
+        <v>0.0009826704496657117</v>
       </c>
       <c r="F380" t="n">
-        <v>0.5013047679155452</v>
+        <v>0.5013047679150893</v>
       </c>
       <c r="G380" t="n">
-        <v>0.4977125616349303</v>
+        <v>0.4977125616351566</v>
       </c>
     </row>
     <row r="381">
@@ -10970,13 +10970,13 @@
         <v>2</v>
       </c>
       <c r="E381" t="n">
-        <v>0.0001274558030031308</v>
+        <v>0.0001274558030034206</v>
       </c>
       <c r="F381" t="n">
-        <v>0.4975586546118586</v>
+        <v>0.4975586546120848</v>
       </c>
       <c r="G381" t="n">
-        <v>0.5023138895852037</v>
+        <v>0.5023138895847469</v>
       </c>
     </row>
     <row r="382">
@@ -10993,13 +10993,13 @@
         <v>1</v>
       </c>
       <c r="E382" t="n">
-        <v>0.0006701529437555005</v>
+        <v>0.0006701529437551958</v>
       </c>
       <c r="F382" t="n">
-        <v>0.4903571101805697</v>
+        <v>0.4903571101803467</v>
       </c>
       <c r="G382" t="n">
-        <v>0.5089727368756605</v>
+        <v>0.5089727368761234</v>
       </c>
     </row>
     <row r="383">
@@ -11016,13 +11016,13 @@
         <v>2</v>
       </c>
       <c r="E383" t="n">
-        <v>0.0001238898946246524</v>
+        <v>0.0001238898946249341</v>
       </c>
       <c r="F383" t="n">
-        <v>0.5084749733938985</v>
+        <v>0.5084749733941296</v>
       </c>
       <c r="G383" t="n">
-        <v>0.4914011367116732</v>
+        <v>0.4914011367112263</v>
       </c>
     </row>
     <row r="384">
@@ -11039,13 +11039,13 @@
         <v>1</v>
       </c>
       <c r="E384" t="n">
-        <v>0.000570803462492753</v>
+        <v>0.0005708034624922339</v>
       </c>
       <c r="F384" t="n">
-        <v>0.4802956095080845</v>
+        <v>0.4802956095076477</v>
       </c>
       <c r="G384" t="n">
-        <v>0.5191335870292701</v>
+        <v>0.5191335870297423</v>
       </c>
     </row>
     <row r="385">
@@ -11062,13 +11062,13 @@
         <v>2</v>
       </c>
       <c r="E385" t="n">
-        <v>0.0001565497305162164</v>
+        <v>0.0001565497305165012</v>
       </c>
       <c r="F385" t="n">
-        <v>0.5184133069490077</v>
+        <v>0.5184133069492435</v>
       </c>
       <c r="G385" t="n">
-        <v>0.481430143320563</v>
+        <v>0.4814301433201251</v>
       </c>
     </row>
     <row r="386">
@@ -11085,13 +11085,13 @@
         <v>1</v>
       </c>
       <c r="E386" t="n">
-        <v>0.001380756148983754</v>
+        <v>0.001380756148982499</v>
       </c>
       <c r="F386" t="n">
-        <v>0.4703881695451076</v>
+        <v>0.4703881695446798</v>
       </c>
       <c r="G386" t="n">
-        <v>0.5282310743060811</v>
+        <v>0.5282310743063213</v>
       </c>
     </row>
     <row r="387">
@@ -11108,13 +11108,13 @@
         <v>2</v>
       </c>
       <c r="E387" t="n">
-        <v>0.0002848689086263441</v>
+        <v>0.0002848689086267327</v>
       </c>
       <c r="F387" t="n">
-        <v>0.5281994694930223</v>
+        <v>0.5281994694935027</v>
       </c>
       <c r="G387" t="n">
-        <v>0.4715156615982994</v>
+        <v>0.4715156615978706</v>
       </c>
     </row>
     <row r="388">
@@ -11131,13 +11131,13 @@
         <v>1</v>
       </c>
       <c r="E388" t="n">
-        <v>0.0006492936059556099</v>
+        <v>0.0006492936059550195</v>
       </c>
       <c r="F388" t="n">
-        <v>0.4604474031282844</v>
+        <v>0.460447403128075</v>
       </c>
       <c r="G388" t="n">
-        <v>0.5389033032656458</v>
+        <v>0.538903303266136</v>
       </c>
     </row>
     <row r="389">
@@ -11154,13 +11154,13 @@
         <v>2</v>
       </c>
       <c r="E389" t="n">
-        <v>0.0001587010354943062</v>
+        <v>0.0001587010354945227</v>
       </c>
       <c r="F389" t="n">
-        <v>0.5383178248145071</v>
+        <v>0.5383178248147518</v>
       </c>
       <c r="G389" t="n">
-        <v>0.4615234741502109</v>
+        <v>0.4615234741497912</v>
       </c>
     </row>
     <row r="390">
@@ -11177,13 +11177,13 @@
         <v>1</v>
       </c>
       <c r="E390" t="n">
-        <v>0.001474587775414844</v>
+        <v>0.001474587775412832</v>
       </c>
       <c r="F390" t="n">
-        <v>0.4490148928923403</v>
+        <v>0.4490148928919319</v>
       </c>
       <c r="G390" t="n">
-        <v>0.5495105193320607</v>
+        <v>0.5495105193328104</v>
       </c>
     </row>
     <row r="391">
@@ -11200,13 +11200,13 @@
         <v>2</v>
       </c>
       <c r="E391" t="n">
-        <v>0.0001871507220762313</v>
+        <v>0.0001871507220765717</v>
       </c>
       <c r="F391" t="n">
-        <v>0.5497923606819886</v>
+        <v>0.5497923606824885</v>
       </c>
       <c r="G391" t="n">
-        <v>0.4500204885958772</v>
+        <v>0.4500204885954679</v>
       </c>
     </row>
     <row r="392">
@@ -11223,13 +11223,13 @@
         <v>1</v>
       </c>
       <c r="E392" t="n">
-        <v>0.0007463993646067442</v>
+        <v>0.0007463993646053865</v>
       </c>
       <c r="F392" t="n">
-        <v>0.4385808316598922</v>
+        <v>0.4385808316590945</v>
       </c>
       <c r="G392" t="n">
-        <v>0.56067276897558</v>
+        <v>0.56067276897609</v>
       </c>
     </row>
     <row r="393">
@@ -11246,13 +11246,13 @@
         <v>2</v>
       </c>
       <c r="E393" t="n">
-        <v>0.0001727375589447729</v>
+        <v>0.0001727375589450086</v>
       </c>
       <c r="F393" t="n">
-        <v>0.5601941352257952</v>
+        <v>0.5601941352263048</v>
       </c>
       <c r="G393" t="n">
-        <v>0.4396331272151633</v>
+        <v>0.4396331272147634</v>
       </c>
     </row>
     <row r="394">
@@ -11269,13 +11269,13 @@
         <v>1</v>
       </c>
       <c r="E394" t="n">
-        <v>0.0005882951504220756</v>
+        <v>0.000588295150420738</v>
       </c>
       <c r="F394" t="n">
-        <v>0.4290228005644268</v>
+        <v>0.4290228005638416</v>
       </c>
       <c r="G394" t="n">
-        <v>0.5703889042852687</v>
+        <v>0.570388904285528</v>
       </c>
     </row>
     <row r="395">
@@ -11292,13 +11292,13 @@
         <v>2</v>
       </c>
       <c r="E395" t="n">
-        <v>0.0002181283663401985</v>
+        <v>0.0002181283663405953</v>
       </c>
       <c r="F395" t="n">
-        <v>0.5695697334614274</v>
+        <v>0.5695697334616864</v>
       </c>
       <c r="G395" t="n">
-        <v>0.4302121381723384</v>
+        <v>0.4302121381717515</v>
       </c>
     </row>
     <row r="396">
@@ -11315,13 +11315,13 @@
         <v>1</v>
       </c>
       <c r="E396" t="n">
-        <v>0.0005799143817029437</v>
+        <v>0.0005799143817024163</v>
       </c>
       <c r="F396" t="n">
-        <v>0.4200315278725926</v>
+        <v>0.4200315278724016</v>
       </c>
       <c r="G396" t="n">
-        <v>0.5793885577454896</v>
+        <v>0.5793885577460165</v>
       </c>
     </row>
     <row r="397">
@@ -11338,13 +11338,13 @@
         <v>2</v>
       </c>
       <c r="E397" t="n">
-        <v>0.000248326308831479</v>
+        <v>0.0002483263088322695</v>
       </c>
       <c r="F397" t="n">
-        <v>0.5785062443082059</v>
+        <v>0.578506244308469</v>
       </c>
       <c r="G397" t="n">
-        <v>0.4212454293831143</v>
+        <v>0.4212454293829228</v>
       </c>
     </row>
     <row r="398">
@@ -11361,13 +11361,13 @@
         <v>1</v>
       </c>
       <c r="E398" t="n">
-        <v>0.0005227943154027164</v>
+        <v>0.0005227943154022408</v>
       </c>
       <c r="F398" t="n">
-        <v>0.4133152718424878</v>
+        <v>0.4133152718422999</v>
       </c>
       <c r="G398" t="n">
-        <v>0.5861619338419586</v>
+        <v>0.5861619338424917</v>
       </c>
     </row>
     <row r="399">
@@ -11384,13 +11384,13 @@
         <v>2</v>
       </c>
       <c r="E399" t="n">
-        <v>0.000217177917654282</v>
+        <v>0.000217177917654677</v>
       </c>
       <c r="F399" t="n">
-        <v>0.5848844557133289</v>
+        <v>0.5848844557135949</v>
       </c>
       <c r="G399" t="n">
-        <v>0.4148983663689251</v>
+        <v>0.4148983663685477</v>
       </c>
     </row>
     <row r="400">
@@ -11407,13 +11407,13 @@
         <v>1</v>
       </c>
       <c r="E400" t="n">
-        <v>0.001063052998355917</v>
+        <v>0.001063052998355434</v>
       </c>
       <c r="F400" t="n">
-        <v>0.4067239499930965</v>
+        <v>0.4067239499929115</v>
       </c>
       <c r="G400" t="n">
-        <v>0.5922129970084009</v>
+        <v>0.5922129970089396</v>
       </c>
     </row>
     <row r="401">
@@ -11430,13 +11430,13 @@
         <v>2</v>
       </c>
       <c r="E401" t="n">
-        <v>0.000155297949037376</v>
+        <v>0.0001552979490375878</v>
       </c>
       <c r="F401" t="n">
-        <v>0.5918064429507992</v>
+        <v>0.5918064429510683</v>
       </c>
       <c r="G401" t="n">
-        <v>0.4080382591000597</v>
+        <v>0.4080382590996886</v>
       </c>
     </row>
     <row r="402">
@@ -11453,10 +11453,10 @@
         <v>1</v>
       </c>
       <c r="E402" t="n">
-        <v>0.0005876304180298386</v>
+        <v>0.0005876304180287697</v>
       </c>
       <c r="F402" t="n">
-        <v>0.3983975410464637</v>
+        <v>0.3983975410461013</v>
       </c>
       <c r="G402" t="n">
         <v>0.6010148285356439</v>
@@ -11476,13 +11476,13 @@
         <v>2</v>
       </c>
       <c r="E403" t="n">
-        <v>0.000132272811422849</v>
+        <v>0.0001322728114230896</v>
       </c>
       <c r="F403" t="n">
-        <v>0.6002570124197413</v>
+        <v>0.6002570124200142</v>
       </c>
       <c r="G403" t="n">
-        <v>0.3996107147689498</v>
+        <v>0.3996107147685864</v>
       </c>
     </row>
     <row r="404">
@@ -11499,13 +11499,13 @@
         <v>1</v>
       </c>
       <c r="E404" t="n">
-        <v>0.0006343729849302653</v>
+        <v>0.0006343729849293998</v>
       </c>
       <c r="F404" t="n">
-        <v>0.389460658740671</v>
+        <v>0.389460658740494</v>
       </c>
       <c r="G404" t="n">
-        <v>0.609904968274176</v>
+        <v>0.6099049682744534</v>
       </c>
     </row>
     <row r="405">
@@ -11522,10 +11522,10 @@
         <v>2</v>
       </c>
       <c r="E405" t="n">
-        <v>0.000226445140634606</v>
+        <v>0.000226445140635018</v>
       </c>
       <c r="F405" t="n">
-        <v>0.6092423267619851</v>
+        <v>0.6092423267622621</v>
       </c>
       <c r="G405" t="n">
         <v>0.3905312280972298</v>
@@ -11545,13 +11545,13 @@
         <v>1</v>
       </c>
       <c r="E406" t="n">
-        <v>0.0007100770075331695</v>
+        <v>0.0007100770075328466</v>
       </c>
       <c r="F406" t="n">
         <v>0.3791819632929062</v>
       </c>
       <c r="G406" t="n">
-        <v>0.6201079596994004</v>
+        <v>0.6201079596996824</v>
       </c>
     </row>
     <row r="407">
@@ -11568,13 +11568,13 @@
         <v>2</v>
       </c>
       <c r="E407" t="n">
-        <v>0.0001116875777904012</v>
+        <v>0.0001116875777906043</v>
       </c>
       <c r="F407" t="n">
         <v>0.6197646047791037</v>
       </c>
       <c r="G407" t="n">
-        <v>0.3801237076431027</v>
+        <v>0.3801237076429298</v>
       </c>
     </row>
     <row r="408">
@@ -11591,13 +11591,13 @@
         <v>1</v>
       </c>
       <c r="E408" t="n">
-        <v>0.0007302674821415505</v>
+        <v>0.0007302674821412185</v>
       </c>
       <c r="F408" t="n">
         <v>0.3684222067028098</v>
       </c>
       <c r="G408" t="n">
-        <v>0.6308475258149722</v>
+        <v>0.630847525815259</v>
       </c>
     </row>
     <row r="409">
@@ -11614,10 +11614,10 @@
         <v>2</v>
       </c>
       <c r="E409" t="n">
-        <v>0.0001020809760598015</v>
+        <v>0.0001020809760600336</v>
       </c>
       <c r="F409" t="n">
-        <v>0.63058931947448</v>
+        <v>0.6305893194747668</v>
       </c>
       <c r="G409" t="n">
         <v>0.3693085995492912</v>
@@ -11637,10 +11637,10 @@
         <v>1</v>
       </c>
       <c r="E410" t="n">
-        <v>0.0008381206732091685</v>
+        <v>0.0008381206732084063</v>
       </c>
       <c r="F410" t="n">
-        <v>0.3557178356928116</v>
+        <v>0.3557178356926499</v>
       </c>
       <c r="G410" t="n">
         <v>0.6434440436341214</v>
@@ -11660,13 +11660,13 @@
         <v>2</v>
       </c>
       <c r="E411" t="n">
-        <v>0.0001293339959378482</v>
+        <v>0.000129333995937907</v>
       </c>
       <c r="F411" t="n">
         <v>0.6432865059753812</v>
       </c>
       <c r="G411" t="n">
-        <v>0.3565841600287569</v>
+        <v>0.3565841600285947</v>
       </c>
     </row>
     <row r="412">
@@ -11683,13 +11683,13 @@
         <v>1</v>
       </c>
       <c r="E412" t="n">
-        <v>0.0009817299617173817</v>
+        <v>0.0009817299617169355</v>
       </c>
       <c r="F412" t="n">
         <v>0.3428675833449543</v>
       </c>
       <c r="G412" t="n">
-        <v>0.6561506866931979</v>
+        <v>0.6561506866934963</v>
       </c>
     </row>
     <row r="413">
@@ -11706,13 +11706,13 @@
         <v>2</v>
       </c>
       <c r="E413" t="n">
-        <v>0.0001098833102907284</v>
+        <v>0.0001098833102908784</v>
       </c>
       <c r="F413" t="n">
         <v>0.6562042510285874</v>
       </c>
       <c r="G413" t="n">
-        <v>0.3436858656613355</v>
+        <v>0.3436858656610229</v>
       </c>
     </row>
     <row r="414">
@@ -11729,10 +11729,10 @@
         <v>1</v>
       </c>
       <c r="E414" t="n">
-        <v>0.0006773497027105986</v>
+        <v>0.0006773497027096746</v>
       </c>
       <c r="F414" t="n">
-        <v>0.3309701056155606</v>
+        <v>0.3309701056154101</v>
       </c>
       <c r="G414" t="n">
         <v>0.6683525446819047</v>
@@ -11752,13 +11752,13 @@
         <v>2</v>
       </c>
       <c r="E415" t="n">
-        <v>0.0001361231741333269</v>
+        <v>0.0001361231741333888</v>
       </c>
       <c r="F415" t="n">
         <v>0.6679877848541249</v>
       </c>
       <c r="G415" t="n">
-        <v>0.3318760919718161</v>
+        <v>0.3318760919716652</v>
       </c>
     </row>
     <row r="416">
@@ -11778,7 +11778,7 @@
         <v>0.0008390715081629106</v>
       </c>
       <c r="F416" t="n">
-        <v>0.3189267058752197</v>
+        <v>0.3189267058750747</v>
       </c>
       <c r="G416" t="n">
         <v>0.6802342226166662</v>
@@ -11798,10 +11798,10 @@
         <v>2</v>
       </c>
       <c r="E417" t="n">
-        <v>0.0001004611508820344</v>
+        <v>0.0001004611508821714</v>
       </c>
       <c r="F417" t="n">
-        <v>0.6802245263189082</v>
+        <v>0.6802245263192175</v>
       </c>
       <c r="G417" t="n">
         <v>0.3196750125300886</v>
@@ -11821,13 +11821,13 @@
         <v>1</v>
       </c>
       <c r="E418" t="n">
-        <v>0.0008011777558104314</v>
+        <v>0.0008011777558093384</v>
       </c>
       <c r="F418" t="n">
-        <v>0.3060599969691038</v>
+        <v>0.3060599969688255</v>
       </c>
       <c r="G418" t="n">
-        <v>0.6931388252750837</v>
+        <v>0.6931388252753989</v>
       </c>
     </row>
     <row r="419">
@@ -11844,13 +11844,13 @@
         <v>2</v>
       </c>
       <c r="E419" t="n">
-        <v>0.0001005589172491637</v>
+        <v>0.0001005589172493466</v>
       </c>
       <c r="F419" t="n">
-        <v>0.6930396704104735</v>
+        <v>0.6930396704107887</v>
       </c>
       <c r="G419" t="n">
-        <v>0.3068597706724224</v>
+        <v>0.3068597706721434</v>
       </c>
     </row>
     <row r="420">
@@ -11867,10 +11867,10 @@
         <v>1</v>
       </c>
       <c r="E420" t="n">
-        <v>0.0006960588441114607</v>
+        <v>0.0006960588441101946</v>
       </c>
       <c r="F420" t="n">
-        <v>0.2942487334524621</v>
+        <v>0.2942487334521945</v>
       </c>
       <c r="G420" t="n">
         <v>0.7050552077034994</v>
@@ -11890,13 +11890,13 @@
         <v>2</v>
       </c>
       <c r="E421" t="n">
-        <v>0.0001196702424044756</v>
+        <v>0.0001196702424046933</v>
       </c>
       <c r="F421" t="n">
-        <v>0.704765623326299</v>
+        <v>0.7047656233266195</v>
       </c>
       <c r="G421" t="n">
-        <v>0.2951147064314038</v>
+        <v>0.2951147064311354</v>
       </c>
     </row>
     <row r="422">
@@ -11913,13 +11913,13 @@
         <v>1</v>
       </c>
       <c r="E422" t="n">
-        <v>0.0005192874273407999</v>
+        <v>0.0005192874273398552</v>
       </c>
       <c r="F422" t="n">
-        <v>0.2849701796118015</v>
+        <v>0.2849701796115423</v>
       </c>
       <c r="G422" t="n">
-        <v>0.7145105329609127</v>
+        <v>0.7145105329612377</v>
       </c>
     </row>
     <row r="423">
@@ -11936,13 +11936,13 @@
         <v>2</v>
       </c>
       <c r="E423" t="n">
-        <v>0.0001311727106783134</v>
+        <v>0.000131172710678552</v>
       </c>
       <c r="F423" t="n">
         <v>0.7138739407162914</v>
       </c>
       <c r="G423" t="n">
-        <v>0.2859948865731672</v>
+        <v>0.2859948865729071</v>
       </c>
     </row>
     <row r="424">
@@ -11959,13 +11959,13 @@
         <v>1</v>
       </c>
       <c r="E424" t="n">
-        <v>0.0006759713263634327</v>
+        <v>0.000675971326362818</v>
       </c>
       <c r="F424" t="n">
-        <v>0.2761522718131355</v>
+        <v>0.2761522718130099</v>
       </c>
       <c r="G424" t="n">
-        <v>0.7231717568604776</v>
+        <v>0.7231717568608065</v>
       </c>
     </row>
     <row r="425">
@@ -11982,13 +11982,13 @@
         <v>2</v>
       </c>
       <c r="E425" t="n">
-        <v>0.0001282267425333796</v>
+        <v>0.0001282267425334963</v>
       </c>
       <c r="F425" t="n">
-        <v>0.7227733765194317</v>
+        <v>0.7227733765197605</v>
       </c>
       <c r="G425" t="n">
-        <v>0.2770983967378129</v>
+        <v>0.2770983967376869</v>
       </c>
     </row>
     <row r="426">
@@ -12005,13 +12005,13 @@
         <v>1</v>
       </c>
       <c r="E426" t="n">
-        <v>0.0008437336958683234</v>
+        <v>0.0008437336958667887</v>
       </c>
       <c r="F426" t="n">
-        <v>0.2657779129740749</v>
+        <v>0.2657779129737123</v>
       </c>
       <c r="G426" t="n">
-        <v>0.7333783533300496</v>
+        <v>0.7333783533303831</v>
       </c>
     </row>
     <row r="427">
@@ -12028,13 +12028,13 @@
         <v>2</v>
       </c>
       <c r="E427" t="n">
-        <v>0.000592317833652716</v>
+        <v>0.0005923178336532547</v>
       </c>
       <c r="F427" t="n">
-        <v>0.7327694979213398</v>
+        <v>0.732769497921673</v>
       </c>
       <c r="G427" t="n">
-        <v>0.2666381842448401</v>
+        <v>0.2666381842447188</v>
       </c>
     </row>
     <row r="428">
@@ -12051,13 +12051,13 @@
         <v>1</v>
       </c>
       <c r="E428" t="n">
-        <v>0.007740944802174096</v>
+        <v>0.007740944802167055</v>
       </c>
       <c r="F428" t="n">
-        <v>0.2482476718085121</v>
+        <v>0.2482476718083992</v>
       </c>
       <c r="G428" t="n">
-        <v>0.7440113833892334</v>
+        <v>0.7440113833895718</v>
       </c>
     </row>
     <row r="429">
@@ -12074,13 +12074,13 @@
         <v>2</v>
       </c>
       <c r="E429" t="n">
-        <v>0.0003227446756195161</v>
+        <v>0.0003227446756196628</v>
       </c>
       <c r="F429" t="n">
-        <v>0.7508367241808421</v>
+        <v>0.7508367241811835</v>
       </c>
       <c r="G429" t="n">
-        <v>0.2488405311435163</v>
+        <v>0.2488405311434032</v>
       </c>
     </row>
     <row r="430">
@@ -12097,10 +12097,10 @@
         <v>1</v>
       </c>
       <c r="E430" t="n">
-        <v>0.001026768134243653</v>
+        <v>0.001026768134243186</v>
       </c>
       <c r="F430" t="n">
-        <v>0.2345541832837815</v>
+        <v>0.2345541832836748</v>
       </c>
       <c r="G430" t="n">
         <v>0.7644190485820941</v>
@@ -12120,13 +12120,13 @@
         <v>2</v>
       </c>
       <c r="E431" t="n">
-        <v>0.000223167332001805</v>
+        <v>0.0002231673320021095</v>
       </c>
       <c r="F431" t="n">
         <v>0.7645658199784469</v>
       </c>
       <c r="G431" t="n">
-        <v>0.235211012689724</v>
+        <v>0.235211012689617</v>
       </c>
     </row>
     <row r="432">
@@ -12143,10 +12143,10 @@
         <v>1</v>
       </c>
       <c r="E432" t="n">
-        <v>0.0006174554131706138</v>
+        <v>0.0006174554131700521</v>
       </c>
       <c r="F432" t="n">
-        <v>0.2258517721947746</v>
+        <v>0.2258517721944664</v>
       </c>
       <c r="G432" t="n">
         <v>0.7735307723922141</v>
@@ -12166,13 +12166,13 @@
         <v>2</v>
       </c>
       <c r="E433" t="n">
-        <v>0.0001129332927016047</v>
+        <v>0.0001129332927018101</v>
       </c>
       <c r="F433" t="n">
         <v>0.773082454854648</v>
       </c>
       <c r="G433" t="n">
-        <v>0.2268046118528702</v>
+        <v>0.2268046118526639</v>
       </c>
     </row>
     <row r="434">
@@ -12189,13 +12189,13 @@
         <v>1</v>
       </c>
       <c r="E434" t="n">
-        <v>0.0004785495785846218</v>
+        <v>0.0004785495785839689</v>
       </c>
       <c r="F434" t="n">
-        <v>0.2184708614008699</v>
+        <v>0.2184708614006712</v>
       </c>
       <c r="G434" t="n">
-        <v>0.78105058902046</v>
+        <v>0.7810505890208151</v>
       </c>
     </row>
     <row r="435">
@@ -12212,13 +12212,13 @@
         <v>2</v>
       </c>
       <c r="E435" t="n">
-        <v>0.0001508509126008265</v>
+        <v>0.0001508509126010322</v>
       </c>
       <c r="F435" t="n">
         <v>0.7804085167714072</v>
       </c>
       <c r="G435" t="n">
-        <v>0.219440632315965</v>
+        <v>0.2194406323158652</v>
       </c>
     </row>
     <row r="436">
@@ -12235,10 +12235,10 @@
         <v>1</v>
       </c>
       <c r="E436" t="n">
-        <v>0.0004298400074921948</v>
+        <v>0.0004298400074918039</v>
       </c>
       <c r="F436" t="n">
-        <v>0.2115257574935923</v>
+        <v>0.2115257574934</v>
       </c>
       <c r="G436" t="n">
         <v>0.7880444024989401</v>
@@ -12258,13 +12258,13 @@
         <v>2</v>
       </c>
       <c r="E437" t="n">
-        <v>0.000101815710333214</v>
+        <v>0.0001018157103333529</v>
       </c>
       <c r="F437" t="n">
         <v>0.7873441188790655</v>
       </c>
       <c r="G437" t="n">
-        <v>0.2125540654106156</v>
+        <v>0.2125540654104223</v>
       </c>
     </row>
     <row r="438">
@@ -12281,13 +12281,13 @@
         <v>1</v>
       </c>
       <c r="E438" t="n">
-        <v>0.0004257212996612305</v>
+        <v>0.0004257212996610369</v>
       </c>
       <c r="F438" t="n">
         <v>0.2043827797971236</v>
       </c>
       <c r="G438" t="n">
-        <v>0.7951914989030777</v>
+        <v>0.7951914989034393</v>
       </c>
     </row>
     <row r="439">
@@ -12304,13 +12304,13 @@
         <v>2</v>
       </c>
       <c r="E439" t="n">
-        <v>0.0001247171882397361</v>
+        <v>0.0001247171882398495</v>
       </c>
       <c r="F439" t="n">
         <v>0.7944959320979293</v>
       </c>
       <c r="G439" t="n">
-        <v>0.2053793507138208</v>
+        <v>0.205379350713634</v>
       </c>
     </row>
     <row r="440">
@@ -12327,10 +12327,10 @@
         <v>1</v>
       </c>
       <c r="E440" t="n">
-        <v>0.0004206673547540246</v>
+        <v>0.000420667354753642</v>
       </c>
       <c r="F440" t="n">
-        <v>0.1982876015349137</v>
+        <v>0.1982876015347333</v>
       </c>
       <c r="G440" t="n">
         <v>0.8012917311103939</v>
@@ -12350,13 +12350,13 @@
         <v>2</v>
       </c>
       <c r="E441" t="n">
-        <v>0.0001788777883344789</v>
+        <v>0.0001788777883347229</v>
       </c>
       <c r="F441" t="n">
-        <v>0.8004083907715475</v>
+        <v>0.8004083907719115</v>
       </c>
       <c r="G441" t="n">
-        <v>0.1994127314400121</v>
+        <v>0.1994127314399214</v>
       </c>
     </row>
     <row r="442">
@@ -12373,10 +12373,10 @@
         <v>1</v>
       </c>
       <c r="E442" t="n">
-        <v>0.000803198677515721</v>
+        <v>0.0008031986775146253</v>
       </c>
       <c r="F442" t="n">
-        <v>0.1928214905576257</v>
+        <v>0.1928214905574503</v>
       </c>
       <c r="G442" t="n">
         <v>0.8063753107648741</v>
@@ -12396,13 +12396,13 @@
         <v>2</v>
       </c>
       <c r="E443" t="n">
-        <v>0.0001649864580780532</v>
+        <v>0.0001649864580782783</v>
       </c>
       <c r="F443" t="n">
-        <v>0.8058707433794925</v>
+        <v>0.805870743379859</v>
       </c>
       <c r="G443" t="n">
-        <v>0.1939642701622658</v>
+        <v>0.1939642701621776</v>
       </c>
     </row>
     <row r="444">
@@ -12419,10 +12419,10 @@
         <v>1</v>
       </c>
       <c r="E444" t="n">
-        <v>0.0005615947918174793</v>
+        <v>0.0005615947918172239</v>
       </c>
       <c r="F444" t="n">
-        <v>0.187726068980413</v>
+        <v>0.1877260689802423</v>
       </c>
       <c r="G444" t="n">
         <v>0.8117123362278301</v>
@@ -12442,13 +12442,13 @@
         <v>2</v>
       </c>
       <c r="E445" t="n">
-        <v>0.0001876047581471917</v>
+        <v>0.0001876047581473623</v>
       </c>
       <c r="F445" t="n">
         <v>0.8108157933121551</v>
       </c>
       <c r="G445" t="n">
-        <v>0.1889966019298867</v>
+        <v>0.1889966019297148</v>
       </c>
     </row>
     <row r="446">
@@ -12465,13 +12465,13 @@
         <v>1</v>
       </c>
       <c r="E446" t="n">
-        <v>0.0006567650527754419</v>
+        <v>0.0006567650527751433</v>
       </c>
       <c r="F446" t="n">
-        <v>0.1824915264678987</v>
+        <v>0.1824915264678157</v>
       </c>
       <c r="G446" t="n">
-        <v>0.8168517084792298</v>
+        <v>0.8168517084796012</v>
       </c>
     </row>
     <row r="447">
@@ -12488,13 +12488,13 @@
         <v>2</v>
       </c>
       <c r="E447" t="n">
-        <v>0.0002367197536523119</v>
+        <v>0.0002367197536525272</v>
       </c>
       <c r="F447" t="n">
         <v>0.8163423057379564</v>
       </c>
       <c r="G447" t="n">
-        <v>0.1834209745084835</v>
+        <v>0.1834209745083167</v>
       </c>
     </row>
     <row r="448">
@@ -12511,13 +12511,13 @@
         <v>1</v>
       </c>
       <c r="E448" t="n">
-        <v>0.001317928997780537</v>
+        <v>0.001317928997779937</v>
       </c>
       <c r="F448" t="n">
-        <v>0.1748891689865177</v>
+        <v>0.1748891689864381</v>
       </c>
       <c r="G448" t="n">
-        <v>0.8237929020154985</v>
+        <v>0.8237929020158731</v>
       </c>
     </row>
     <row r="449">
@@ -12534,10 +12534,10 @@
         <v>2</v>
       </c>
       <c r="E449" t="n">
-        <v>0.002434152630635712</v>
+        <v>0.002434152630639033</v>
       </c>
       <c r="F449" t="n">
-        <v>0.8217193110665164</v>
+        <v>0.82171931106689</v>
       </c>
       <c r="G449" t="n">
         <v>0.1758465363026624</v>
@@ -12580,13 +12580,13 @@
         <v>2</v>
       </c>
       <c r="E451" t="n">
-        <v>0.0002119941414136054</v>
+        <v>0.000211994141413991</v>
       </c>
       <c r="F451" t="n">
         <v>0.8266332981815048</v>
       </c>
       <c r="G451" t="n">
-        <v>0.1731547076769957</v>
+        <v>0.1731547076770745</v>
       </c>
     </row>
     <row r="452">
@@ -12603,13 +12603,13 @@
         <v>1</v>
       </c>
       <c r="E452" t="n">
-        <v>0.0004036761066359693</v>
+        <v>0.0004036761066357857</v>
       </c>
       <c r="F452" t="n">
         <v>0.168568711674584</v>
       </c>
       <c r="G452" t="n">
-        <v>0.8310276122190042</v>
+        <v>0.8310276122186263</v>
       </c>
     </row>
     <row r="453">
@@ -12626,13 +12626,13 @@
         <v>2</v>
       </c>
       <c r="E453" t="n">
-        <v>0.0002042508682232872</v>
+        <v>0.0002042508682238445</v>
       </c>
       <c r="F453" t="n">
         <v>0.8296213007111579</v>
       </c>
       <c r="G453" t="n">
-        <v>0.1701744484205252</v>
+        <v>0.1701744484206026</v>
       </c>
     </row>
     <row r="454">
@@ -12672,13 +12672,13 @@
         <v>2</v>
       </c>
       <c r="E455" t="n">
-        <v>0.0004008900493126446</v>
+        <v>0.0004008900493131915</v>
       </c>
       <c r="F455" t="n">
         <v>0.8313380792758694</v>
       </c>
       <c r="G455" t="n">
-        <v>0.1682610306749227</v>
+        <v>0.1682610306748462</v>
       </c>
     </row>
     <row r="456">
@@ -12718,7 +12718,7 @@
         <v>2</v>
       </c>
       <c r="E457" t="n">
-        <v>0.0002892421662164213</v>
+        <v>0.0002892421662172105</v>
       </c>
       <c r="F457" t="n">
         <v>0.8335791160630529</v>
@@ -12741,10 +12741,10 @@
         <v>1</v>
       </c>
       <c r="E458" t="n">
-        <v>0.0002491764102400846</v>
+        <v>0.0002491764102399713</v>
       </c>
       <c r="F458" t="n">
-        <v>0.1630838287224444</v>
+        <v>0.1630838287223703</v>
       </c>
       <c r="G458" t="n">
         <v>0.8366669948675347</v>
@@ -12764,7 +12764,7 @@
         <v>2</v>
       </c>
       <c r="E459" t="n">
-        <v>0.0002709249361673381</v>
+        <v>0.0002709249361680773</v>
       </c>
       <c r="F459" t="n">
         <v>0.8344365287318154</v>
@@ -12787,7 +12787,7 @@
         <v>1</v>
       </c>
       <c r="E460" t="n">
-        <v>0.0004267986756303995</v>
+        <v>0.0004267986756305936</v>
       </c>
       <c r="F460" t="n">
         <v>0.1626133287823349</v>
@@ -12810,7 +12810,7 @@
         <v>2</v>
       </c>
       <c r="E461" t="n">
-        <v>0.004078880280637533</v>
+        <v>0.004078880280644953</v>
       </c>
       <c r="F461" t="n">
         <v>0.8307448735307613</v>
@@ -12833,10 +12833,10 @@
         <v>1</v>
       </c>
       <c r="E462" t="n">
-        <v>0.001229329740368095</v>
+        <v>0.001229329740369772</v>
       </c>
       <c r="F462" t="n">
-        <v>0.1661382978934456</v>
+        <v>0.1661382978935212</v>
       </c>
       <c r="G462" t="n">
         <v>0.8326323723659684</v>
@@ -12856,7 +12856,7 @@
         <v>2</v>
       </c>
       <c r="E463" t="n">
-        <v>0.0007458917715415321</v>
+        <v>0.0007458917715428889</v>
       </c>
       <c r="F463" t="n">
         <v>0.8301149079812453</v>
@@ -12882,7 +12882,7 @@
         <v>0.00101166516852673</v>
       </c>
       <c r="F464" t="n">
-        <v>0.1665540645209964</v>
+        <v>0.1665540645210722</v>
       </c>
       <c r="G464" t="n">
         <v>0.83243427031032</v>
@@ -12902,7 +12902,7 @@
         <v>2</v>
       </c>
       <c r="E465" t="n">
-        <v>0.0002645240831002342</v>
+        <v>0.0002645240831007154</v>
       </c>
       <c r="F465" t="n">
         <v>0.8306770462494443</v>
@@ -12925,10 +12925,10 @@
         <v>1</v>
       </c>
       <c r="E466" t="n">
-        <v>0.0003261603041830263</v>
+        <v>0.0003261603041831746</v>
       </c>
       <c r="F466" t="n">
-        <v>0.1662244698210272</v>
+        <v>0.1662244698211028</v>
       </c>
       <c r="G466" t="n">
         <v>0.8334493698747329</v>
@@ -12948,13 +12948,13 @@
         <v>2</v>
       </c>
       <c r="E467" t="n">
-        <v>0.0003794910098470921</v>
+        <v>0.0003794910098479549</v>
       </c>
       <c r="F467" t="n">
         <v>0.8308936213335992</v>
       </c>
       <c r="G467" t="n">
-        <v>0.1687268876566619</v>
+        <v>0.1687268876567386</v>
       </c>
     </row>
     <row r="468">
@@ -12974,10 +12974,10 @@
         <v>0.0003206298000242651</v>
       </c>
       <c r="F468" t="n">
-        <v>0.1665695803514335</v>
+        <v>0.1665695803515093</v>
       </c>
       <c r="G468" t="n">
-        <v>0.8331097898487453</v>
+        <v>0.8331097898483665</v>
       </c>
     </row>
     <row r="469">
@@ -12994,13 +12994,13 @@
         <v>2</v>
       </c>
       <c r="E469" t="n">
-        <v>0.0005253065607747797</v>
+        <v>0.0005253065607757352</v>
       </c>
       <c r="F469" t="n">
         <v>0.8304563186002903</v>
       </c>
       <c r="G469" t="n">
-        <v>0.1690183748388772</v>
+        <v>0.1690183748389541</v>
       </c>
     </row>
     <row r="470">
@@ -13017,10 +13017,10 @@
         <v>1</v>
       </c>
       <c r="E470" t="n">
-        <v>0.0004813649348941248</v>
+        <v>0.0004813649348945626</v>
       </c>
       <c r="F470" t="n">
-        <v>0.1665136473505973</v>
+        <v>0.1665136473507488</v>
       </c>
       <c r="G470" t="n">
         <v>0.833004987714413</v>
@@ -13040,13 +13040,13 @@
         <v>2</v>
       </c>
       <c r="E471" t="n">
-        <v>0.002395007400305862</v>
+        <v>0.002395007400306952</v>
       </c>
       <c r="F471" t="n">
         <v>0.8285131878568209</v>
       </c>
       <c r="G471" t="n">
-        <v>0.1690918047429394</v>
+        <v>0.1690918047430932</v>
       </c>
     </row>
     <row r="472">
@@ -13063,13 +13063,13 @@
         <v>1</v>
       </c>
       <c r="E472" t="n">
-        <v>0.00935867700808168</v>
+        <v>0.009358677008077423</v>
       </c>
       <c r="F472" t="n">
-        <v>0.1593883666977811</v>
+        <v>0.1593883666978536</v>
       </c>
       <c r="G472" t="n">
-        <v>0.8312529562942687</v>
+        <v>0.8312529562938907</v>
       </c>
     </row>
     <row r="473">
@@ -13086,13 +13086,13 @@
         <v>2</v>
       </c>
       <c r="E473" t="n">
-        <v>0.005961394394788925</v>
+        <v>0.005961394394786213</v>
       </c>
       <c r="F473" t="n">
-        <v>0.8330627003687532</v>
+        <v>0.8330627003683744</v>
       </c>
       <c r="G473" t="n">
-        <v>0.1609759052365683</v>
+        <v>0.1609759052367147</v>
       </c>
     </row>
     <row r="474">
@@ -13109,10 +13109,10 @@
         <v>1</v>
       </c>
       <c r="E474" t="n">
-        <v>0.01485481614686566</v>
+        <v>0.0148548161468589</v>
       </c>
       <c r="F474" t="n">
-        <v>0.1478447218282087</v>
+        <v>0.1478447218283431</v>
       </c>
       <c r="G474" t="n">
         <v>0.8373004620248146</v>
@@ -13132,13 +13132,13 @@
         <v>2</v>
       </c>
       <c r="E475" t="n">
-        <v>0.002469991725268311</v>
+        <v>0.002469991725267187</v>
       </c>
       <c r="F475" t="n">
-        <v>0.8488092332080436</v>
+        <v>0.8488092332076576</v>
       </c>
       <c r="G475" t="n">
-        <v>0.1487207750668373</v>
+        <v>0.148720775066905</v>
       </c>
     </row>
     <row r="476">
@@ -13155,10 +13155,10 @@
         <v>1</v>
       </c>
       <c r="E476" t="n">
-        <v>0.005290323148980373</v>
+        <v>0.005290323148982778</v>
       </c>
       <c r="F476" t="n">
-        <v>0.138896727969802</v>
+        <v>0.1388967279698652</v>
       </c>
       <c r="G476" t="n">
         <v>0.855812948881349</v>
@@ -13184,7 +13184,7 @@
         <v>0.8589114309384013</v>
       </c>
       <c r="G477" t="n">
-        <v>0.1393424211468221</v>
+        <v>0.1393424211467587</v>
       </c>
     </row>
     <row r="478">
@@ -13204,7 +13204,7 @@
         <v>0.001775863911128102</v>
       </c>
       <c r="F478" t="n">
-        <v>0.1297336989638477</v>
+        <v>0.1297336989637888</v>
       </c>
       <c r="G478" t="n">
         <v>0.8684904371249582</v>
@@ -13224,13 +13224,13 @@
         <v>2</v>
       </c>
       <c r="E479" t="n">
-        <v>0.00031944927118624</v>
+        <v>0.0003194492711863853</v>
       </c>
       <c r="F479" t="n">
         <v>0.8694673064145815</v>
       </c>
       <c r="G479" t="n">
-        <v>0.1302132443141018</v>
+        <v>0.130213244314161</v>
       </c>
     </row>
     <row r="480">
@@ -13247,7 +13247,7 @@
         <v>1</v>
       </c>
       <c r="E480" t="n">
-        <v>0.003015955479969559</v>
+        <v>0.00301595547997093</v>
       </c>
       <c r="F480" t="n">
         <v>0.1162207642369977</v>
@@ -13270,7 +13270,7 @@
         <v>2</v>
       </c>
       <c r="E481" t="n">
-        <v>0.0004262183171034597</v>
+        <v>0.0004262183171036535</v>
       </c>
       <c r="F481" t="n">
         <v>0.8829461825528777</v>
@@ -13293,10 +13293,10 @@
         <v>1</v>
       </c>
       <c r="E482" t="n">
-        <v>0.001385356561164528</v>
+        <v>0.001385356561166418</v>
       </c>
       <c r="F482" t="n">
-        <v>0.1042615753391799</v>
+        <v>0.1042615753392273</v>
       </c>
       <c r="G482" t="n">
         <v>0.8943530680997155</v>
@@ -13316,7 +13316,7 @@
         <v>2</v>
       </c>
       <c r="E483" t="n">
-        <v>0.0003421536983484128</v>
+        <v>0.0003421536983485685</v>
       </c>
       <c r="F483" t="n">
         <v>0.894996697516656</v>
@@ -13339,10 +13339,10 @@
         <v>1</v>
       </c>
       <c r="E484" t="n">
-        <v>0.001209192005638173</v>
+        <v>0.001209192005639273</v>
       </c>
       <c r="F484" t="n">
-        <v>0.09506565848992717</v>
+        <v>0.09506565848988394</v>
       </c>
       <c r="G484" t="n">
         <v>0.9037251495042932</v>
@@ -13362,10 +13362,10 @@
         <v>2</v>
       </c>
       <c r="E485" t="n">
-        <v>0.0005268764782255026</v>
+        <v>0.0005268764782262213</v>
       </c>
       <c r="F485" t="n">
-        <v>0.9039843986796564</v>
+        <v>0.9039843986800675</v>
       </c>
       <c r="G485" t="n">
         <v>0.09548872484193367</v>
@@ -13385,13 +13385,13 @@
         <v>1</v>
       </c>
       <c r="E486" t="n">
-        <v>0.001294037495832575</v>
+        <v>0.001294037495833751</v>
       </c>
       <c r="F486" t="n">
-        <v>0.08869701979959586</v>
+        <v>0.08869701979947486</v>
       </c>
       <c r="G486" t="n">
-        <v>0.9100089427044171</v>
+        <v>0.9100089427048309</v>
       </c>
     </row>
     <row r="487">
@@ -13408,13 +13408,13 @@
         <v>2</v>
       </c>
       <c r="E487" t="n">
-        <v>0.001048203567951919</v>
+        <v>0.001048203567952873</v>
       </c>
       <c r="F487" t="n">
         <v>0.9096430850959595</v>
       </c>
       <c r="G487" t="n">
-        <v>0.08930871133630296</v>
+        <v>0.08930871133622173</v>
       </c>
     </row>
     <row r="488">
@@ -13431,10 +13431,10 @@
         <v>1</v>
       </c>
       <c r="E488" t="n">
-        <v>0.0006344180574423892</v>
+        <v>0.0006344180574426777</v>
       </c>
       <c r="F488" t="n">
-        <v>0.08696919222899316</v>
+        <v>0.08696919222891406</v>
       </c>
       <c r="G488" t="n">
         <v>0.9123963897137668</v>
@@ -13454,13 +13454,13 @@
         <v>2</v>
       </c>
       <c r="E489" t="n">
-        <v>0.000162076672840003</v>
+        <v>0.0001620766728401504</v>
       </c>
       <c r="F489" t="n">
         <v>0.911628576992305</v>
       </c>
       <c r="G489" t="n">
-        <v>0.08820934633478164</v>
+        <v>0.08820934633470141</v>
       </c>
     </row>
     <row r="490">
@@ -13477,10 +13477,10 @@
         <v>1</v>
       </c>
       <c r="E490" t="n">
-        <v>0.0003684241425033217</v>
+        <v>0.0003684241425034892</v>
       </c>
       <c r="F490" t="n">
-        <v>0.08500322978296139</v>
+        <v>0.08500322978288408</v>
       </c>
       <c r="G490" t="n">
         <v>0.9146283460747316</v>
@@ -13506,7 +13506,7 @@
         <v>0.913296854418244</v>
       </c>
       <c r="G491" t="n">
-        <v>0.08628081712043593</v>
+        <v>0.08628081712031824</v>
       </c>
     </row>
     <row r="492">
@@ -13523,10 +13523,10 @@
         <v>1</v>
       </c>
       <c r="E492" t="n">
-        <v>0.0008022594710772283</v>
+        <v>0.0008022594710768634</v>
       </c>
       <c r="F492" t="n">
-        <v>0.08368100340136617</v>
+        <v>0.08368100340129006</v>
       </c>
       <c r="G492" t="n">
         <v>0.9155167371275135</v>
@@ -13546,13 +13546,13 @@
         <v>2</v>
       </c>
       <c r="E493" t="n">
-        <v>0.0007049837189838736</v>
+        <v>0.0007049837189845148</v>
       </c>
       <c r="F493" t="n">
         <v>0.9141349696752507</v>
       </c>
       <c r="G493" t="n">
-        <v>0.08516004660589178</v>
+        <v>0.08516004660581433</v>
       </c>
     </row>
     <row r="494">
@@ -13569,13 +13569,13 @@
         <v>1</v>
       </c>
       <c r="E494" t="n">
-        <v>0.0009515420735345645</v>
+        <v>0.0009515420735358626</v>
       </c>
       <c r="F494" t="n">
-        <v>0.08308517138389207</v>
+        <v>0.08308517138381651</v>
       </c>
       <c r="G494" t="n">
-        <v>0.9159632865423838</v>
+        <v>0.9159632865428003</v>
       </c>
     </row>
     <row r="495">
@@ -13592,13 +13592,13 @@
         <v>2</v>
       </c>
       <c r="E495" t="n">
-        <v>0.002151277436678294</v>
+        <v>0.002151277436680251</v>
       </c>
       <c r="F495" t="n">
         <v>0.9128700563442267</v>
       </c>
       <c r="G495" t="n">
-        <v>0.08497866621903342</v>
+        <v>0.08497866621895614</v>
       </c>
     </row>
     <row r="496">
@@ -13615,10 +13615,10 @@
         <v>1</v>
       </c>
       <c r="E496" t="n">
-        <v>0.001556270010232559</v>
+        <v>0.001556270010234682</v>
       </c>
       <c r="F496" t="n">
-        <v>0.08426062465711136</v>
+        <v>0.08426062465703472</v>
       </c>
       <c r="G496" t="n">
         <v>0.9141831053327326</v>
@@ -13638,13 +13638,13 @@
         <v>2</v>
       </c>
       <c r="E497" t="n">
-        <v>0.001031426444302067</v>
+        <v>0.001031426444303005</v>
       </c>
       <c r="F497" t="n">
         <v>0.9121412127069515</v>
       </c>
       <c r="G497" t="n">
-        <v>0.08682736084861492</v>
+        <v>0.08682736084853596</v>
       </c>
     </row>
     <row r="498">
@@ -13661,10 +13661,10 @@
         <v>1</v>
       </c>
       <c r="E498" t="n">
-        <v>0.0003679203291838926</v>
+        <v>0.0003679203291840599</v>
       </c>
       <c r="F498" t="n">
-        <v>0.08612783737534226</v>
+        <v>0.08612783737530309</v>
       </c>
       <c r="G498" t="n">
         <v>0.9135042422954809</v>
@@ -13684,13 +13684,13 @@
         <v>2</v>
       </c>
       <c r="E499" t="n">
-        <v>0.0003311086013759727</v>
+        <v>0.0003311086013762739</v>
       </c>
       <c r="F499" t="n">
         <v>0.9106711646688866</v>
       </c>
       <c r="G499" t="n">
-        <v>0.08899772672989203</v>
+        <v>0.08899772672985157</v>
       </c>
     </row>
     <row r="500">
@@ -13707,7 +13707,7 @@
         <v>1</v>
       </c>
       <c r="E500" t="n">
-        <v>0.0002133981001820592</v>
+        <v>0.0002133981001821562</v>
       </c>
       <c r="F500" t="n">
         <v>0.08773020819055698</v>
@@ -13730,13 +13730,13 @@
         <v>2</v>
       </c>
       <c r="E501" t="n">
-        <v>0.0001941960583721229</v>
+        <v>0.0001941960583722112</v>
       </c>
       <c r="F501" t="n">
         <v>0.909807559392549</v>
       </c>
       <c r="G501" t="n">
-        <v>0.0899982445490051</v>
+        <v>0.08999824454896417</v>
       </c>
     </row>
     <row r="502">
@@ -13756,7 +13756,7 @@
         <v>0.0002505389426455662</v>
       </c>
       <c r="F502" t="n">
-        <v>0.08817808803595344</v>
+        <v>0.08817808803587324</v>
       </c>
       <c r="G502" t="n">
         <v>0.9115713730215759</v>
@@ -13776,13 +13776,13 @@
         <v>2</v>
       </c>
       <c r="E503" t="n">
-        <v>0.0003031356237146008</v>
+        <v>0.0003031356237148765</v>
       </c>
       <c r="F503" t="n">
         <v>0.9092838478986094</v>
       </c>
       <c r="G503" t="n">
-        <v>0.09041301647780613</v>
+        <v>0.0904130164777239</v>
       </c>
     </row>
     <row r="504">
@@ -13799,13 +13799,13 @@
         <v>1</v>
       </c>
       <c r="E504" t="n">
-        <v>0.0001639031252323661</v>
+        <v>0.0001639031252325152</v>
       </c>
       <c r="F504" t="n">
-        <v>0.08912570358030167</v>
+        <v>0.08912570358026115</v>
       </c>
       <c r="G504" t="n">
-        <v>0.9107103932942547</v>
+        <v>0.9107103932946689</v>
       </c>
     </row>
     <row r="505">
@@ -13822,13 +13822,13 @@
         <v>2</v>
       </c>
       <c r="E505" t="n">
-        <v>0.000255354138648071</v>
+        <v>0.0002553541386483032</v>
       </c>
       <c r="F505" t="n">
         <v>0.9077834529229377</v>
       </c>
       <c r="G505" t="n">
-        <v>0.09196119293857601</v>
+        <v>0.09196119293845055</v>
       </c>
     </row>
     <row r="506">
@@ -13848,7 +13848,7 @@
         <v>0.0003099057104418575</v>
       </c>
       <c r="F506" t="n">
-        <v>0.09045324627121364</v>
+        <v>0.09045324627113137</v>
       </c>
       <c r="G506" t="n">
         <v>0.9092368480183227</v>
@@ -13874,7 +13874,7 @@
         <v>0.9026455067979928</v>
       </c>
       <c r="G507" t="n">
-        <v>0.09331080413359068</v>
+        <v>0.0933108041335058</v>
       </c>
     </row>
     <row r="508">
@@ -13891,10 +13891,10 @@
         <v>1</v>
       </c>
       <c r="E508" t="n">
-        <v>0.004790475844166207</v>
+        <v>0.004790475844164028</v>
       </c>
       <c r="F508" t="n">
-        <v>0.0912803439470433</v>
+        <v>0.0912803439470018</v>
       </c>
       <c r="G508" t="n">
         <v>0.9039291802089374</v>
@@ -13920,7 +13920,7 @@
         <v>0.8531855226056485</v>
       </c>
       <c r="G509" t="n">
-        <v>0.09412804961049454</v>
+        <v>0.09412804961045174</v>
       </c>
     </row>
     <row r="510">
@@ -13937,13 +13937,13 @@
         <v>0</v>
       </c>
       <c r="E510" t="n">
-        <v>0.1455058925756227</v>
+        <v>0.1455058925755565</v>
       </c>
       <c r="F510" t="n">
-        <v>0.0001650511912139287</v>
+        <v>0.0001650511912152798</v>
       </c>
       <c r="G510" t="n">
-        <v>0.8543290562330315</v>
+        <v>0.8543290562334199</v>
       </c>
     </row>
     <row r="511">
@@ -13963,10 +13963,10 @@
         <v>0.9999362045987442</v>
       </c>
       <c r="F511" t="n">
-        <v>6.15949980131052e-07</v>
+        <v>6.15949980139175e-07</v>
       </c>
       <c r="G511" t="n">
-        <v>6.317945113550325e-05</v>
+        <v>6.317945113553198e-05</v>
       </c>
     </row>
     <row r="512">
@@ -13986,10 +13986,10 @@
         <v>1</v>
       </c>
       <c r="F512" t="n">
-        <v>7.295839881705639e-18</v>
+        <v>7.295839881722228e-18</v>
       </c>
       <c r="G512" t="n">
-        <v>1.939659925382244e-21</v>
+        <v>1.939659925388418e-21</v>
       </c>
     </row>
     <row r="513">
@@ -14009,10 +14009,10 @@
         <v>0.9999109450625404</v>
       </c>
       <c r="F513" t="n">
-        <v>8.805124263506482e-05</v>
+        <v>8.805124263530506e-05</v>
       </c>
       <c r="G513" t="n">
-        <v>1.003694634435555e-06</v>
+        <v>1.003694634439206e-06</v>
       </c>
     </row>
     <row r="514">
@@ -14032,10 +14032,10 @@
         <v>0.9999147233721564</v>
       </c>
       <c r="F514" t="n">
-        <v>7.503225470641772e-08</v>
+        <v>7.503225470706601e-08</v>
       </c>
       <c r="G514" t="n">
-        <v>8.520159550517947e-05</v>
+        <v>8.52015955052957e-05</v>
       </c>
     </row>
     <row r="515">
@@ -14055,10 +14055,10 @@
         <v>0.9999889027423727</v>
       </c>
       <c r="F515" t="n">
-        <v>1.10680796634604e-05</v>
+        <v>1.106807966348054e-05</v>
       </c>
       <c r="G515" t="n">
-        <v>2.917786339982602e-08</v>
+        <v>2.917786339983929e-08</v>
       </c>
     </row>
     <row r="516">
@@ -14078,10 +14078,10 @@
         <v>0.9997404610359998</v>
       </c>
       <c r="F516" t="n">
-        <v>0.0002476564268976919</v>
+        <v>0.0002476564268980297</v>
       </c>
       <c r="G516" t="n">
-        <v>1.188253700819526e-05</v>
+        <v>1.188253700822228e-05</v>
       </c>
     </row>
     <row r="517">
@@ -14101,10 +14101,10 @@
         <v>0.9997535052384324</v>
       </c>
       <c r="F517" t="n">
-        <v>2.170062055385811e-07</v>
+        <v>2.170062055413442e-07</v>
       </c>
       <c r="G517" t="n">
-        <v>0.0002462777555159441</v>
+        <v>0.0002462777555162801</v>
       </c>
     </row>
     <row r="518">
@@ -14124,10 +14124,10 @@
         <v>0.9999999812894205</v>
       </c>
       <c r="F518" t="n">
-        <v>7.078663224338714e-10</v>
+        <v>7.078663224409532e-10</v>
       </c>
       <c r="G518" t="n">
-        <v>1.800261280925365e-08</v>
+        <v>1.800261280929459e-08</v>
       </c>
     </row>
     <row r="519">
@@ -14147,10 +14147,10 @@
         <v>0.9999972129210349</v>
       </c>
       <c r="F519" t="n">
-        <v>2.786448646607599e-06</v>
+        <v>2.786448646613935e-06</v>
       </c>
       <c r="G519" t="n">
-        <v>6.301303773365814e-10</v>
+        <v>6.301303773388737e-10</v>
       </c>
     </row>
     <row r="520">
@@ -14170,10 +14170,10 @@
         <v>0.9228147677057859</v>
       </c>
       <c r="F520" t="n">
-        <v>0.07717809395415454</v>
+        <v>0.07717809395425983</v>
       </c>
       <c r="G520" t="n">
-        <v>7.138339951748407e-06</v>
+        <v>7.138339951771129e-06</v>
       </c>
     </row>
     <row r="521">
@@ -14193,10 +14193,10 @@
         <v>0.9164635812487588</v>
       </c>
       <c r="F521" t="n">
-        <v>0.006344136770034412</v>
+        <v>0.006344136770040183</v>
       </c>
       <c r="G521" t="n">
-        <v>0.07719228198103892</v>
+        <v>0.07719228198107403</v>
       </c>
     </row>
     <row r="522">
@@ -14216,10 +14216,10 @@
         <v>0.9389891722329629</v>
       </c>
       <c r="F522" t="n">
-        <v>0.05460296145038964</v>
+        <v>0.05460296145041447</v>
       </c>
       <c r="G522" t="n">
-        <v>0.006407866316840806</v>
+        <v>0.006407866316846635</v>
       </c>
     </row>
     <row r="523">
@@ -14239,10 +14239,10 @@
         <v>0.9378474310943723</v>
       </c>
       <c r="F523" t="n">
-        <v>0.00738265557493323</v>
+        <v>0.007382655574946658</v>
       </c>
       <c r="G523" t="n">
-        <v>0.05476991333084381</v>
+        <v>0.05476991333086871</v>
       </c>
     </row>
     <row r="524">
@@ -14262,10 +14262,10 @@
         <v>0.9725235696561609</v>
       </c>
       <c r="F524" t="n">
-        <v>0.02004752374704767</v>
+        <v>0.02004752374707502</v>
       </c>
       <c r="G524" t="n">
-        <v>0.007428906596950459</v>
+        <v>0.007428906596960595</v>
       </c>
     </row>
     <row r="525">
@@ -14285,10 +14285,10 @@
         <v>0.9614300561605119</v>
       </c>
       <c r="F525" t="n">
-        <v>0.01849955711426859</v>
+        <v>0.01849955711430224</v>
       </c>
       <c r="G525" t="n">
-        <v>0.02007038672514833</v>
+        <v>0.02007038672517571</v>
       </c>
     </row>
     <row r="526">
@@ -14308,10 +14308,10 @@
         <v>0.9631241203408447</v>
       </c>
       <c r="F526" t="n">
-        <v>0.01818399836324659</v>
+        <v>0.0181839983632714</v>
       </c>
       <c r="G526" t="n">
-        <v>0.01869188129569849</v>
+        <v>0.01869188129572399</v>
       </c>
     </row>
     <row r="527">
@@ -14328,13 +14328,13 @@
         <v>0</v>
       </c>
       <c r="E527" t="n">
-        <v>0.9553569238763764</v>
+        <v>0.955356923875942</v>
       </c>
       <c r="F527" t="n">
-        <v>0.02641460226526655</v>
+        <v>0.02641460226529057</v>
       </c>
       <c r="G527" t="n">
-        <v>0.01822847385855343</v>
+        <v>0.0182284738585783</v>
       </c>
     </row>
     <row r="528">
@@ -14354,10 +14354,10 @@
         <v>0.9534923808731949</v>
       </c>
       <c r="F528" t="n">
-        <v>0.01989878472191609</v>
+        <v>0.01989878472194324</v>
       </c>
       <c r="G528" t="n">
-        <v>0.02660883440480322</v>
+        <v>0.02660883440483952</v>
       </c>
     </row>
     <row r="529">
@@ -14377,10 +14377,10 @@
         <v>0.9667161666467704</v>
       </c>
       <c r="F529" t="n">
-        <v>0.01332437660946392</v>
+        <v>0.01332437660948209</v>
       </c>
       <c r="G529" t="n">
-        <v>0.01995945674355041</v>
+        <v>0.01995945674357763</v>
       </c>
     </row>
     <row r="530">
@@ -14400,10 +14400,10 @@
         <v>0.9859620996371132</v>
       </c>
       <c r="F530" t="n">
-        <v>0.0006591284611222902</v>
+        <v>0.0006591284611231895</v>
       </c>
       <c r="G530" t="n">
-        <v>0.01337877190163092</v>
+        <v>0.01337877190164309</v>
       </c>
     </row>
     <row r="531">
@@ -14423,10 +14423,10 @@
         <v>0.9990717429850895</v>
       </c>
       <c r="F531" t="n">
-        <v>0.000272121340246581</v>
+        <v>0.0002721213402469523</v>
       </c>
       <c r="G531" t="n">
-        <v>0.0006561356744504956</v>
+        <v>0.0006561356744513908</v>
       </c>
     </row>
     <row r="532">
@@ -14446,10 +14446,10 @@
         <v>0.9996933938342849</v>
       </c>
       <c r="F532" t="n">
-        <v>3.418564728539002e-05</v>
+        <v>3.418564728543665e-05</v>
       </c>
       <c r="G532" t="n">
-        <v>0.0002724205183016689</v>
+        <v>0.0002724205183019167</v>
       </c>
     </row>
     <row r="533">
@@ -14469,10 +14469,10 @@
         <v>0.9999650605901814</v>
       </c>
       <c r="F533" t="n">
-        <v>1.136516066532935e-06</v>
+        <v>1.136516066534486e-06</v>
       </c>
       <c r="G533" t="n">
-        <v>3.380289376761581e-05</v>
+        <v>3.380289376764655e-05</v>
       </c>
     </row>
     <row r="534">
@@ -14492,10 +14492,10 @@
         <v>0.9977734063459591</v>
       </c>
       <c r="F534" t="n">
-        <v>0.002225515463570045</v>
+        <v>0.002225515463573081</v>
       </c>
       <c r="G534" t="n">
-        <v>1.078190463485018e-06</v>
+        <v>1.078190463485998e-06</v>
       </c>
     </row>
     <row r="535">
@@ -14515,10 +14515,10 @@
         <v>0.9553591172578785</v>
       </c>
       <c r="F535" t="n">
-        <v>0.04227091387943266</v>
+        <v>0.0422709138794711</v>
       </c>
       <c r="G535" t="n">
-        <v>0.002369968862544004</v>
+        <v>0.002369968862547237</v>
       </c>
     </row>
     <row r="536">
@@ -14633,7 +14633,7 @@
         <v>0.8058679781678878</v>
       </c>
       <c r="G540" t="n">
-        <v>0.1930714533860977</v>
+        <v>0.1930714533861855</v>
       </c>
     </row>
     <row r="541">
@@ -14653,7 +14653,7 @@
         <v>0.004609971688071561</v>
       </c>
       <c r="F541" t="n">
-        <v>0.1800569958848703</v>
+        <v>0.1800569958847884</v>
       </c>
       <c r="G541" t="n">
         <v>0.8153330324271493</v>
@@ -14673,13 +14673,13 @@
         <v>1</v>
       </c>
       <c r="E542" t="n">
-        <v>0.01276521042369976</v>
+        <v>0.01276521042370556</v>
       </c>
       <c r="F542" t="n">
         <v>0.8065785279644039</v>
       </c>
       <c r="G542" t="n">
-        <v>0.1806562616119325</v>
+        <v>0.1806562616120147</v>
       </c>
     </row>
     <row r="543">
@@ -14719,7 +14719,7 @@
         <v>1</v>
       </c>
       <c r="E544" t="n">
-        <v>0.007282211445894758</v>
+        <v>0.00728221144589807</v>
       </c>
       <c r="F544" t="n">
         <v>0.8216622537045303</v>
@@ -14745,7 +14745,7 @@
         <v>0.006703228474400887</v>
       </c>
       <c r="F545" t="n">
-        <v>0.1671749582750861</v>
+        <v>0.1671749582749341</v>
       </c>
       <c r="G545" t="n">
         <v>0.8261218132505228</v>
@@ -14765,13 +14765,13 @@
         <v>1</v>
       </c>
       <c r="E546" t="n">
-        <v>0.006151826426019129</v>
+        <v>0.006151826426021927</v>
       </c>
       <c r="F546" t="n">
         <v>0.8256626509084902</v>
       </c>
       <c r="G546" t="n">
-        <v>0.1681855226654418</v>
+        <v>0.1681855226653654</v>
       </c>
     </row>
     <row r="547">
@@ -14788,10 +14788,10 @@
         <v>2</v>
       </c>
       <c r="E547" t="n">
-        <v>0.002445378633686201</v>
+        <v>0.002445378633687314</v>
       </c>
       <c r="F547" t="n">
-        <v>0.1690292306668078</v>
+        <v>0.1690292306667309</v>
       </c>
       <c r="G547" t="n">
         <v>0.8285253906993978</v>
@@ -14811,7 +14811,7 @@
         <v>1</v>
       </c>
       <c r="E548" t="n">
-        <v>0.002363405799722225</v>
+        <v>0.002363405799724374</v>
       </c>
       <c r="F548" t="n">
         <v>0.8262688271193976</v>
@@ -14834,10 +14834,10 @@
         <v>2</v>
       </c>
       <c r="E549" t="n">
-        <v>0.004111130195579452</v>
+        <v>0.00411113019558319</v>
       </c>
       <c r="F549" t="n">
-        <v>0.1668431022268928</v>
+        <v>0.1668431022269687</v>
       </c>
       <c r="G549" t="n">
         <v>0.8290457675776155</v>
@@ -14857,13 +14857,13 @@
         <v>1</v>
       </c>
       <c r="E550" t="n">
-        <v>0.008745969974665476</v>
+        <v>0.008745969974661498</v>
       </c>
       <c r="F550" t="n">
         <v>0.8221196204198006</v>
       </c>
       <c r="G550" t="n">
-        <v>0.1691344096053108</v>
+        <v>0.1691344096053878</v>
       </c>
     </row>
     <row r="551">
@@ -14880,7 +14880,7 @@
         <v>2</v>
       </c>
       <c r="E551" t="n">
-        <v>0.02030771079000632</v>
+        <v>0.02030771079002479</v>
       </c>
       <c r="F551" t="n">
         <v>0.1547205419099692</v>
@@ -14903,13 +14903,13 @@
         <v>1</v>
       </c>
       <c r="E552" t="n">
-        <v>0.07559361825532165</v>
+        <v>0.0755936182553904</v>
       </c>
       <c r="F552" t="n">
         <v>0.7676162842704226</v>
       </c>
       <c r="G552" t="n">
-        <v>0.1567900974743028</v>
+        <v>0.1567900974743741</v>
       </c>
     </row>
     <row r="553">
@@ -14926,10 +14926,10 @@
         <v>2</v>
       </c>
       <c r="E553" t="n">
-        <v>0.02245857010022241</v>
+        <v>0.02245857010024283</v>
       </c>
       <c r="F553" t="n">
-        <v>0.2094085263579959</v>
+        <v>0.2094085263580912</v>
       </c>
       <c r="G553" t="n">
         <v>0.7681329035417437</v>
@@ -14952,7 +14952,7 @@
         <v>0.01199669610589489</v>
       </c>
       <c r="F554" t="n">
-        <v>0.7714239407028329</v>
+        <v>0.7714239407024821</v>
       </c>
       <c r="G554" t="n">
         <v>0.2165793631914791</v>
@@ -14972,13 +14972,13 @@
         <v>2</v>
       </c>
       <c r="E555" t="n">
-        <v>0.009250650389611297</v>
+        <v>0.009250650389615504</v>
       </c>
       <c r="F555" t="n">
-        <v>0.2182263960105031</v>
+        <v>0.2182263960106023</v>
       </c>
       <c r="G555" t="n">
-        <v>0.7725229535999423</v>
+        <v>0.7725229535995909</v>
       </c>
     </row>
     <row r="556">
@@ -14995,13 +14995,13 @@
         <v>1</v>
       </c>
       <c r="E556" t="n">
-        <v>0.004727690424546818</v>
+        <v>0.004727690424548968</v>
       </c>
       <c r="F556" t="n">
         <v>0.7733990046122775</v>
       </c>
       <c r="G556" t="n">
-        <v>0.2218733049633684</v>
+        <v>0.2218733049632675</v>
       </c>
     </row>
     <row r="557">
@@ -15018,7 +15018,7 @@
         <v>2</v>
       </c>
       <c r="E557" t="n">
-        <v>0.001138813679538284</v>
+        <v>0.001138813679540355</v>
       </c>
       <c r="F557" t="n">
         <v>0.2233445165380079</v>
@@ -15041,13 +15041,13 @@
         <v>1</v>
       </c>
       <c r="E558" t="n">
-        <v>0.0003643285739497529</v>
+        <v>0.00036432857395025</v>
       </c>
       <c r="F558" t="n">
         <v>0.7729759484737139</v>
       </c>
       <c r="G558" t="n">
-        <v>0.2266597229523799</v>
+        <v>0.2266597229522768</v>
       </c>
     </row>
     <row r="559">
@@ -15064,7 +15064,7 @@
         <v>2</v>
       </c>
       <c r="E559" t="n">
-        <v>0.0002689306722346102</v>
+        <v>0.0002689306722352217</v>
       </c>
       <c r="F559" t="n">
         <v>0.2241260374091941</v>
@@ -15087,7 +15087,7 @@
         <v>1</v>
       </c>
       <c r="E560" t="n">
-        <v>0.0005685187398612426</v>
+        <v>0.0005685187398617598</v>
       </c>
       <c r="F560" t="n">
         <v>0.772004921570849</v>
@@ -15110,10 +15110,10 @@
         <v>2</v>
       </c>
       <c r="E561" t="n">
-        <v>0.0004573531964085053</v>
+        <v>0.0004573531964091293</v>
       </c>
       <c r="F561" t="n">
-        <v>0.225344183042345</v>
+        <v>0.2253441830424474</v>
       </c>
       <c r="G561" t="n">
         <v>0.7741984637610407</v>
@@ -15133,13 +15133,13 @@
         <v>1</v>
       </c>
       <c r="E562" t="n">
-        <v>0.000691840087864103</v>
+        <v>0.0006918400878647322</v>
       </c>
       <c r="F562" t="n">
         <v>0.7711479566834289</v>
       </c>
       <c r="G562" t="n">
-        <v>0.2281602032286783</v>
+        <v>0.2281602032288859</v>
       </c>
     </row>
     <row r="563">
@@ -15156,10 +15156,10 @@
         <v>2</v>
       </c>
       <c r="E563" t="n">
-        <v>0.0007415098716670668</v>
+        <v>0.0007415098716684155</v>
       </c>
       <c r="F563" t="n">
-        <v>0.2251502025552171</v>
+        <v>0.2251502025553195</v>
       </c>
       <c r="G563" t="n">
         <v>0.7741082875729011</v>
@@ -15179,13 +15179,13 @@
         <v>1</v>
       </c>
       <c r="E564" t="n">
-        <v>0.001538737144746131</v>
+        <v>0.00153873714474753</v>
       </c>
       <c r="F564" t="n">
-        <v>0.7704401240396992</v>
+        <v>0.7704401240393489</v>
       </c>
       <c r="G564" t="n">
-        <v>0.2280211388156392</v>
+        <v>0.2280211388157428</v>
       </c>
     </row>
     <row r="565">
@@ -15202,10 +15202,10 @@
         <v>2</v>
       </c>
       <c r="E565" t="n">
-        <v>0.000314244301855909</v>
+        <v>0.0003142443018561948</v>
       </c>
       <c r="F565" t="n">
-        <v>0.2277776716946174</v>
+        <v>0.227777671694721</v>
       </c>
       <c r="G565" t="n">
         <v>0.771908084003623</v>
@@ -15225,13 +15225,13 @@
         <v>1</v>
       </c>
       <c r="E566" t="n">
-        <v>0.0006792788957952816</v>
+        <v>0.0006792788957955904</v>
       </c>
       <c r="F566" t="n">
-        <v>0.7662727430887305</v>
+        <v>0.766272743088382</v>
       </c>
       <c r="G566" t="n">
-        <v>0.2330479780156789</v>
+        <v>0.2330479780157848</v>
       </c>
     </row>
     <row r="567">
@@ -15248,10 +15248,10 @@
         <v>2</v>
       </c>
       <c r="E567" t="n">
-        <v>0.001073467375059929</v>
+        <v>0.001073467375061882</v>
       </c>
       <c r="F567" t="n">
-        <v>0.2310295193683717</v>
+        <v>0.2310295193684767</v>
       </c>
       <c r="G567" t="n">
         <v>0.7678970132564726</v>
@@ -15271,13 +15271,13 @@
         <v>1</v>
       </c>
       <c r="E568" t="n">
-        <v>0.0008641487342518658</v>
+        <v>0.0008641487342526518</v>
       </c>
       <c r="F568" t="n">
-        <v>0.7637721251439624</v>
+        <v>0.7637721251436151</v>
       </c>
       <c r="G568" t="n">
-        <v>0.2353637261219191</v>
+        <v>0.2353637261220262</v>
       </c>
     </row>
     <row r="569">
@@ -15294,10 +15294,10 @@
         <v>2</v>
       </c>
       <c r="E569" t="n">
-        <v>0.0002755326458847612</v>
+        <v>0.0002755326458852624</v>
       </c>
       <c r="F569" t="n">
-        <v>0.2345639666613062</v>
+        <v>0.2345639666615195</v>
       </c>
       <c r="G569" t="n">
         <v>0.7651605006928081</v>
@@ -15317,13 +15317,13 @@
         <v>1</v>
       </c>
       <c r="E570" t="n">
-        <v>0.0004221082979120663</v>
+        <v>0.0004221082979124502</v>
       </c>
       <c r="F570" t="n">
-        <v>0.7595370926798685</v>
+        <v>0.7595370926795231</v>
       </c>
       <c r="G570" t="n">
-        <v>0.2400407990221787</v>
+        <v>0.240040799022397</v>
       </c>
     </row>
     <row r="571">
@@ -15340,13 +15340,13 @@
         <v>2</v>
       </c>
       <c r="E571" t="n">
-        <v>0.0003216170462560103</v>
+        <v>0.000321617046256449</v>
       </c>
       <c r="F571" t="n">
-        <v>0.2384651006270526</v>
+        <v>0.2384651006273779</v>
       </c>
       <c r="G571" t="n">
-        <v>0.7612132823265171</v>
+        <v>0.7612132823261709</v>
       </c>
     </row>
     <row r="572">
@@ -15363,13 +15363,13 @@
         <v>1</v>
       </c>
       <c r="E572" t="n">
-        <v>0.001439136028152206</v>
+        <v>0.001439136028153515</v>
       </c>
       <c r="F572" t="n">
         <v>0.7547396275496773</v>
       </c>
       <c r="G572" t="n">
-        <v>0.2438212364220244</v>
+        <v>0.243821236422357</v>
       </c>
     </row>
     <row r="573">
@@ -15386,13 +15386,13 @@
         <v>2</v>
       </c>
       <c r="E573" t="n">
-        <v>0.000254226800512047</v>
+        <v>0.0002542268005121627</v>
       </c>
       <c r="F573" t="n">
-        <v>0.2439010433073668</v>
+        <v>0.2439010433075886</v>
       </c>
       <c r="G573" t="n">
-        <v>0.7558447298922815</v>
+        <v>0.7558447298919377</v>
       </c>
     </row>
     <row r="574">
@@ -15409,13 +15409,13 @@
         <v>1</v>
       </c>
       <c r="E574" t="n">
-        <v>0.001518273948197559</v>
+        <v>0.001518273948196179</v>
       </c>
       <c r="F574" t="n">
-        <v>0.746642440171489</v>
+        <v>0.7466424401711493</v>
       </c>
       <c r="G574" t="n">
-        <v>0.2518392858805246</v>
+        <v>0.2518392858807537</v>
       </c>
     </row>
     <row r="575">
@@ -15432,13 +15432,13 @@
         <v>2</v>
       </c>
       <c r="E575" t="n">
-        <v>0.003029824489821393</v>
+        <v>0.003029824489820016</v>
       </c>
       <c r="F575" t="n">
-        <v>0.2491666280651786</v>
+        <v>0.2491666280655185</v>
       </c>
       <c r="G575" t="n">
-        <v>0.7478035474451923</v>
+        <v>0.7478035474445122</v>
       </c>
     </row>
   </sheetData>
